--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="posts" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,7 +482,6 @@
           <t>来ましたー！</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -513,7 +512,6 @@
           <t>気になって来てみました♪</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -546,7 +544,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -579,7 +576,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -610,7 +606,6 @@
           <t>来ましたー</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -643,7 +638,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -674,7 +668,6 @@
           <t>きたよん</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -705,7 +698,6 @@
           <t>きたぞ</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -738,7 +730,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -771,7 +762,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -802,7 +792,6 @@
           <t>はじめてです！</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -833,7 +822,6 @@
           <t>あそびきてみました！</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -864,7 +852,6 @@
           <t>べろべろんちょ</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -897,7 +884,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -930,7 +916,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -963,7 +948,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1064,6 +1048,1286 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>26656</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>22:30:42</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>はなまる</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>久しぶりの</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>日曜日</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>26657</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>22:31:02</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>26658</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>22:33:32</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>26659</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>22:35:17</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>26660</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>22:46:52</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ゆうと</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>これから行こうと思います</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>26661</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>23:05:54</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>26662</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>23:11:17</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>カー</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26663</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>23:11:36</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26664</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>23:45:37</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ミコト、まいまい、テクノ</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ちいかわ</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>トークに</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>26665</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>23:45:57</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>26666</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>00:14:17</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>りょうちゃん</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>バンビ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>はしご</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26667</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>00:14:41</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>26668</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>01:18:22</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>らうら</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>少し</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>きたんご</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>26669</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>01:18:40</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>26672</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>19:02:51</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>タツヤ</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>牛タン青味噌</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>持ってきた！！</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>26673</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>19:04:33</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>26674</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>20:00:29</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ふくてゃ、T山</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>激辛祭り！</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>サルサとグリーンカレーあります</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>26675</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>20:00:51</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>イベたのしみに</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>きたよー♪</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>26676</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>20:02:02</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>26677</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>20:02:14</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>26678</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>20:10:13</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Bee</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>今週も</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>楽しみに♪</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>26679</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>20:20:35</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>−、N</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>辛いの苦手だけど</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>頑張ります！</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>26680</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>20:32:57</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>麻婆豆腐</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>持ってきたー</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>26681</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>20:33:16</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>26682</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>20:33:28</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>26683</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>20:33:41</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>26684</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>20:55:12</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>KUMA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>大宮バンビから</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>宇都宮は初です！</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>26685</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>20:58:09</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>26686</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>21:17:05</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>コテッチャン</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>来たぜ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>月曜！！</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>26687</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>21:17:33</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>26688</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>21:40:04</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>なお</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>お土産</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>あるよ♪</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>26689</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>21:46:29</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>26690</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>22:30:38</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ボンタ</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>きてみました</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>26691</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>22:31:02</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>26692</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>22:39:46</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ゆん</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>久々</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>きたよーん</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>26693</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>22:50:20</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>26694</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>22:55:44</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>でで</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>イベ楽しみに</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>26695</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>22:56:32</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>26696</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>23:23:33</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>いっちゃん</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>きましたー</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>26697</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>23:23:50</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1077,7 +1077,6 @@
           <t>日曜日</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1110,7 +1109,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1141,7 +1139,6 @@
           <t>きたよー</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1174,7 +1171,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1205,7 +1201,6 @@
           <t>これから行こうと思います</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1238,7 +1233,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1269,7 +1263,6 @@
           <t>来ました</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1302,7 +1295,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1333,7 +1325,6 @@
           <t>トークに</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1366,7 +1357,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1397,7 +1387,6 @@
           <t>はしご</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1430,7 +1419,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1461,7 +1449,6 @@
           <t>きたんご</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1494,7 +1481,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1525,7 +1511,6 @@
           <t>持ってきた！！</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1558,7 +1543,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1589,7 +1573,6 @@
           <t>サルサとグリーンカレーあります</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1620,7 +1603,6 @@
           <t>きたよー♪</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1653,7 +1635,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1686,7 +1667,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1717,7 +1697,6 @@
           <t>楽しみに♪</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1748,7 +1727,6 @@
           <t>頑張ります！</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1779,7 +1757,6 @@
           <t>持ってきたー</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1812,7 +1789,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1845,7 +1821,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1878,7 +1853,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1909,7 +1883,6 @@
           <t>宇都宮は初です！</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1942,7 +1915,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1973,7 +1945,6 @@
           <t>月曜！！</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2006,7 +1977,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2037,7 +2007,6 @@
           <t>あるよ♪</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2070,7 +2039,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2101,7 +2069,6 @@
           <t>きてみました</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2134,7 +2101,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2165,7 +2131,6 @@
           <t>きたよーん</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2198,7 +2163,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2229,7 +2193,6 @@
           <t>きたよー</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2262,7 +2225,6 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2293,7 +2255,6 @@
           <t>きましたー</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2326,7 +2287,813 @@
 スタッフ一同心よりお待ちしておりますね</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>26716</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>16:50:15</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>だいち</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>初来店</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>よろしくお願いします
+本日、伺います</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>26717</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>19:02:02</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+風も強いのでお気をつけておこしくださいませ！
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>26718</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>19:51:43</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ダイチ</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>きてます！！</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>26720</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>19:56:45</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>26721</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>21:09:24</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>nuri</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>はじめていきます</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>緊張しますが行ってみようと思います！</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>26722</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>21:23:41</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+初めての方でもお気軽にご来店いただけます！！
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>26724</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>21:33:39</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>きんたまよ</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2人でデート帰り</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ギンギンと雨でびしゃびしゃもう着きます</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>26725</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>21:35:58</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>仕事終わりに</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>きました！！</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>26726</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>21:36:28</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>26727</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>21:36:39</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>26728</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>21:51:29</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>マロ</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>久しぶりに</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>エルちゃんに会いに！</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>26729</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>22:41:17</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>のり、あや</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ふたりで</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>きたよー！！</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>26730</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>22:43:44</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ひろとも、ゆうき</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>気になってきちゃいました♪</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>26731</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>22:44:01</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>26732</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>22:44:17</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>26733</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>22:44:28</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>26734</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>00:43:48</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>テクノとポチ</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ふたりで</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>きまちた♪</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>26735</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>00:44:18</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>26736</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>01:16:21</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>少し休んでから</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>きた！</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>26737</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>01:20:38</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>26738</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>03:46:49</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>JPTR</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>はじめてきました！</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>26739</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>03:55:48</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>26741</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>04:29:59</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの水曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>本日8月11日の営業時間は♪
+オープン14:00！ラスト5:00なのよ☆
+担当は
+ツッコミはお任せのShizu
+えちえち裏垢女子のモカチ
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>img20260812042959.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>26742</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>04:31:31</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>☆割引キャンペーン開催中☆</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>【団体割引キャンペーン見ました】と
+受付スタッフに言って頂ければ…
+／
+おひとり様毎に！！
+2000円割引します！！！
+＼
+お得に遊びませんか？
+仕事終わり、飲み会終わりなど
+ぜひぜひお気軽にお越しくださいませ♪
+【団体割引キャンペーン見ました】と
+受付スタッフに言って頂ければ…
+／
+おひとり様毎に！！
+2000円割引します！！！
+＼
+お得に遊びませんか？
+仕事終わり、飲み会終わりなど
+ぜひぜひお気軽にお越しくださいませ♪</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>img20260812043131.jpg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2318,7 +2318,6 @@
 本日、伺います</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2352,7 +2351,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2383,7 +2381,6 @@
           <t>きてます！！</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2416,7 +2413,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2447,7 +2443,6 @@
           <t>緊張しますが行ってみようと思います！</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2481,7 +2476,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2512,7 +2506,6 @@
           <t>ギンギンと雨でびしゃびしゃもう着きます</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2543,7 +2536,6 @@
           <t>きました！！</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2576,7 +2568,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2609,7 +2600,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2640,7 +2630,6 @@
           <t>エルちゃんに会いに！</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2671,7 +2660,6 @@
           <t>きたよー！！</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2702,7 +2690,6 @@
           <t>気になってきちゃいました♪</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2735,7 +2722,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2768,7 +2754,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2801,7 +2786,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2832,7 +2816,6 @@
           <t>きまちた♪</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2865,7 +2848,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2896,7 +2878,6 @@
           <t>きた！</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2929,7 +2910,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2960,7 +2940,6 @@
           <t>はじめてきました！</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2993,7 +2972,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3095,6 +3073,1257 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>26743</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>14:54:08</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ゆぴ</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>連休</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>楽しみます</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>26744</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>15:14:31</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>26745</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>17:37:22</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>連日</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>登場！</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>26746</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>17:39:06</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>マッスル</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>こんちわ</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>きまっする</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>26747</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>17:39:40</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>26748</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>17:39:51</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>26749</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>19:11:18</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>やえ</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>都内かえり</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>26750</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>19:12:18</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>かずき、フジ</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>二人で</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>二年ぶり</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>26751</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>19:13:57</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>26752</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>19:14:09</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>26753</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>20:39:01</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ゆうき</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ひさしぶり</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>26754</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>20:39:19</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>26755</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>21:13:40</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>よしおたん</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>韓国パブ</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>いってきた</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>26756</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>21:13:57</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>26757</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>21:37:26</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>りゅう、たく</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>26758</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>21:38:52</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>26759</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>21:52:18</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>きちゃ！</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>26760</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>21:52:35</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>よしやん、かな</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>きまんた</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>26761</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>21:52:56</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>26762</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>21:53:11</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>26763</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>23:13:38</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>マナティ</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>酔い冷ましに</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>行きます</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>26764</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>23:14:29</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>26765</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>01:39:12</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>あゆ</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>26766</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>01:46:01</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>げん、ともち</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>26767</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>01:46:28</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>26768</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>01:46:39</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>26769</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>02:07:49</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>まおし</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>ひさびさに</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>きたゆ</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>26770</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>02:08:11</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>26771</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>02:37:55</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>すー</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>きちゃ</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>26772</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>02:38:15</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>26773</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>02:55:31</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>たかやま、りりこ</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>きた！</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>26774</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>02:55:54</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>まいまいん</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>きちゃー！！！！</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>26775</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>02:56:22</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>26776</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>02:56:33</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>26777</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>03:20:48</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>キム、みれい</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>きまちた</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>26778</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>03:44:47</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>26779</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>03:49:01</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの木曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>本日8月13日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+ツッコミはお任せのShizu
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>img20260813034901.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>26780</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>03:49:54</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>☆割引キャンペーン開催中☆</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>【団体割引キャンペーン見ました】と
+受付スタッフに言って頂ければ…
+／
+おひとり様毎に！！
+2000円割引します！！！
+＼
+お得に遊びませんか？
+仕事終わり、飲み会終わりなど
+ぜひぜひお気軽にお越しくださいませ♪
+【団体割引キャンペーン見ました】と
+受付スタッフに言って頂ければ…
+／
+おひとり様毎に！！
+2000円割引します！！！
+＼
+お得に遊びませんか？
+仕事終わり、飲み会終わりなど
+ぜひぜひお気軽にお越しくださいませ♪</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>img20260813034954.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3102,7 +3102,6 @@
           <t>楽しみます</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3135,7 +3134,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3166,7 +3164,6 @@
           <t>登場！</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3197,7 +3194,6 @@
           <t>きまっする</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3230,7 +3226,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3263,7 +3258,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3294,7 +3288,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3325,7 +3318,6 @@
           <t>二年ぶり</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -3358,7 +3350,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3391,7 +3382,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3422,7 +3412,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -3455,7 +3444,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -3486,7 +3474,6 @@
           <t>いってきた</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -3519,7 +3506,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3550,7 +3536,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3583,7 +3568,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -3614,7 +3598,6 @@
           <t>きちゃ！</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3645,7 +3628,6 @@
           <t>きまんた</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3678,7 +3660,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -3711,7 +3692,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -3742,7 +3722,6 @@
           <t>行きます</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -3775,7 +3754,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -3806,7 +3784,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -3837,7 +3814,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -3870,7 +3846,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -3903,7 +3878,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -3934,7 +3908,6 @@
           <t>きたゆ</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -3967,7 +3940,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -3998,7 +3970,6 @@
           <t>きちゃ</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -4031,7 +4002,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -4062,7 +4032,6 @@
           <t>きた！</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -4093,7 +4062,6 @@
           <t>きちゃー！！！！</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -4126,7 +4094,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -4159,7 +4126,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -4190,7 +4156,6 @@
           <t>きまちた</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -4223,7 +4188,6 @@
 スタッフ一同心よりお待ちしておりますね♪</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -4324,6 +4288,1066 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>26781</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>19:10:31</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ふみ</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>26782</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>19:11:47</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>26783</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>19:16:23</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>ほぼ</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>オープン凸</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>26784</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>19:16:46</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>26785</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>19:57:51</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>のんのん</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>めずらしく</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>はやめに！</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>26786</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>20:08:06</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>きむ、りさ</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>26787</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>20:10:37</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>飲みに</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>26788</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>20:10:59</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>26789</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>20:11:23</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>26790</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>20:11:42</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>26791</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>20:24:38</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>たます</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>ひさしぶり</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>26792</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>20:24:51</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>26793</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>21:05:25</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>かける</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>26794</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>21:05:39</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>26795</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>21:27:52</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>オ・スー</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>あそびに</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>きましたよ</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>26796</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>21:28:08</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>26797</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>23:31:30</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ぽちゃりす組</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>26798</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>23:31:45</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>26799</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>01:11:19</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>おちんぽベルセルク</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>26800</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>01:11:39</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>26801</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>01:31:53</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>zin、あゆ</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>仕事終わりに</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>26802</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>01:32:22</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>26803</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>01:34:21</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>みれい</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>昨日ぶり</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>26804</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>01:34:41</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>26805</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>02:06:00</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ごん、ぶりちゃん</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>二人で</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>26806</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>02:06:19</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>26807</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>02:20:44</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>まい</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>シゴオワ</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>きた</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>26808</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>02:21:07</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>TKC</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>飲みに</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>きた！</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>26809</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>02:21:24</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>おぉぉぉぉぉぉぉぉぉ♪</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>26810</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>02:21:34</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>お待ちしておりまぁす♪</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>来店予告ありがとうございます♪
+ぜひぜひお越し下さい☆
+スタッフ一同心よりお待ちしておりますね♪</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>26811</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>04:24:18</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの週末営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>本日8月14日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+ツッコミはお任せのShizu
+新妻マゾヒストのミコト
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>img20260814042418.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>26812</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>04:26:24</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>☆割引キャンペーン開催中☆</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>【団体割引キャンペーン見ました】と
+受付スタッフに言って頂ければ…
+／
+おひとり様毎に！！
+2000円割引します！！！
+＼
+お得に遊びませんか？
+仕事終わり、飲み会終わりなど
+ぜひぜひお気軽にお越しくださいませ♪
+【団体割引キャンペーン見ました】と
+受付スタッフに言って頂ければ…
+／
+おひとり様毎に！！
+2000円割引します！！！
+＼
+お得に遊びませんか？
+仕事終わり、飲み会終わりなど
+ぜひぜひお気軽にお越しくださいませ♪</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>img20260814042624.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,15 +439,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>出勤者</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>題名</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>画像ファイル</t>
         </is>
@@ -472,12 +477,13 @@
           <t>いぬ、マッチョ、ももたろ</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>ムキムキ三人衆で</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>来ましたー！</t>
         </is>
@@ -502,12 +508,13 @@
           <t>ゆうたん、カモリ</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>カップルで</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>気になって来てみました♪</t>
         </is>
@@ -532,12 +539,13 @@
           <t>アキ、コオリ</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>はじめてさん連れて</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>来ましたー</t>
         </is>
@@ -562,12 +570,13 @@
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>ちょいのみ</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>きたよん</t>
         </is>
@@ -592,12 +601,13 @@
           <t>てつ</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
         <is>
           <t>田中</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>きたぞ</t>
         </is>
@@ -622,12 +632,13 @@
           <t>H,M,D</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
         <is>
           <t>みんなで</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>はじめてです！</t>
         </is>
@@ -652,12 +663,13 @@
           <t>ともゆき</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
         <is>
           <t>はじめて</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>あそびきてみました！</t>
         </is>
@@ -682,12 +694,13 @@
           <t>まいまい</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
         <is>
           <t>しごわ</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>べろべろんちょ</t>
         </is>
@@ -714,10 +727,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>欲求不満のポコチンハンター　える</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>★☆★朝までアゲアゲの火曜日営業が始まるわよ♪★☆★</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>本日8月11日の営業時間は♪
 オープン19:00！ラスト5:00なのよ☆
@@ -734,7 +752,7 @@
 宇都宮市宿郷1−12−9　カサブランカビル5F</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>img20260811042347.jpg</t>
         </is>
@@ -742,59 +760,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>26715</v>
+        <v>26656</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>04:25:06</t>
+          <t>22:30:42</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>★BAMBITCH★</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>☆割引キャンペーン開催中☆ ★BAMBITCH★</t>
-        </is>
-      </c>
+          <t>はなまる</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>【団体割引キャンペーン見ました】と
-受付スタッフに言って頂ければ…
-／
-おひとり様毎に！！
-2000円割引します！！！
-＼
-お得に遊びませんか？
-仕事終わり、飲み会終わりなど
-ぜひぜひお気軽にお越しくださいませ♪
-【団体割引キャンペーン見ました】と
-受付スタッフに言って頂ければ…
-／
-おひとり様毎に！！
-2000円割引します！！！
-＼
-お得に遊びませんか？
-仕事終わり、飲み会終わりなど
-ぜひぜひお気軽にお越しくださいませ♪</t>
+          <t>久しぶりの</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>img20260811042506.jpg</t>
+          <t>日曜日</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>26656</v>
+        <v>26658</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -803,28 +800,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>22:30:42</t>
+          <t>22:33:32</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>はなまる</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>久しぶりの</t>
-        </is>
-      </c>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>日曜日</t>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>きたよー</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>26658</v>
+        <v>26660</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -833,28 +831,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>22:33:32</t>
+          <t>22:46:52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>大塚</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>今</t>
-        </is>
-      </c>
+          <t>ゆうと</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>きたよー</t>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>これから行こうと思います</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>26660</v>
+        <v>26662</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -863,28 +862,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22:46:52</t>
+          <t>23:11:17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ゆうと</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>初めて</t>
-        </is>
-      </c>
+          <t>カー</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>これから行こうと思います</t>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>来ました</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>26662</v>
+        <v>26664</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -893,58 +893,60 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>23:11:17</t>
+          <t>23:45:37</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>カー</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>今</t>
-        </is>
-      </c>
+          <t>ミコト、まいまい、テクノ</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>来ました</t>
+          <t>ちいかわ</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>トークに</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>26664</v>
+        <v>26666</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>23:45:37</t>
+          <t>00:14:17</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ミコト、まいまい、テクノ</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ちいかわ</t>
-        </is>
-      </c>
+          <t>りょうちゃん</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>トークに</t>
+          <t>バンビ</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>はしご</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>26666</v>
+        <v>26668</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -953,28 +955,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>00:14:17</t>
+          <t>01:18:22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>バンビ</t>
-        </is>
-      </c>
+          <t>らうら</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>はしご</t>
+          <t>少し</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>きたんご</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>26668</v>
+        <v>26672</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -983,28 +986,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01:18:22</t>
+          <t>19:02:51</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>らうら</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>少し</t>
-        </is>
-      </c>
+          <t>タツヤ</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>きたんご</t>
+          <t>牛タン青味噌</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>持ってきた！！</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>26672</v>
+        <v>26674</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1013,28 +1017,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19:02:51</t>
+          <t>20:00:29</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>タツヤ</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>牛タン青味噌</t>
-        </is>
-      </c>
+          <t>ふくてゃ、T山</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>持ってきた！！</t>
+          <t>激辛祭り！</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>サルサとグリーンカレーあります</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>26674</v>
+        <v>26675</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1043,28 +1048,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20:00:29</t>
+          <t>20:00:51</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ふくてゃ、T山</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>激辛祭り！</t>
-        </is>
-      </c>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>サルサとグリーンカレーあります</t>
+          <t>イベたのしみに</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>きたよー♪</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>26675</v>
+        <v>26678</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1073,28 +1079,29 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>20:00:51</t>
+          <t>20:10:13</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ひがん</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>イベたのしみに</t>
-        </is>
-      </c>
+          <t>Bee</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>きたよー♪</t>
+          <t>今週も</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>楽しみに♪</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>26678</v>
+        <v>26679</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1103,28 +1110,29 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20:10:13</t>
+          <t>20:20:35</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bee</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>今週も</t>
-        </is>
-      </c>
+          <t>−、N</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>楽しみに♪</t>
+          <t>辛いの苦手だけど</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>26679</v>
+        <v>26680</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1133,28 +1141,29 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>20:20:35</t>
+          <t>20:32:57</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>−、N</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>辛いの苦手だけど</t>
-        </is>
-      </c>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>頑張ります！</t>
+          <t>麻婆豆腐</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>持ってきたー</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>26680</v>
+        <v>26684</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1163,28 +1172,29 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20:32:57</t>
+          <t>20:55:12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>テクノ</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>麻婆豆腐</t>
-        </is>
-      </c>
+          <t>KUMA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>持ってきたー</t>
+          <t>大宮バンビから</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>宇都宮は初です！</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>26684</v>
+        <v>26686</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1193,28 +1203,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20:55:12</t>
+          <t>21:17:05</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KUMA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>大宮バンビから</t>
-        </is>
-      </c>
+          <t>コテッチャン</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>宇都宮は初です！</t>
+          <t>来たぜ</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>月曜！！</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26686</v>
+        <v>26688</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1223,28 +1234,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>21:17:05</t>
+          <t>21:40:04</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>来たぜ</t>
-        </is>
-      </c>
+          <t>なお</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>月曜！！</t>
+          <t>お土産</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>あるよ♪</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26688</v>
+        <v>26690</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1253,28 +1265,29 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>21:40:04</t>
+          <t>22:30:38</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>なお</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>お土産</t>
-        </is>
-      </c>
+          <t>ボンタ</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>あるよ♪</t>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>きてみました</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>26690</v>
+        <v>26692</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1283,28 +1296,29 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>22:30:38</t>
+          <t>22:39:46</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ボンタ</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>初めて</t>
-        </is>
-      </c>
+          <t>ゆん</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>きてみました</t>
+          <t>久々</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>きたよーん</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>26692</v>
+        <v>26694</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1313,28 +1327,29 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>22:39:46</t>
+          <t>22:55:44</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ゆん</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>久々</t>
-        </is>
-      </c>
+          <t>でで</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>きたよーん</t>
+          <t>イベ楽しみに</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>きたよー</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>26694</v>
+        <v>26696</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1343,58 +1358,61 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>22:55:44</t>
+          <t>23:23:33</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>でで</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>イベ楽しみに</t>
-        </is>
-      </c>
+          <t>いっちゃん</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>きたよー</t>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>きましたー</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>26696</v>
+        <v>26716</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>23:23:33</t>
+          <t>16:50:15</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>遊びに</t>
-        </is>
-      </c>
+          <t>だいち</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>きましたー</t>
+          <t>初来店</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>よろしくお願いします
+本日、伺います</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>26716</v>
+        <v>26718</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1403,29 +1421,29 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16:50:15</t>
+          <t>19:51:43</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>だいち</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>初来店</t>
-        </is>
-      </c>
+          <t>ダイチ</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>よろしくお願いします
-本日、伺います</t>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>きてます！！</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>26718</v>
+        <v>26721</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1434,28 +1452,29 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19:51:43</t>
+          <t>21:09:24</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ダイチ</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>はじめて</t>
-        </is>
-      </c>
+          <t>nuri</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>きてます！！</t>
+          <t>はじめていきます</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>緊張しますが行ってみようと思います！</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>26721</v>
+        <v>26724</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1464,28 +1483,29 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>21:09:24</t>
+          <t>21:33:39</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>nuri</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>はじめていきます</t>
-        </is>
-      </c>
+          <t>きんたまよ</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>緊張しますが行ってみようと思います！</t>
+          <t>2人でデート帰り</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ギンギンと雨でびしゃびしゃもう着きます</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>26724</v>
+        <v>26725</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1494,28 +1514,29 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>21:33:39</t>
+          <t>21:35:58</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2人でデート帰り</t>
-        </is>
-      </c>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ギンギンと雨でびしゃびしゃもう着きます</t>
+          <t>仕事終わりに</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>きました！！</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>26725</v>
+        <v>26728</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1524,28 +1545,29 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>21:35:58</t>
+          <t>21:51:29</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ゆずき</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>仕事終わりに</t>
-        </is>
-      </c>
+          <t>マロ</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>きました！！</t>
+          <t>久しぶりに</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>エルちゃんに会いに！</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>26728</v>
+        <v>26729</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1554,28 +1576,29 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>21:51:29</t>
+          <t>22:41:17</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>マロ</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>久しぶりに</t>
-        </is>
-      </c>
+          <t>のり、あや</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>エルちゃんに会いに！</t>
+          <t>ふたりで</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>きたよー！！</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>26729</v>
+        <v>26730</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1584,58 +1607,60 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>22:41:17</t>
+          <t>22:43:44</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>のり、あや</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>ふたりで</t>
-        </is>
-      </c>
+          <t>ひろとも、ゆうき</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>きたよー！！</t>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>気になってきちゃいました♪</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>26730</v>
+        <v>26734</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>22:43:44</t>
+          <t>00:43:48</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ひろとも、ゆうき</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>はじめて</t>
-        </is>
-      </c>
+          <t>テクノとポチ</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>気になってきちゃいました♪</t>
+          <t>ふたりで</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>きまちた♪</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>26734</v>
+        <v>26736</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1644,28 +1669,29 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>00:43:48</t>
+          <t>01:16:21</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>ふたりで</t>
-        </is>
-      </c>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>きまちた♪</t>
+          <t>少し休んでから</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>きた！</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>26736</v>
+        <v>26738</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1674,28 +1700,29 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01:16:21</t>
+          <t>03:46:49</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>まいまい</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>少し休んでから</t>
-        </is>
-      </c>
+          <t>JPTR</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>きた！</t>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>はじめてきました！</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>26738</v>
+        <v>26741</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1704,50 +1731,25 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>03:46:49</t>
+          <t>04:29:59</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>★BAMBITCH★</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>みんなで</t>
+          <t>ツッコミはお任せのShizu / えちえち裏垢女子のモカチ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>はじめてきました！</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>26741</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>04:29:59</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>★BAMBITCH★</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
           <t>★☆★朝までアゲアゲの水曜日営業が始まるわよ♪★☆★</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>本日8月11日の営業時間は♪
 オープン14:00！ラスト5:00なのよ☆
@@ -1765,15 +1767,46 @@
 宇都宮市宿郷1−12−9　カサブランカビル5F</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>img20260812042959.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>26743</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>14:54:08</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ゆぴ</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>連休</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>img20260812042959.jpg</t>
+          <t>楽しみます</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>26742</v>
+        <v>26745</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1782,50 +1815,29 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>04:31:31</t>
+          <t>17:37:22</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>★BAMBITCH★</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>☆割引キャンペーン開催中☆</t>
-        </is>
-      </c>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>【団体割引キャンペーン見ました】と
-受付スタッフに言って頂ければ…
-／
-おひとり様毎に！！
-2000円割引します！！！
-＼
-お得に遊びませんか？
-仕事終わり、飲み会終わりなど
-ぜひぜひお気軽にお越しくださいませ♪
-【団体割引キャンペーン見ました】と
-受付スタッフに言って頂ければ…
-／
-おひとり様毎に！！
-2000円割引します！！！
-＼
-お得に遊びませんか？
-仕事終わり、飲み会終わりなど
-ぜひぜひお気軽にお越しくださいませ♪</t>
+          <t>連日</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>img20260812043131.jpg</t>
+          <t>登場！</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>26743</v>
+        <v>26746</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1834,28 +1846,29 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>14:54:08</t>
+          <t>17:39:06</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>連休</t>
-        </is>
-      </c>
+          <t>マッスル</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>楽しみます</t>
+          <t>こんちわ</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>きまっする</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>26745</v>
+        <v>26749</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1864,28 +1877,29 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>17:37:22</t>
+          <t>19:11:18</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ゆずき</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>連日</t>
-        </is>
-      </c>
+          <t>やえ</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>登場！</t>
+          <t>都内かえり</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>きました</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>26746</v>
+        <v>26750</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1894,28 +1908,29 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>17:39:06</t>
+          <t>19:12:18</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>マッスル</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>こんちわ</t>
-        </is>
-      </c>
+          <t>かずき、フジ</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>きまっする</t>
+          <t>二人で</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>二年ぶり</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>26749</v>
+        <v>26753</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1924,28 +1939,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>19:11:18</t>
+          <t>20:39:01</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>やえ</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>都内かえり</t>
-        </is>
-      </c>
+          <t>ゆうき</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>きました</t>
+          <t>ひさしぶり</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>きました！</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>26750</v>
+        <v>26755</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1954,28 +1970,29 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>19:12:18</t>
+          <t>21:13:40</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>かずき、フジ</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>二人で</t>
-        </is>
-      </c>
+          <t>よしおたん</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>二年ぶり</t>
+          <t>韓国パブ</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>いってきた</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>26753</v>
+        <v>26757</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1984,28 +2001,29 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>20:39:01</t>
+          <t>21:37:26</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ゆうき</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>ひさしぶり</t>
-        </is>
-      </c>
+          <t>りゅう、たく</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>きました！</t>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>きました</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>26755</v>
+        <v>26759</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2014,28 +2032,29 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>21:13:40</t>
+          <t>21:52:18</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>よしおたん</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>韓国パブ</t>
-        </is>
-      </c>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>いってきた</t>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>きちゃ！</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>26757</v>
+        <v>26760</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2044,28 +2063,29 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>21:37:26</t>
+          <t>21:52:35</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>りゅう、たく</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
+          <t>よしやん、かな</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>きました</t>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>きまんた</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>26759</v>
+        <v>26763</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2074,88 +2094,91 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>21:52:18</t>
+          <t>23:13:38</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>今</t>
-        </is>
-      </c>
+          <t>マナティ</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>きちゃ！</t>
+          <t>酔い冷ましに</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>行きます</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>26760</v>
+        <v>26765</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>21:52:35</t>
+          <t>01:39:12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>よしやん、かな</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
+          <t>あゆ</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>きまんた</t>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>きました</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>26763</v>
+        <v>26766</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>23:13:38</t>
+          <t>01:46:01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>マナティ</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>酔い冷ましに</t>
-        </is>
-      </c>
+          <t>げん、ともち</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>行きます</t>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>きました</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>26765</v>
+        <v>26769</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2164,28 +2187,29 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01:39:12</t>
+          <t>02:07:49</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>あゆ</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>今</t>
-        </is>
-      </c>
+          <t>まおし</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>きました</t>
+          <t>ひさびさに</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>きたゆ</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>26766</v>
+        <v>26771</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2194,28 +2218,29 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>01:46:01</t>
+          <t>02:37:55</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>げん、ともち</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
+          <t>すー</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>きました</t>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>きちゃ</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>26769</v>
+        <v>26773</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2224,28 +2249,29 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>02:07:49</t>
+          <t>02:55:31</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>まおし</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>ひさびさに</t>
-        </is>
-      </c>
+          <t>たかやま、りりこ</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>きたゆ</t>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>きた！</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>26771</v>
+        <v>26774</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2254,28 +2280,29 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>02:37:55</t>
+          <t>02:55:54</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>すー</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
+          <t>まいまいん</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>きちゃ</t>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>きちゃー！！！！</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>26773</v>
+        <v>26777</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2284,28 +2311,29 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>02:55:31</t>
+          <t>03:20:48</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>たかやま、りりこ</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>今</t>
-        </is>
-      </c>
+          <t>キム、みれい</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>きた！</t>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>きまちた</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>26774</v>
+        <v>26779</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2314,80 +2342,25 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>02:55:54</t>
+          <t>03:49:01</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>★BAMBITCH★</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>今</t>
+          <t>ツッコミはお任せのShizu</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>きちゃー！！！！</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>26777</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>03:20:48</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>キム、みれい</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>さっき</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>きまちた</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>26779</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>03:49:01</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>★BAMBITCH★</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
           <t>★☆★朝までアゲアゲの木曜日営業が始まるわよ♪★☆★</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>本日8月13日の営業時間は♪
 オープン19:00！ラスト5:00なのよ☆
@@ -2404,15 +2377,77 @@
 宇都宮市宿郷1−12−9　カサブランカビル5F</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>img20260813034901.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>26781</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>19:10:31</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ふみ</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>26783</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>19:16:23</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>ほぼ</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>img20260813034901.jpg</t>
+          <t>オープン凸</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>26780</v>
+        <v>26785</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2421,50 +2456,29 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>03:49:54</t>
+          <t>19:57:51</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>★BAMBITCH★</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>☆割引キャンペーン開催中☆</t>
-        </is>
-      </c>
+          <t>のんのん</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>【団体割引キャンペーン見ました】と
-受付スタッフに言って頂ければ…
-／
-おひとり様毎に！！
-2000円割引します！！！
-＼
-お得に遊びませんか？
-仕事終わり、飲み会終わりなど
-ぜひぜひお気軽にお越しくださいませ♪
-【団体割引キャンペーン見ました】と
-受付スタッフに言って頂ければ…
-／
-おひとり様毎に！！
-2000円割引します！！！
-＼
-お得に遊びませんか？
-仕事終わり、飲み会終わりなど
-ぜひぜひお気軽にお越しくださいませ♪</t>
+          <t>めずらしく</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>img20260813034954.jpg</t>
+          <t>はやめに！</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>26781</v>
+        <v>26786</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2473,28 +2487,29 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>19:10:31</t>
+          <t>20:08:06</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ふみ</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>はじめて</t>
-        </is>
-      </c>
+          <t>きむ、りさ</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>きました♪</t>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>きました</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>26783</v>
+        <v>26787</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2503,28 +2518,29 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>19:16:23</t>
+          <t>20:10:37</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ひがん</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>ほぼ</t>
-        </is>
-      </c>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>オープン凸</t>
+          <t>飲みに</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>きました！</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>26785</v>
+        <v>26791</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2533,28 +2549,29 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>19:57:51</t>
+          <t>20:24:38</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>のんのん</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>めずらしく</t>
-        </is>
-      </c>
+          <t>たます</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>はやめに！</t>
+          <t>ひさしぶり</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>きました！</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>26786</v>
+        <v>26793</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2563,28 +2580,29 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>20:08:06</t>
+          <t>21:05:25</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>きむ、りさ</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>今日も</t>
-        </is>
-      </c>
+          <t>かける</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>きました</t>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>きました！</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>26787</v>
+        <v>26795</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2593,28 +2611,29 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>20:10:37</t>
+          <t>21:27:52</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>りん</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>飲みに</t>
-        </is>
-      </c>
+          <t>オ・スー</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>きました！</t>
+          <t>あそびに</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>きましたよ</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>26791</v>
+        <v>26797</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2623,20 +2642,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>20:24:38</t>
+          <t>23:31:30</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>たます</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>ひさしぶり</t>
-        </is>
-      </c>
+          <t>ぽちゃりす組</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -2644,97 +2664,100 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>26793</v>
+        <v>26799</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>21:05:25</t>
+          <t>01:11:19</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>かける</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>はじめて</t>
-        </is>
-      </c>
+          <t>おちんぽベルセルク</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>きました！</t>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>きました♪</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>26795</v>
+        <v>26801</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>21:27:52</t>
+          <t>01:31:53</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>オ・スー</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>あそびに</t>
-        </is>
-      </c>
+          <t>zin、あゆ</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>きましたよ</t>
+          <t>仕事終わりに</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>きました</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>26797</v>
+        <v>26803</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>23:31:30</t>
+          <t>01:34:21</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ぽちゃりす組</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>いま</t>
-        </is>
-      </c>
+          <t>みれい</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>きました！</t>
+          <t>昨日ぶり</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>きました</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>26799</v>
+        <v>26805</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2743,28 +2766,29 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>01:11:19</t>
+          <t>02:06:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>すこし</t>
-        </is>
-      </c>
+          <t>ごん、ぶりちゃん</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>きました♪</t>
+          <t>二人で</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>きました！</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>26801</v>
+        <v>26807</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2773,28 +2797,29 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>01:31:53</t>
+          <t>02:20:44</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>zin、あゆ</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>仕事終わりに</t>
-        </is>
-      </c>
+          <t>まい</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>きました</t>
+          <t>シゴオワ</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>きた</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>26803</v>
+        <v>26808</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2803,28 +2828,29 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>01:34:21</t>
+          <t>02:21:07</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>みれい</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>昨日ぶり</t>
-        </is>
-      </c>
+          <t>TKC</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>きました</t>
+          <t>飲みに</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>きた！</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>26805</v>
+        <v>26811</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -2833,110 +2859,25 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>02:06:00</t>
+          <t>04:24:18</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ごん、ぶりちゃん</t>
+          <t>★BAMBITCH★</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>二人で</t>
+          <t>ツッコミはお任せのShizu / 新妻マゾヒストのミコト</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>きました！</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>26807</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>02:20:44</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>まい</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>シゴオワ</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>きた</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>26808</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>02:21:07</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>TKC</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>飲みに</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>きた！</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>26811</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>04:24:18</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>★BAMBITCH★</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
           <t>★☆★朝までアゲアゲの週末営業が始まるわよ♪★☆★</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>本日8月14日の営業時間は♪
 オープン19:00！ラスト5:00なのよ☆
@@ -2954,61 +2895,9 @@
 宇都宮市宿郷1−12−9　カサブランカビル5F</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>img20260814042418.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>26812</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>04:26:24</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>★BAMBITCH★</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>☆割引キャンペーン開催中☆</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>【団体割引キャンペーン見ました】と
-受付スタッフに言って頂ければ…
-／
-おひとり様毎に！！
-2000円割引します！！！
-＼
-お得に遊びませんか？
-仕事終わり、飲み会終わりなど
-ぜひぜひお気軽にお越しくださいませ♪
-【団体割引キャンペーン見ました】と
-受付スタッフに言って頂ければ…
-／
-おひとり様毎に！！
-2000円割引します！！！
-＼
-お得に遊びませんか？
-仕事終わり、飲み会終わりなど
-ぜひぜひお気軽にお越しくださいませ♪</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>img20260814042624.jpg</t>
         </is>
       </c>
     </row>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,6 @@
           <t>いぬ、マッチョ、ももたろ</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>ムキムキ三人衆で</t>
@@ -508,7 +507,6 @@
           <t>ゆうたん、カモリ</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>カップルで</t>
@@ -539,7 +537,6 @@
           <t>アキ、コオリ</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>はじめてさん連れて</t>
@@ -570,7 +567,6 @@
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>ちょいのみ</t>
@@ -601,7 +597,6 @@
           <t>てつ</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>田中</t>
@@ -632,7 +627,6 @@
           <t>H,M,D</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>みんなで</t>
@@ -663,7 +657,6 @@
           <t>ともゆき</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -694,7 +687,6 @@
           <t>まいまい</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>しごわ</t>
@@ -777,7 +769,6 @@
           <t>はなまる</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>久しぶりの</t>
@@ -808,7 +799,6 @@
           <t>大塚</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>今</t>
@@ -839,7 +829,6 @@
           <t>ゆうと</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>初めて</t>
@@ -870,7 +859,6 @@
           <t>カー</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>今</t>
@@ -901,7 +889,6 @@
           <t>ミコト、まいまい、テクノ</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>ちいかわ</t>
@@ -932,7 +919,6 @@
           <t>りょうちゃん</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>バンビ</t>
@@ -963,7 +949,6 @@
           <t>らうら</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>少し</t>
@@ -994,7 +979,6 @@
           <t>タツヤ</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>牛タン青味噌</t>
@@ -1025,7 +1009,6 @@
           <t>ふくてゃ、T山</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>激辛祭り！</t>
@@ -1056,7 +1039,6 @@
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>イベたのしみに</t>
@@ -1087,7 +1069,6 @@
           <t>Bee</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>今週も</t>
@@ -1118,7 +1099,6 @@
           <t>−、N</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>辛いの苦手だけど</t>
@@ -1149,7 +1129,6 @@
           <t>テクノ</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>麻婆豆腐</t>
@@ -1180,7 +1159,6 @@
           <t>KUMA</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>大宮バンビから</t>
@@ -1211,7 +1189,6 @@
           <t>コテッチャン</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>来たぜ</t>
@@ -1242,7 +1219,6 @@
           <t>なお</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>お土産</t>
@@ -1273,7 +1249,6 @@
           <t>ボンタ</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>初めて</t>
@@ -1304,7 +1279,6 @@
           <t>ゆん</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>久々</t>
@@ -1335,7 +1309,6 @@
           <t>でで</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>イベ楽しみに</t>
@@ -1366,7 +1339,6 @@
           <t>いっちゃん</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>遊びに</t>
@@ -1397,7 +1369,6 @@
           <t>だいち</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>初来店</t>
@@ -1429,7 +1400,6 @@
           <t>ダイチ</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -1460,7 +1430,6 @@
           <t>nuri</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>はじめていきます</t>
@@ -1491,7 +1460,6 @@
           <t>きんたまよ</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>2人でデート帰り</t>
@@ -1522,7 +1490,6 @@
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>仕事終わりに</t>
@@ -1553,7 +1520,6 @@
           <t>マロ</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>久しぶりに</t>
@@ -1584,7 +1550,6 @@
           <t>のり、あや</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>ふたりで</t>
@@ -1615,7 +1580,6 @@
           <t>ひろとも、ゆうき</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -1646,7 +1610,6 @@
           <t>テクノとポチ</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>ふたりで</t>
@@ -1677,7 +1640,6 @@
           <t>まいまい</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>少し休んでから</t>
@@ -1708,7 +1670,6 @@
           <t>JPTR</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>みんなで</t>
@@ -1792,7 +1753,6 @@
           <t>ゆぴ</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>連休</t>
@@ -1823,7 +1783,6 @@
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>連日</t>
@@ -1854,7 +1813,6 @@
           <t>マッスル</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>こんちわ</t>
@@ -1885,7 +1843,6 @@
           <t>やえ</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>都内かえり</t>
@@ -1916,7 +1873,6 @@
           <t>かずき、フジ</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>二人で</t>
@@ -1947,7 +1903,6 @@
           <t>ゆうき</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>ひさしぶり</t>
@@ -1978,7 +1933,6 @@
           <t>よしおたん</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>韓国パブ</t>
@@ -2009,7 +1963,6 @@
           <t>りゅう、たく</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>今</t>
@@ -2040,7 +1993,6 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>今</t>
@@ -2071,7 +2023,6 @@
           <t>よしやん、かな</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>今</t>
@@ -2102,7 +2053,6 @@
           <t>マナティ</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>酔い冷ましに</t>
@@ -2133,7 +2083,6 @@
           <t>あゆ</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>今</t>
@@ -2164,7 +2113,6 @@
           <t>げん、ともち</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>今</t>
@@ -2195,7 +2143,6 @@
           <t>まおし</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>ひさびさに</t>
@@ -2226,7 +2173,6 @@
           <t>すー</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>今</t>
@@ -2257,7 +2203,6 @@
           <t>たかやま、りりこ</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>今</t>
@@ -2288,7 +2233,6 @@
           <t>まいまいん</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>今</t>
@@ -2319,7 +2263,6 @@
           <t>キム、みれい</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>さっき</t>
@@ -2402,7 +2345,6 @@
           <t>ふみ</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -2433,7 +2375,6 @@
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>ほぼ</t>
@@ -2464,7 +2405,6 @@
           <t>のんのん</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>めずらしく</t>
@@ -2495,7 +2435,6 @@
           <t>きむ、りさ</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>今日も</t>
@@ -2526,7 +2465,6 @@
           <t>りん</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>飲みに</t>
@@ -2557,7 +2495,6 @@
           <t>たます</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>ひさしぶり</t>
@@ -2588,7 +2525,6 @@
           <t>かける</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -2619,7 +2555,6 @@
           <t>オ・スー</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>あそびに</t>
@@ -2650,7 +2585,6 @@
           <t>ぽちゃりす組</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>いま</t>
@@ -2681,7 +2615,6 @@
           <t>おちんぽベルセルク</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>すこし</t>
@@ -2712,7 +2645,6 @@
           <t>zin、あゆ</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>仕事終わりに</t>
@@ -2743,7 +2675,6 @@
           <t>みれい</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>昨日ぶり</t>
@@ -2774,7 +2705,6 @@
           <t>ごん、ぶりちゃん</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>二人で</t>
@@ -2805,7 +2735,6 @@
           <t>まい</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>シゴオワ</t>
@@ -2836,7 +2765,6 @@
           <t>TKC</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>飲みに</t>
@@ -2901,6 +2829,827 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>26813</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>19:06:50</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>おとは</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>金曜</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>きたよーん♪</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>26814</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>19:07:26</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>よっち</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>今日はオープンから</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>26817</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>19:24:35</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>りょう</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>これから</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>これから寄ってみます！</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>26818</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>19:32:01</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>まいまい、ゆずき</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>飲みおわ</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>きました！！</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>26819</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>19:40:45</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>マッスル</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>きまんた！</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>26820</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>19:43:56</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ねここ</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>26821</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>19:51:19</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ゆず、ちぇちぇ</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>はじめて二人で</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>きました！！</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>26822</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>20:15:26</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>たいせー</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>緊張しますが、本日お伺いします</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>26823</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>20:18:29</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>bee</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ぶんぶん</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>蜂さん！</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>26824</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>20:18:55</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>カズ</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>早めに来ました</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>26833</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>21:45:29</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>たいせい</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>来ました！！</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>26834</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>21:48:50</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>かい</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>前橋から</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>来ました！！</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>26837</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>21:58:15</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>るい</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>26838</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>22:05:09</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>タツヤ</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>戦って</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>きましたー</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>26839</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>22:06:17</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ででたゃ</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>きたよん！</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>26843</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>22:48:24</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>あにー、りえ、ゆり</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>しごおわ</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>行くマス</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>26845</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>22:55:59</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>みなっち</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>26849</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>23:22:10</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>しゅん</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>いきます</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>久しぶりに</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>26851</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>00:11:14</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>きむら</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>今から</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>おじやましますー</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>26853</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>00:13:48</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>26855</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>00:44:59</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ましゅ、絶</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>26857</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>01:35:32</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>りお、めい、まい</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>しごおわ</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>26859</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>02:19:37</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>だいご</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>よばれて</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>きちゃよ</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>26861</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>02:59:37</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ザッキー、よっしー</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>26863</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>03:58:08</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ツッコミはお任せのShizu / えちえち裏垢女子のモカチ</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの週末営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>本日8月15日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+ツッコミはお任せのShizu
+えちえち裏垢女子のモカチ
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>img20260815035808.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2848,7 +2848,6 @@
           <t>おとは</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>金曜</t>
@@ -2859,7 +2858,6 @@
           <t>きたよーん♪</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2880,7 +2878,6 @@
           <t>よっち</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>今日はオープンから</t>
@@ -2891,7 +2888,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2912,7 +2908,6 @@
           <t>りょう</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>これから</t>
@@ -2923,7 +2918,6 @@
           <t>これから寄ってみます！</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2944,7 +2938,6 @@
           <t>まいまい、ゆずき</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>飲みおわ</t>
@@ -2955,7 +2948,6 @@
           <t>きました！！</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2976,7 +2968,6 @@
           <t>マッスル</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>今日も</t>
@@ -2987,7 +2978,6 @@
           <t>きまんた！</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3008,7 +2998,6 @@
           <t>ねここ</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -3019,7 +3008,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3040,7 +3028,6 @@
           <t>ゆず、ちぇちぇ</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>はじめて二人で</t>
@@ -3051,7 +3038,6 @@
           <t>きました！！</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3072,7 +3058,6 @@
           <t>たいせー</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>初めて</t>
@@ -3083,7 +3068,6 @@
           <t>緊張しますが、本日お伺いします</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3104,7 +3088,6 @@
           <t>bee</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>ぶんぶん</t>
@@ -3115,7 +3098,6 @@
           <t>蜂さん！</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3136,7 +3118,6 @@
           <t>カズ</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>今日は</t>
@@ -3147,7 +3128,6 @@
           <t>早めに来ました</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3168,7 +3148,6 @@
           <t>たいせい</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>初めて</t>
@@ -3179,7 +3158,6 @@
           <t>来ました！！</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3200,7 +3178,6 @@
           <t>かい</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>前橋から</t>
@@ -3211,7 +3188,6 @@
           <t>来ました！！</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3232,7 +3208,6 @@
           <t>るい</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>遊びに</t>
@@ -3243,7 +3218,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3264,7 +3238,6 @@
           <t>タツヤ</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>戦って</t>
@@ -3275,7 +3248,6 @@
           <t>きましたー</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -3296,7 +3268,6 @@
           <t>ででたゃ</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>遊びに</t>
@@ -3307,7 +3278,6 @@
           <t>きたよん！</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3328,7 +3298,6 @@
           <t>あにー、りえ、ゆり</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>しごおわ</t>
@@ -3339,7 +3308,6 @@
           <t>行くマス</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3360,7 +3328,6 @@
           <t>みなっち</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>遊びに</t>
@@ -3371,7 +3338,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -3392,7 +3358,6 @@
           <t>しゅん</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>いきます</t>
@@ -3403,7 +3368,6 @@
           <t>久しぶりに</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -3424,7 +3388,6 @@
           <t>きむら</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>今から</t>
@@ -3435,7 +3398,6 @@
           <t>おじやましますー</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -3456,7 +3418,6 @@
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>いま</t>
@@ -3467,7 +3428,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3488,7 +3448,6 @@
           <t>ましゅ、絶</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>遊びに</t>
@@ -3499,7 +3458,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3520,7 +3478,6 @@
           <t>りお、めい、まい</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>しごおわ</t>
@@ -3531,7 +3488,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -3552,7 +3508,6 @@
           <t>だいご</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>よばれて</t>
@@ -3563,7 +3518,6 @@
           <t>きちゃよ</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3584,7 +3538,6 @@
           <t>ザッキー、よっしー</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>初めて</t>
@@ -3595,7 +3548,6 @@
           <t>きました♪</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3650,6 +3602,826 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>26865</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>18:51:45</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>おじきち</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>きたよ！</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>26867</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>18:57:32</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>まろ、おとは</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>はやめに</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>きたよ</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>26869</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>19:28:11</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>たつや</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>きたｚ</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>26870</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>19:28:38</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>S、Y</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>２回目</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>26871</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>19:28:53</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>よっち</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>26875</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>19:49:47</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>きょうも</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>いるよ</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>26876</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>19:50:08</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>まっする</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>きたんご</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>26879</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>20:30:43</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>26881</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>20:46:17</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>まいなちゅ、えぬ</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>きちゃ</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>26882</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>20:46:44</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>こてっちゃん</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>ひさびさ土曜に</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>きたよ！</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>26885</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>21:38:55</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>みーみ</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>ひさびさ</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>26887</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>22:17:43</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>あっくん、まりん</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>ひさしぶり</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>26889</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>22:48:19</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>お土産持ってきた！</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>26891</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>23:09:30</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NMGK、彩</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>二人で</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>26893</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>23:14:42</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>だいさく、たくや</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>ふたりで！</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>26895</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>00:00:10</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>ましゅ、きむ、どえむちゃん</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>三人で</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>26897</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>00:42:06</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>女子三人衆</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>きました！！</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>26898</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>00:42:29</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>かず、のんのん</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>きたよ</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>26899</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>00:42:42</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>けん</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>26903</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>01:04:50</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>れー、ぷらぐいん</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>きまいた</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>26905</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>01:31:58</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>K、N</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>きたよ！</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>26906</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>01:32:06</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ぺぺ</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>このあといきます！</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>初めまして、よろしくお願いします！</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>26907</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>01:32:29</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>みずき、りく、りん</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>女子三人</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>26911</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>02:19:30</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>しん</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>きたんご</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>26913</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>04:06:23</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>天然の100人ネキのねむ</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの日曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>本日8月16日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+天然の100人ネキのねむ
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>img20260816040623.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="posts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="来店履歴" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="来店回数" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3621,7 +3623,6 @@
           <t>おじきち</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>今</t>
@@ -3632,7 +3633,6 @@
           <t>きたよ！</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -3653,7 +3653,6 @@
           <t>まろ、おとは</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>はやめに</t>
@@ -3664,7 +3663,6 @@
           <t>きたよ</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -3685,7 +3683,6 @@
           <t>たつや</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>今</t>
@@ -3696,7 +3693,6 @@
           <t>きたｚ</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -3717,7 +3713,6 @@
           <t>S、Y</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>２回目</t>
@@ -3728,7 +3723,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -3749,7 +3743,6 @@
           <t>よっち</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>今</t>
@@ -3760,7 +3753,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -3781,7 +3773,6 @@
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>きょうも</t>
@@ -3792,7 +3783,6 @@
           <t>いるよ</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -3813,7 +3803,6 @@
           <t>まっする</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>今</t>
@@ -3824,7 +3813,6 @@
           <t>きたんご</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -3845,7 +3833,6 @@
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>今</t>
@@ -3856,7 +3843,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -3877,7 +3863,6 @@
           <t>まいなちゅ、えぬ</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>今</t>
@@ -3888,7 +3873,6 @@
           <t>きちゃ</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -3909,7 +3893,6 @@
           <t>こてっちゃん</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>ひさびさ土曜に</t>
@@ -3920,7 +3903,6 @@
           <t>きたよ！</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -3941,7 +3923,6 @@
           <t>みーみ</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>ひさびさ</t>
@@ -3952,7 +3933,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -3973,7 +3953,6 @@
           <t>あっくん、まりん</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>ひさしぶり</t>
@@ -3984,7 +3963,6 @@
           <t>きました♪</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -4005,7 +3983,6 @@
           <t>STR</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>いま</t>
@@ -4016,7 +3993,6 @@
           <t>お土産持ってきた！</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -4037,7 +4013,6 @@
           <t>NMGK、彩</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>二人で</t>
@@ -4048,7 +4023,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -4069,7 +4043,6 @@
           <t>だいさく、たくや</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>今日は</t>
@@ -4080,7 +4053,6 @@
           <t>ふたりで！</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -4101,7 +4073,6 @@
           <t>ましゅ、きむ、どえむちゃん</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>三人で</t>
@@ -4112,7 +4083,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -4133,7 +4103,6 @@
           <t>女子三人衆</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>今</t>
@@ -4144,7 +4113,6 @@
           <t>きました！！</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -4165,7 +4133,6 @@
           <t>かず、のんのん</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>さっき</t>
@@ -4176,7 +4143,6 @@
           <t>きたよ</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -4197,7 +4163,6 @@
           <t>けん</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>初めて</t>
@@ -4208,7 +4173,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -4229,7 +4193,6 @@
           <t>れー、ぷらぐいん</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>今</t>
@@ -4240,7 +4203,6 @@
           <t>きまいた</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -4261,7 +4223,6 @@
           <t>K、N</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>今日も</t>
@@ -4272,7 +4233,6 @@
           <t>きたよ！</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -4293,7 +4253,6 @@
           <t>ぺぺ</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>このあといきます！</t>
@@ -4304,7 +4263,6 @@
           <t>初めまして、よろしくお願いします！</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -4325,7 +4283,6 @@
           <t>みずき、りく、りん</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>女子三人</t>
@@ -4336,7 +4293,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -4357,7 +4313,6 @@
           <t>しん</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>いま</t>
@@ -4368,7 +4323,6 @@
           <t>きたんご</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -4425,4 +4379,9013 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H163"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>来店日</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>時刻</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>個人名</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>何回目</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>同伴(元の名前)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>題名</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>22:30:42</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>26656</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>はなまる</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>はなまる</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>久しぶりの</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>日曜日</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>22:33:32</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>26658</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>22:46:52</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>26660</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ゆうと</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ゆうと</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>これから行こうと思います</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>23:11:17</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>26662</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>カー</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>カー</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>23:45:37</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>26664</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ミコト、まいまい、テクノ</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ちいかわ</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>トークに</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>23:45:37</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>26664</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ミコト、まいまい、テクノ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ちいかわ</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>トークに</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>23:45:37</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>26664</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ミコト、まいまい、テクノ</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ちいかわ</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>トークに</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>00:14:17</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>26666</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>りょうちゃん</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>りょうちゃん</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>バンビ</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>はしご</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>01:18:22</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>26668</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>らうら</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>らうら</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>少し</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>きたんご</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19:02:51</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>26672</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>タツヤ</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>タツヤ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>牛タン青味噌</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>持ってきた！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20:00:29</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>26674</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ふくてゃ</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ふくてゃ、T山</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>激辛祭り！</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>サルサとグリーンカレーあります</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20:00:29</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>26674</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>T山</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ふくてゃ、T山</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>激辛祭り！</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>サルサとグリーンカレーあります</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>20:00:51</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>26675</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>イベたのしみに</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>きたよー♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20:10:13</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>26678</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bee</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bee</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>今週も</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>楽しみに♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20:20:35</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>26679</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>−、N</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>辛いの苦手だけど</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>頑張ります！</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20:20:35</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>26679</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>−、N</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>辛いの苦手だけど</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>頑張ります！</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20:32:57</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>26680</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>麻婆豆腐</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>持ってきたー</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>20:55:12</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>26684</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>KUMA</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>KUMA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>大宮バンビから</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>宇都宮は初です！</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>21:17:05</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>26686</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>コテッチャン</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>コテッチャン</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>来たぜ</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>月曜！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>21:40:04</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>26688</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>なお</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>なお</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>お土産</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>あるよ♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>22:30:38</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>26690</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ボンタ</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ボンタ</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>きてみました</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>22:39:46</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>26692</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ゆん</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ゆん</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>久々</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>きたよーん</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>22:55:44</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>26694</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>でで</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>でで</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>イベ楽しみに</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>23:23:33</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>26696</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>いっちゃん</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>いっちゃん</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>きましたー</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>23:55:47</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>26698</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>いぬ</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>いぬ、マッチョ、ももたろ</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ムキムキ三人衆で</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>来ましたー！</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>23:55:47</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>26698</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>マッチョ</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>いぬ、マッチョ、ももたろ</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ムキムキ三人衆で</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>来ましたー！</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>23:55:47</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>26698</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ももたろ</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>いぬ、マッチョ、ももたろ</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ムキムキ三人衆で</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>来ましたー！</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>23:56:21</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>26699</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ゆうたん</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ゆうたん、カモリ</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>カップルで</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>気になって来てみました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>23:56:21</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>26699</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>カモリ</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ゆうたん、カモリ</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>カップルで</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>気になって来てみました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>00:23:10</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>26702</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>アキ</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>アキ、コオリ</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>はじめてさん連れて</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>来ましたー</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>00:23:10</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>26702</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>コオリ</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>アキ、コオリ</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>はじめてさん連れて</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>来ましたー</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>01:06:16</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>26704</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ちょいのみ</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>きたよん</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>01:06:58</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>26705</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>てつ</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>てつ</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>田中</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>きたぞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>01:29:31</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>26708</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>H,M,D</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>はじめてです！</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>01:29:31</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>26708</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>H,M,D</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>はじめてです！</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>01:29:31</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>26708</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>H,M,D</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>はじめてです！</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>01:39:43</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>26709</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ともゆき</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ともゆき</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>あそびきてみました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>02:33:48</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>26710</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>しごわ</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>べろべろんちょ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>16:50:15</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>26716</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>だいち</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>だいち</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>初来店</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>よろしくお願いします
+本日、伺います</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>19:51:43</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>26718</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ダイチ</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ダイチ</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>きてます！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>21:09:24</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>26721</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>nuri</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>nuri</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>はじめていきます</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>緊張しますが行ってみようと思います！</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>21:33:39</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>26724</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>きんたまよ</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>きんたまよ</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2人でデート帰り</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ギンギンと雨でびしゃびしゃもう着きます</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>21:35:58</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>26725</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>仕事終わりに</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>きました！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>21:51:29</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>26728</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>マロ</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>マロ</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>久しぶりに</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>エルちゃんに会いに！</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>22:41:17</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>26729</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>のり</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>のり、あや</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ふたりで</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>きたよー！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>22:41:17</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>26729</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>あや</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>のり、あや</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ふたりで</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>きたよー！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>22:43:44</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>26730</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ひろとも</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ひろとも、ゆうき</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>気になってきちゃいました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>22:43:44</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>26730</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ゆうき</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>ひろとも、ゆうき</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>気になってきちゃいました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>00:43:48</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>26734</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>テクノとポチ</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>テクノとポチ</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ふたりで</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>きまちた♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>01:16:21</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>26736</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>少し休んでから</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>きた！</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>03:46:49</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>26738</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>JPTR</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>JPTR</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>はじめてきました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>14:54:08</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>26743</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ゆぴ</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ゆぴ</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>連休</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>楽しみます</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>17:37:22</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>26745</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>連日</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>登場！</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>17:39:06</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>26746</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>マッスル</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>マッスル</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>こんちわ</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>きまっする</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>19:11:18</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>26749</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>やえ</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>やえ</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>都内かえり</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>19:12:18</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>26750</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>かずき</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>かずき、フジ</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>二人で</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>二年ぶり</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>19:12:18</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>26750</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>フジ</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>かずき、フジ</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>二人で</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>二年ぶり</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>20:39:01</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>26753</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ゆうき</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ゆうき</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ひさしぶり</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>21:13:40</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>26755</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>よしおたん</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>よしおたん</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>韓国パブ</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>いってきた</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>21:37:26</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>26757</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>りゅう</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>りゅう、たく</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>21:37:26</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>26757</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>たく</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>りゅう、たく</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>21:52:18</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>26759</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>きちゃ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>21:52:35</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>26760</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>よしやん</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>よしやん、かな</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>きまんた</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>21:52:35</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>26760</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>かな</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>よしやん、かな</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>きまんた</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>23:13:38</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>26763</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>マナティ</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>マナティ</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>酔い冷ましに</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>行きます</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>01:39:12</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>26765</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>あゆ</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>あゆ</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>01:46:01</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>26766</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>げん</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>げん、ともち</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>01:46:01</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>26766</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ともち</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>げん、ともち</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>02:07:49</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>26769</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>まおし</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>まおし</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ひさびさに</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>きたゆ</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>02:37:55</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>26771</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>すー</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>すー</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>きちゃ</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>02:55:31</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>26773</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>たかやま</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>たかやま、りりこ</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>きた！</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>02:55:31</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>26773</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>りりこ</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>たかやま、りりこ</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>きた！</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>02:55:54</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>26774</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>まいまいん</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>まいまいん</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>きちゃー！！！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>03:20:48</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>26777</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>キム</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>キム、みれい</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>きまちた</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>03:20:48</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>26777</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>みれい</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>キム、みれい</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>きまちた</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>19:10:31</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>26781</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ふみ</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ふみ</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>19:16:23</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>26783</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ほぼ</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>オープン凸</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>19:57:51</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>26785</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>のんのん</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>のんのん</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>めずらしく</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>はやめに！</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>20:08:06</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>26786</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>きむ</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>きむ、りさ</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>20:08:06</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>26786</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>りさ</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>きむ、りさ</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>20:10:37</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>26787</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>飲みに</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>20:24:38</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>26791</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>たます</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>たます</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>ひさしぶり</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>21:05:25</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>26793</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>かける</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>かける</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>21:27:52</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>26795</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>オ・スー</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>オ・スー</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>あそびに</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>きましたよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>23:31:30</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>26797</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ぽちゃりす組</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ぽちゃりす組</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>01:11:19</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>26799</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>おちんぽベルセルク</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>おちんぽベルセルク</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>01:31:53</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>26801</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>zin</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>zin、あゆ</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>仕事終わりに</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>01:31:53</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>26801</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>あゆ</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>2</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>zin、あゆ</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>仕事終わりに</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>01:34:21</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>26803</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>みれい</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>みれい</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>昨日ぶり</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>02:06:00</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>26805</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ごん</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>ごん、ぶりちゃん</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>二人で</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>02:06:00</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>26805</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ぶりちゃん</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>ごん、ぶりちゃん</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>二人で</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>02:20:44</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>26807</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>まい</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>まい</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>シゴオワ</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>きた</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>02:21:07</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>26808</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>TKC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>TKC</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>飲みに</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>きた！</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>19:06:50</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>26813</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>おとは</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>おとは</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>金曜</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>きたよーん♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>19:07:26</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>26814</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>よっち</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>よっち</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>今日はオープンから</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>19:24:35</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>26817</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>りょう</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>りょう</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>これから</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>これから寄ってみます！</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>19:32:01</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>26818</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>4</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>まいまい、ゆずき</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>飲みおわ</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>きました！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>19:32:01</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>26818</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>4</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>まいまい、ゆずき</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>飲みおわ</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>きました！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>19:40:45</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>26819</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>マッスル</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>マッスル</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>きまんた！</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>19:43:56</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>26820</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ねここ</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>ねここ</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>19:51:19</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>26821</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ゆず</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>ゆず、ちぇちぇ</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>はじめて二人で</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>きました！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>19:51:19</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>26821</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ちぇちぇ</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>ゆず、ちぇちぇ</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>はじめて二人で</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>きました！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>20:15:26</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>26822</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>たいせー</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>たいせー</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>緊張しますが、本日お伺いします</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>20:18:29</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>26823</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>bee</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>bee</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>ぶんぶん</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>蜂さん！</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>20:18:55</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>26824</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>カズ</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>カズ</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>早めに来ました</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>21:45:29</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>26833</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>たいせい</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>たいせい</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>来ました！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>21:48:50</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>26834</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>かい</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>かい</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>前橋から</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>来ました！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>21:58:15</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>26837</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>るい</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>るい</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>22:05:09</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>26838</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>タツヤ</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>タツヤ</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>戦って</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>きましたー</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>22:06:17</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>26839</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ででたゃ</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>ででたゃ</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>きたよん！</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>22:48:24</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>26843</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>あにー</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>あにー、りえ、ゆり</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>しごおわ</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>行くマス</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>22:48:24</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>26843</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>りえ</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>あにー、りえ、ゆり</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>しごおわ</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>行くマス</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>22:48:24</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>26843</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ゆり</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>あにー、りえ、ゆり</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>しごおわ</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>行くマス</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>22:55:59</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>26845</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>みなっち</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>みなっち</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>23:22:10</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>26849</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>しゅん</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>しゅん</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>いきます</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>久しぶりに</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>00:11:14</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>26851</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>きむら</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>きむら</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>今から</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>おじやましますー</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>00:13:48</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>26853</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>3</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>00:44:59</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>26855</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>ましゅ、絶</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>00:44:59</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>26855</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>絶</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>ましゅ、絶</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>01:35:32</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>26857</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>りお</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>りお、めい、まい</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>しごおわ</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>01:35:32</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>26857</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>めい</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>りお、めい、まい</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>しごおわ</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>01:35:32</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>26857</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>まい</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>2</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>りお、めい、まい</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>しごおわ</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>02:19:37</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>26859</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>だいご</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>だいご</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>よばれて</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>きちゃよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>02:59:37</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>26861</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ザッキー</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>ザッキー、よっしー</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>02:59:37</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>26861</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>よっしー</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>ザッキー、よっしー</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>18:51:45</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>26865</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>おじきち</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>おじきち</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>きたよ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>18:57:32</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>26867</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>まろ</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>まろ、おとは</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>はやめに</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>きたよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>18:57:32</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>26867</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>おとは</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>2</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>まろ、おとは</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>はやめに</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>きたよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>19:28:11</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>26869</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>たつや</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>たつや</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>きたｚ</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>19:28:38</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>26870</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>S、Y</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>２回目</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>19:28:38</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>26870</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>S、Y</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>２回目</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>19:28:53</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>26871</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>よっち</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>2</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>よっち</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>19:49:47</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>26875</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>5</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>きょうも</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>いるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>19:50:08</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>26876</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>まっする</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>まっする</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>きたんご</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>20:30:43</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>26879</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>4</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>20:46:17</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>26881</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>まいなちゅ</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>まいなちゅ、えぬ</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>きちゃ</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>20:46:17</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>26881</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>えぬ</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>まいなちゅ、えぬ</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>きちゃ</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>20:46:44</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>26882</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>こてっちゃん</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>こてっちゃん</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>ひさびさ土曜に</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>きたよ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>21:38:55</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>26885</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>みーみ</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>みーみ</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>ひさびさ</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>22:17:43</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>26887</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>あっくん</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>あっくん、まりん</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>ひさしぶり</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>22:17:43</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>26887</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>まりん</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>あっくん、まりん</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>ひさしぶり</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>22:48:19</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>26889</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>お土産持ってきた！</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>23:09:30</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>26891</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NMGK</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>NMGK、彩</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>二人で</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>23:09:30</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>26891</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>NMGK、彩</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>二人で</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>23:14:42</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>26893</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>だいさく</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>だいさく、たくや</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>ふたりで！</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>23:14:42</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>26893</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>たくや</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>だいさく、たくや</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>ふたりで！</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>00:00:10</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>26895</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>2</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>ましゅ、きむ、どえむちゃん</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>三人で</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>00:00:10</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>26895</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>きむ</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>2</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>ましゅ、きむ、どえむちゃん</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>三人で</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>00:00:10</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>26895</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>どえむちゃん</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>ましゅ、きむ、どえむちゃん</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>三人で</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>00:42:06</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>26897</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>女子三人衆</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>女子三人衆</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>きました！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>00:42:29</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>26898</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>かず</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>かず、のんのん</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>きたよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>00:42:29</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>26898</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>のんのん</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>かず、のんのん</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>きたよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>00:42:42</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>26899</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>けん</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>けん</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>01:04:50</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>26903</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>れー</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>れー、ぷらぐいん</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>きまいた</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>01:04:50</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>26903</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>ぷらぐいん</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>1</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>れー、ぷらぐいん</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>きまいた</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>01:31:58</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>26905</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>K、N</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>きたよ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>01:31:58</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>26905</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>2</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>K、N</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>きたよ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>01:32:06</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>26906</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ぺぺ</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>ぺぺ</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>このあといきます！</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>初めまして、よろしくお願いします！</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>01:32:29</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>26907</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>みずき</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>みずき、りく、りん</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>女子三人</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>01:32:29</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>26907</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>りく</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>みずき、りく、りん</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>女子三人</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>01:32:29</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>26907</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>2</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>みずき、りく、りん</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>女子三人</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>02:19:30</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>26911</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>しん</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>しん</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>きたんご</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D139"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>個人名</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>来店回数</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>初回</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>最終</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>あゆ</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>おとは</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>きむ</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>のんのん</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>まい</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>みれい</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ゆうき</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>よっち</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>タツヤ</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>マッスル</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Bee</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>JPTR</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>KUMA</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NMGK</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TKC</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T山</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>bee</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>nuri</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>zin</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>あっくん</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>あにー</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>あや</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>いっちゃん</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>いぬ</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>えぬ</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>おじきち</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>おちんぽベルセルク</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>かい</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>かける</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>かず</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>かずき</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>かな</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>きむら</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>きんたまよ</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>けん</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>げん</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>こてっちゃん</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ごん</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>しゅん</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>しん</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>すー</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>たいせい</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>たいせー</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>たかやま</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>たく</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>たくや</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>たつや</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>たます</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>だいご</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>だいさく</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>だいち</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ちぇちぇ</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>てつ</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>でで</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ででたゃ</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ともち</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ともゆき</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>どえむちゃん</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>なお</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ねここ</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>のり</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>はなまる</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ひろとも</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ふくてゃ</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ふみ</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ぶりちゃん</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ぷらぐいん</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ぺぺ</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ぽちゃりす組</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>まいなちゅ</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>まいまいん</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>まおし</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>まっする</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>まりん</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>まろ</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>みずき</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>みなっち</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>みーみ</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>めい</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ももたろ</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>やえ</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ゆうたん</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ゆうと</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ゆず</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ゆぴ</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ゆり</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ゆん</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>よしおたん</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>よしやん</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>よっしー</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>らうら</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>りえ</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>りお</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>りく</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>りさ</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>りゅう</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>りょう</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>りょうちゃん</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>りりこ</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>るい</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>れー</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>アキ</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>オ・スー</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>カズ</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>カモリ</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>カー</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>キム</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>コオリ</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>コテッチャン</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ザッキー</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ダイチ</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>テクノとポチ</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>フジ</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ボンタ</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>マッチョ</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>マナティ</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>マロ</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>女子三人衆</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>絶</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -10,6 +10,7 @@
     <sheet name="posts" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="来店履歴" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="来店回数" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="曜日別" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4387,7 +4388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H163"/>
+  <dimension ref="A1:I163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4398,35 +4399,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>曜日</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>時刻</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>個人名</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>何回目</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>同伴(元の名前)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>題名</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
@@ -4440,31 +4446,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>22:30:42</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>26656</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>はなまる</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>はなまる</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>久しぶりの</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>日曜日</t>
         </is>
@@ -4478,31 +4489,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>22:33:32</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>26658</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>大塚</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>大塚</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>きたよー</t>
         </is>
@@ -4516,31 +4532,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>22:46:52</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>26660</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>ゆうと</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>ゆうと</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>初めて</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>これから行こうと思います</t>
         </is>
@@ -4554,31 +4575,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>23:11:17</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>26662</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>カー</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>カー</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>来ました</t>
         </is>
@@ -4592,31 +4618,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>23:45:37</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>26664</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>ミコト</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>ミコト、まいまい、テクノ</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>ちいかわ</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>トークに</t>
         </is>
@@ -4630,31 +4661,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>23:45:37</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>26664</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>まいまい</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>ミコト、まいまい、テクノ</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>ちいかわ</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>トークに</t>
         </is>
@@ -4668,31 +4704,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>23:45:37</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>26664</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>テクノ</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>ミコト、まいまい、テクノ</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>ちいかわ</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>トークに</t>
         </is>
@@ -4706,31 +4747,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>00:14:17</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>26666</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>りょうちゃん</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>りょうちゃん</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>バンビ</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>はしご</t>
         </is>
@@ -4744,31 +4790,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>01:18:22</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>26668</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>らうら</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>らうら</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>少し</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>きたんご</t>
         </is>
@@ -4782,31 +4833,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>19:02:51</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>26672</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>タツヤ</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>タツヤ</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>牛タン青味噌</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>持ってきた！！</t>
         </is>
@@ -4820,31 +4876,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>20:00:29</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>26674</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>ふくてゃ</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>ふくてゃ、T山</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>激辛祭り！</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>サルサとグリーンカレーあります</t>
         </is>
@@ -4858,31 +4919,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>20:00:29</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>26674</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>T山</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>ふくてゃ、T山</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>激辛祭り！</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>サルサとグリーンカレーあります</t>
         </is>
@@ -4896,31 +4962,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>20:00:51</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>26675</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>ひがん</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>イベたのしみに</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>きたよー♪</t>
         </is>
@@ -4934,31 +5005,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>20:10:13</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>26678</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Bee</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>Bee</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>今週も</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>楽しみに♪</t>
         </is>
@@ -4972,31 +5048,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>20:20:35</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>26679</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>−、N</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>辛いの苦手だけど</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>頑張ります！</t>
         </is>
@@ -5010,31 +5091,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>20:20:35</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>26679</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>−、N</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>辛いの苦手だけど</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>頑張ります！</t>
         </is>
@@ -5048,31 +5134,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>20:32:57</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>26680</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>テクノ</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>2</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>テクノ</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>麻婆豆腐</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>持ってきたー</t>
         </is>
@@ -5086,31 +5177,36 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>20:55:12</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>26684</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>KUMA</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>KUMA</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>大宮バンビから</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>宇都宮は初です！</t>
         </is>
@@ -5124,31 +5220,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>21:17:05</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>26686</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>コテッチャン</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>コテッチャン</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>来たぜ</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>月曜！！</t>
         </is>
@@ -5162,31 +5263,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>21:40:04</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>26688</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>なお</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>なお</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>お土産</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>あるよ♪</t>
         </is>
@@ -5200,31 +5306,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>22:30:38</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>26690</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>ボンタ</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>ボンタ</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>初めて</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>きてみました</t>
         </is>
@@ -5238,31 +5349,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>22:39:46</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>26692</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>ゆん</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>ゆん</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>久々</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>きたよーん</t>
         </is>
@@ -5276,31 +5392,36 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>22:55:44</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>26694</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>でで</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>でで</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>イベ楽しみに</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>きたよー</t>
         </is>
@@ -5314,31 +5435,36 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>23:23:33</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>26696</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>いっちゃん</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>いっちゃん</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>遊びに</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>きましたー</t>
         </is>
@@ -5352,31 +5478,36 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>23:55:47</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>26698</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>いぬ</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>いぬ、マッチョ、ももたろ</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>ムキムキ三人衆で</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>来ましたー！</t>
         </is>
@@ -5390,31 +5521,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>23:55:47</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>26698</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>マッチョ</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>いぬ、マッチョ、ももたろ</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>ムキムキ三人衆で</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>来ましたー！</t>
         </is>
@@ -5428,31 +5564,36 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>23:55:47</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>26698</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>ももたろ</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>いぬ、マッチョ、ももたろ</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>ムキムキ三人衆で</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>来ましたー！</t>
         </is>
@@ -5466,31 +5607,36 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>23:56:21</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>26699</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>ゆうたん</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>ゆうたん、カモリ</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>カップルで</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>気になって来てみました♪</t>
         </is>
@@ -5504,31 +5650,36 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>23:56:21</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>26699</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>カモリ</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>ゆうたん、カモリ</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>カップルで</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>気になって来てみました♪</t>
         </is>
@@ -5542,31 +5693,36 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>00:23:10</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>26702</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>アキ</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>アキ、コオリ</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>はじめてさん連れて</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>来ましたー</t>
         </is>
@@ -5580,31 +5736,36 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>00:23:10</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>26702</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>コオリ</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>アキ、コオリ</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>はじめてさん連れて</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>来ましたー</t>
         </is>
@@ -5618,31 +5779,36 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>01:06:16</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>26704</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>ちょいのみ</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>きたよん</t>
         </is>
@@ -5656,31 +5822,36 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>01:06:58</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="D34" t="n">
         <v>26705</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>てつ</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>てつ</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>田中</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>きたぞ</t>
         </is>
@@ -5694,31 +5865,36 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>01:29:31</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="D35" t="n">
         <v>26708</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>H,M,D</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>みんなで</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>はじめてです！</t>
         </is>
@@ -5732,31 +5908,36 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>01:29:31</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="D36" t="n">
         <v>26708</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>H,M,D</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>みんなで</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>はじめてです！</t>
         </is>
@@ -5770,31 +5951,36 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>01:29:31</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>26708</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>H,M,D</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>みんなで</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>はじめてです！</t>
         </is>
@@ -5808,31 +5994,36 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>01:39:43</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="D38" t="n">
         <v>26709</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>ともゆき</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>ともゆき</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>はじめて</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>あそびきてみました！</t>
         </is>
@@ -5846,31 +6037,36 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>02:33:48</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>26710</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>まいまい</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>2</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>まいまい</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>しごわ</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>べろべろんちょ</t>
         </is>
@@ -5884,31 +6080,36 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>16:50:15</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="D40" t="n">
         <v>26716</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>だいち</t>
         </is>
       </c>
-      <c r="E40" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>だいち</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>初来店</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>よろしくお願いします
 本日、伺います</t>
@@ -5923,31 +6124,36 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>19:51:43</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="D41" t="n">
         <v>26718</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>ダイチ</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>ダイチ</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>はじめて</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>きてます！！</t>
         </is>
@@ -5961,31 +6167,36 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>21:09:24</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="D42" t="n">
         <v>26721</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>nuri</t>
         </is>
       </c>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>nuri</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>はじめていきます</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>緊張しますが行ってみようと思います！</t>
         </is>
@@ -5999,31 +6210,36 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>21:33:39</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="D43" t="n">
         <v>26724</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>きんたまよ</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>きんたまよ</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>2人でデート帰り</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>ギンギンと雨でびしゃびしゃもう着きます</t>
         </is>
@@ -6037,31 +6253,36 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>21:35:58</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="D44" t="n">
         <v>26725</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>2</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>仕事終わりに</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>きました！！</t>
         </is>
@@ -6075,31 +6296,36 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>21:51:29</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="D45" t="n">
         <v>26728</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>マロ</t>
         </is>
       </c>
-      <c r="E45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>マロ</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>久しぶりに</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>エルちゃんに会いに！</t>
         </is>
@@ -6113,31 +6339,36 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>22:41:17</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="D46" t="n">
         <v>26729</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>のり</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>のり、あや</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>ふたりで</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>きたよー！！</t>
         </is>
@@ -6151,31 +6382,36 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>22:41:17</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="D47" t="n">
         <v>26729</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>あや</t>
         </is>
       </c>
-      <c r="E47" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>のり、あや</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>ふたりで</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>きたよー！！</t>
         </is>
@@ -6189,31 +6425,36 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>22:43:44</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="D48" t="n">
         <v>26730</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>ひろとも</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>ひろとも、ゆうき</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>はじめて</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>気になってきちゃいました♪</t>
         </is>
@@ -6227,31 +6468,36 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>22:43:44</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="D49" t="n">
         <v>26730</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>ゆうき</t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>ひろとも、ゆうき</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>はじめて</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>気になってきちゃいました♪</t>
         </is>
@@ -6265,31 +6511,36 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>00:43:48</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="D50" t="n">
         <v>26734</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>テクノとポチ</t>
         </is>
       </c>
-      <c r="E50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr">
         <is>
           <t>テクノとポチ</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>ふたりで</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>きまちた♪</t>
         </is>
@@ -6303,31 +6554,36 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>01:16:21</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="D51" t="n">
         <v>26736</v>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>まいまい</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>3</v>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>まいまい</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>少し休んでから</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>きた！</t>
         </is>
@@ -6341,31 +6597,36 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>03:46:49</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="D52" t="n">
         <v>26738</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>JPTR</t>
         </is>
       </c>
-      <c r="E52" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>JPTR</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>みんなで</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>はじめてきました！</t>
         </is>
@@ -6379,31 +6640,36 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>14:54:08</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="D53" t="n">
         <v>26743</v>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>ゆぴ</t>
         </is>
       </c>
-      <c r="E53" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="inlineStr">
         <is>
           <t>ゆぴ</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>連休</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>楽しみます</t>
         </is>
@@ -6417,31 +6683,36 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>17:37:22</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="D54" t="n">
         <v>26745</v>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>3</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>連日</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>登場！</t>
         </is>
@@ -6455,31 +6726,36 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>17:39:06</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="D55" t="n">
         <v>26746</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>マッスル</t>
         </is>
       </c>
-      <c r="E55" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>マッスル</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>こんちわ</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>きまっする</t>
         </is>
@@ -6493,31 +6769,36 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>19:11:18</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="D56" t="n">
         <v>26749</v>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>やえ</t>
         </is>
       </c>
-      <c r="E56" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>やえ</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>都内かえり</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -6531,31 +6812,36 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>19:12:18</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="D57" t="n">
         <v>26750</v>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>かずき</t>
         </is>
       </c>
-      <c r="E57" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="inlineStr">
         <is>
           <t>かずき、フジ</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>二人で</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>二年ぶり</t>
         </is>
@@ -6569,31 +6855,36 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>19:12:18</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="D58" t="n">
         <v>26750</v>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>フジ</t>
         </is>
       </c>
-      <c r="E58" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>かずき、フジ</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>二人で</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>二年ぶり</t>
         </is>
@@ -6607,31 +6898,36 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>20:39:01</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="D59" t="n">
         <v>26753</v>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>ゆうき</t>
         </is>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>2</v>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>ゆうき</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>ひさしぶり</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -6645,31 +6941,36 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>21:13:40</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="D60" t="n">
         <v>26755</v>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>よしおたん</t>
         </is>
       </c>
-      <c r="E60" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="inlineStr">
         <is>
           <t>よしおたん</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>韓国パブ</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>いってきた</t>
         </is>
@@ -6683,31 +6984,36 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>21:37:26</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="D61" t="n">
         <v>26757</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>りゅう</t>
         </is>
       </c>
-      <c r="E61" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr">
         <is>
           <t>りゅう、たく</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -6721,31 +7027,36 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>21:37:26</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="D62" t="n">
         <v>26757</v>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>たく</t>
         </is>
       </c>
-      <c r="E62" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="inlineStr">
         <is>
           <t>りゅう、たく</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -6759,31 +7070,36 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>21:52:18</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="D63" t="n">
         <v>26759</v>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E63" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>きちゃ！</t>
         </is>
@@ -6797,31 +7113,36 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>21:52:35</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="D64" t="n">
         <v>26760</v>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>よしやん</t>
         </is>
       </c>
-      <c r="E64" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>よしやん、かな</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>きまんた</t>
         </is>
@@ -6835,31 +7156,36 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
           <t>21:52:35</t>
         </is>
       </c>
-      <c r="C65" t="n">
+      <c r="D65" t="n">
         <v>26760</v>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>かな</t>
         </is>
       </c>
-      <c r="E65" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="inlineStr">
         <is>
           <t>よしやん、かな</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>きまんた</t>
         </is>
@@ -6873,31 +7199,36 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>23:13:38</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="D66" t="n">
         <v>26763</v>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>マナティ</t>
         </is>
       </c>
-      <c r="E66" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="inlineStr">
         <is>
           <t>マナティ</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>酔い冷ましに</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>行きます</t>
         </is>
@@ -6911,31 +7242,36 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>01:39:12</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="D67" t="n">
         <v>26765</v>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>あゆ</t>
         </is>
       </c>
-      <c r="E67" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>あゆ</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -6949,31 +7285,36 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
           <t>01:46:01</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="D68" t="n">
         <v>26766</v>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>げん</t>
         </is>
       </c>
-      <c r="E68" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>げん、ともち</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -6987,31 +7328,36 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
           <t>01:46:01</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="D69" t="n">
         <v>26766</v>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>ともち</t>
         </is>
       </c>
-      <c r="E69" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>げん、ともち</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -7025,31 +7371,36 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
           <t>02:07:49</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="D70" t="n">
         <v>26769</v>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>まおし</t>
         </is>
       </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="inlineStr">
         <is>
           <t>まおし</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>ひさびさに</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>きたゆ</t>
         </is>
@@ -7063,31 +7414,36 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
           <t>02:37:55</t>
         </is>
       </c>
-      <c r="C71" t="n">
+      <c r="D71" t="n">
         <v>26771</v>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>すー</t>
         </is>
       </c>
-      <c r="E71" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>すー</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>きちゃ</t>
         </is>
@@ -7101,31 +7457,36 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
           <t>02:55:31</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="D72" t="n">
         <v>26773</v>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>たかやま</t>
         </is>
       </c>
-      <c r="E72" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="inlineStr">
         <is>
           <t>たかやま、りりこ</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>きた！</t>
         </is>
@@ -7139,31 +7500,36 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
           <t>02:55:31</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="D73" t="n">
         <v>26773</v>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>りりこ</t>
         </is>
       </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" t="inlineStr">
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr">
         <is>
           <t>たかやま、りりこ</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>きた！</t>
         </is>
@@ -7177,31 +7543,36 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
           <t>02:55:54</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="D74" t="n">
         <v>26774</v>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>まいまいん</t>
         </is>
       </c>
-      <c r="E74" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>まいまいん</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>きちゃー！！！！</t>
         </is>
@@ -7215,31 +7586,36 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
           <t>03:20:48</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="D75" t="n">
         <v>26777</v>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>キム</t>
         </is>
       </c>
-      <c r="E75" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="inlineStr">
         <is>
           <t>キム、みれい</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>さっき</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>きまちた</t>
         </is>
@@ -7253,31 +7629,36 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
           <t>03:20:48</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="D76" t="n">
         <v>26777</v>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>みれい</t>
         </is>
       </c>
-      <c r="E76" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>キム、みれい</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>さっき</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>きまちた</t>
         </is>
@@ -7291,31 +7672,36 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
           <t>19:10:31</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="D77" t="n">
         <v>26781</v>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>ふみ</t>
         </is>
       </c>
-      <c r="E77" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="inlineStr">
         <is>
           <t>ふみ</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>はじめて</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>きました♪</t>
         </is>
@@ -7329,31 +7715,36 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
           <t>19:16:23</t>
         </is>
       </c>
-      <c r="C78" t="n">
+      <c r="D78" t="n">
         <v>26783</v>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E78" t="n">
+      <c r="F78" t="n">
         <v>2</v>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>ひがん</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>ほぼ</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>オープン凸</t>
         </is>
@@ -7367,31 +7758,36 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
           <t>19:57:51</t>
         </is>
       </c>
-      <c r="C79" t="n">
+      <c r="D79" t="n">
         <v>26785</v>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>のんのん</t>
         </is>
       </c>
-      <c r="E79" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="inlineStr">
         <is>
           <t>のんのん</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>めずらしく</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>はやめに！</t>
         </is>
@@ -7405,31 +7801,36 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
           <t>20:08:06</t>
         </is>
       </c>
-      <c r="C80" t="n">
+      <c r="D80" t="n">
         <v>26786</v>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>きむ</t>
         </is>
       </c>
-      <c r="E80" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>きむ、りさ</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>今日も</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -7443,31 +7844,36 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
           <t>20:08:06</t>
         </is>
       </c>
-      <c r="C81" t="n">
+      <c r="D81" t="n">
         <v>26786</v>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>りさ</t>
         </is>
       </c>
-      <c r="E81" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" t="inlineStr">
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>きむ、りさ</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>今日も</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -7481,31 +7887,36 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
           <t>20:10:37</t>
         </is>
       </c>
-      <c r="C82" t="n">
+      <c r="D82" t="n">
         <v>26787</v>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>りん</t>
         </is>
       </c>
-      <c r="E82" t="n">
-        <v>1</v>
-      </c>
-      <c r="F82" t="inlineStr">
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>りん</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>飲みに</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -7519,31 +7930,36 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
           <t>20:24:38</t>
         </is>
       </c>
-      <c r="C83" t="n">
+      <c r="D83" t="n">
         <v>26791</v>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>たます</t>
         </is>
       </c>
-      <c r="E83" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" t="inlineStr">
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="inlineStr">
         <is>
           <t>たます</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>ひさしぶり</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -7557,31 +7973,36 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
           <t>21:05:25</t>
         </is>
       </c>
-      <c r="C84" t="n">
+      <c r="D84" t="n">
         <v>26793</v>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>かける</t>
         </is>
       </c>
-      <c r="E84" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" t="inlineStr">
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>かける</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>はじめて</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -7595,31 +8016,36 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
           <t>21:27:52</t>
         </is>
       </c>
-      <c r="C85" t="n">
+      <c r="D85" t="n">
         <v>26795</v>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>オ・スー</t>
         </is>
       </c>
-      <c r="E85" t="n">
-        <v>1</v>
-      </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>オ・スー</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>あそびに</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>きましたよ</t>
         </is>
@@ -7633,31 +8059,36 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
           <t>23:31:30</t>
         </is>
       </c>
-      <c r="C86" t="n">
+      <c r="D86" t="n">
         <v>26797</v>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>ぽちゃりす組</t>
         </is>
       </c>
-      <c r="E86" t="n">
-        <v>1</v>
-      </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>ぽちゃりす組</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>いま</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -7671,31 +8102,36 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
           <t>01:11:19</t>
         </is>
       </c>
-      <c r="C87" t="n">
+      <c r="D87" t="n">
         <v>26799</v>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>おちんぽベルセルク</t>
         </is>
       </c>
-      <c r="E87" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>おちんぽベルセルク</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>すこし</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>きました♪</t>
         </is>
@@ -7709,31 +8145,36 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
           <t>01:31:53</t>
         </is>
       </c>
-      <c r="C88" t="n">
+      <c r="D88" t="n">
         <v>26801</v>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>zin</t>
         </is>
       </c>
-      <c r="E88" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" t="inlineStr">
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>zin、あゆ</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>仕事終わりに</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -7747,31 +8188,36 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
           <t>01:31:53</t>
         </is>
       </c>
-      <c r="C89" t="n">
+      <c r="D89" t="n">
         <v>26801</v>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>あゆ</t>
         </is>
       </c>
-      <c r="E89" t="n">
+      <c r="F89" t="n">
         <v>2</v>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>zin、あゆ</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>仕事終わりに</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -7785,31 +8231,36 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
           <t>01:34:21</t>
         </is>
       </c>
-      <c r="C90" t="n">
+      <c r="D90" t="n">
         <v>26803</v>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>みれい</t>
         </is>
       </c>
-      <c r="E90" t="n">
+      <c r="F90" t="n">
         <v>2</v>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>みれい</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>昨日ぶり</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -7823,31 +8274,36 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
           <t>02:06:00</t>
         </is>
       </c>
-      <c r="C91" t="n">
+      <c r="D91" t="n">
         <v>26805</v>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>ごん</t>
         </is>
       </c>
-      <c r="E91" t="n">
-        <v>1</v>
-      </c>
-      <c r="F91" t="inlineStr">
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="inlineStr">
         <is>
           <t>ごん、ぶりちゃん</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>二人で</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -7861,31 +8317,36 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
           <t>02:06:00</t>
         </is>
       </c>
-      <c r="C92" t="n">
+      <c r="D92" t="n">
         <v>26805</v>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>ぶりちゃん</t>
         </is>
       </c>
-      <c r="E92" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" t="inlineStr">
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>ごん、ぶりちゃん</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>二人で</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -7899,31 +8360,36 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
           <t>02:20:44</t>
         </is>
       </c>
-      <c r="C93" t="n">
+      <c r="D93" t="n">
         <v>26807</v>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>まい</t>
         </is>
       </c>
-      <c r="E93" t="n">
-        <v>1</v>
-      </c>
-      <c r="F93" t="inlineStr">
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>まい</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>シゴオワ</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>きた</t>
         </is>
@@ -7937,31 +8403,36 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
           <t>02:21:07</t>
         </is>
       </c>
-      <c r="C94" t="n">
+      <c r="D94" t="n">
         <v>26808</v>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>TKC</t>
         </is>
       </c>
-      <c r="E94" t="n">
-        <v>1</v>
-      </c>
-      <c r="F94" t="inlineStr">
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>TKC</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>飲みに</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>きた！</t>
         </is>
@@ -7975,31 +8446,36 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
           <t>19:06:50</t>
         </is>
       </c>
-      <c r="C95" t="n">
+      <c r="D95" t="n">
         <v>26813</v>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>おとは</t>
         </is>
       </c>
-      <c r="E95" t="n">
-        <v>1</v>
-      </c>
-      <c r="F95" t="inlineStr">
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>おとは</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>金曜</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>きたよーん♪</t>
         </is>
@@ -8013,31 +8489,36 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
           <t>19:07:26</t>
         </is>
       </c>
-      <c r="C96" t="n">
+      <c r="D96" t="n">
         <v>26814</v>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>よっち</t>
         </is>
       </c>
-      <c r="E96" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" t="inlineStr">
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="inlineStr">
         <is>
           <t>よっち</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>今日はオープンから</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -8051,31 +8532,36 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
           <t>19:24:35</t>
         </is>
       </c>
-      <c r="C97" t="n">
+      <c r="D97" t="n">
         <v>26817</v>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>りょう</t>
         </is>
       </c>
-      <c r="E97" t="n">
-        <v>1</v>
-      </c>
-      <c r="F97" t="inlineStr">
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>りょう</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>これから</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>これから寄ってみます！</t>
         </is>
@@ -8089,31 +8575,36 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
           <t>19:32:01</t>
         </is>
       </c>
-      <c r="C98" t="n">
+      <c r="D98" t="n">
         <v>26818</v>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>まいまい</t>
         </is>
       </c>
-      <c r="E98" t="n">
+      <c r="F98" t="n">
         <v>4</v>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>まいまい、ゆずき</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>飲みおわ</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>きました！！</t>
         </is>
@@ -8127,31 +8618,36 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
           <t>19:32:01</t>
         </is>
       </c>
-      <c r="C99" t="n">
+      <c r="D99" t="n">
         <v>26818</v>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="E99" t="n">
+      <c r="F99" t="n">
         <v>4</v>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>まいまい、ゆずき</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>飲みおわ</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>きました！！</t>
         </is>
@@ -8165,31 +8661,36 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
           <t>19:40:45</t>
         </is>
       </c>
-      <c r="C100" t="n">
+      <c r="D100" t="n">
         <v>26819</v>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>マッスル</t>
         </is>
       </c>
-      <c r="E100" t="n">
+      <c r="F100" t="n">
         <v>2</v>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>マッスル</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>今日も</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>きまんた！</t>
         </is>
@@ -8203,31 +8704,36 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
           <t>19:43:56</t>
         </is>
       </c>
-      <c r="C101" t="n">
+      <c r="D101" t="n">
         <v>26820</v>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>ねここ</t>
         </is>
       </c>
-      <c r="E101" t="n">
-        <v>1</v>
-      </c>
-      <c r="F101" t="inlineStr">
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" t="inlineStr">
         <is>
           <t>ねここ</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>はじめて</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -8241,31 +8747,36 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
           <t>19:51:19</t>
         </is>
       </c>
-      <c r="C102" t="n">
+      <c r="D102" t="n">
         <v>26821</v>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>ゆず</t>
         </is>
       </c>
-      <c r="E102" t="n">
-        <v>1</v>
-      </c>
-      <c r="F102" t="inlineStr">
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="inlineStr">
         <is>
           <t>ゆず、ちぇちぇ</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>はじめて二人で</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>きました！！</t>
         </is>
@@ -8279,31 +8790,36 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
           <t>19:51:19</t>
         </is>
       </c>
-      <c r="C103" t="n">
+      <c r="D103" t="n">
         <v>26821</v>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>ちぇちぇ</t>
         </is>
       </c>
-      <c r="E103" t="n">
-        <v>1</v>
-      </c>
-      <c r="F103" t="inlineStr">
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" t="inlineStr">
         <is>
           <t>ゆず、ちぇちぇ</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>はじめて二人で</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>きました！！</t>
         </is>
@@ -8317,31 +8833,36 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
           <t>20:15:26</t>
         </is>
       </c>
-      <c r="C104" t="n">
+      <c r="D104" t="n">
         <v>26822</v>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>たいせー</t>
         </is>
       </c>
-      <c r="E104" t="n">
-        <v>1</v>
-      </c>
-      <c r="F104" t="inlineStr">
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" t="inlineStr">
         <is>
           <t>たいせー</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>初めて</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>緊張しますが、本日お伺いします</t>
         </is>
@@ -8355,31 +8876,36 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
           <t>20:18:29</t>
         </is>
       </c>
-      <c r="C105" t="n">
+      <c r="D105" t="n">
         <v>26823</v>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>bee</t>
         </is>
       </c>
-      <c r="E105" t="n">
-        <v>1</v>
-      </c>
-      <c r="F105" t="inlineStr">
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" t="inlineStr">
         <is>
           <t>bee</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>ぶんぶん</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>蜂さん！</t>
         </is>
@@ -8393,31 +8919,36 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
           <t>20:18:55</t>
         </is>
       </c>
-      <c r="C106" t="n">
+      <c r="D106" t="n">
         <v>26824</v>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>カズ</t>
         </is>
       </c>
-      <c r="E106" t="n">
-        <v>1</v>
-      </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" t="inlineStr">
         <is>
           <t>カズ</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>今日は</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>早めに来ました</t>
         </is>
@@ -8431,31 +8962,36 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
           <t>21:45:29</t>
         </is>
       </c>
-      <c r="C107" t="n">
+      <c r="D107" t="n">
         <v>26833</v>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>たいせい</t>
         </is>
       </c>
-      <c r="E107" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" t="inlineStr">
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="inlineStr">
         <is>
           <t>たいせい</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>初めて</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>来ました！！</t>
         </is>
@@ -8469,31 +9005,36 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
           <t>21:48:50</t>
         </is>
       </c>
-      <c r="C108" t="n">
+      <c r="D108" t="n">
         <v>26834</v>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>かい</t>
         </is>
       </c>
-      <c r="E108" t="n">
-        <v>1</v>
-      </c>
-      <c r="F108" t="inlineStr">
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" t="inlineStr">
         <is>
           <t>かい</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t>前橋から</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t>来ました！！</t>
         </is>
@@ -8507,31 +9048,36 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
           <t>21:58:15</t>
         </is>
       </c>
-      <c r="C109" t="n">
+      <c r="D109" t="n">
         <v>26837</v>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>るい</t>
         </is>
       </c>
-      <c r="E109" t="n">
-        <v>1</v>
-      </c>
-      <c r="F109" t="inlineStr">
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" t="inlineStr">
         <is>
           <t>るい</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>遊びに</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -8545,31 +9091,36 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
           <t>22:05:09</t>
         </is>
       </c>
-      <c r="C110" t="n">
+      <c r="D110" t="n">
         <v>26838</v>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>タツヤ</t>
         </is>
       </c>
-      <c r="E110" t="n">
+      <c r="F110" t="n">
         <v>2</v>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>タツヤ</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t>戦って</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t>きましたー</t>
         </is>
@@ -8583,31 +9134,36 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
           <t>22:06:17</t>
         </is>
       </c>
-      <c r="C111" t="n">
+      <c r="D111" t="n">
         <v>26839</v>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>ででたゃ</t>
         </is>
       </c>
-      <c r="E111" t="n">
-        <v>1</v>
-      </c>
-      <c r="F111" t="inlineStr">
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" t="inlineStr">
         <is>
           <t>ででたゃ</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>遊びに</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t>きたよん！</t>
         </is>
@@ -8621,31 +9177,36 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
           <t>22:48:24</t>
         </is>
       </c>
-      <c r="C112" t="n">
+      <c r="D112" t="n">
         <v>26843</v>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="E112" t="inlineStr">
         <is>
           <t>あにー</t>
         </is>
       </c>
-      <c r="E112" t="n">
-        <v>1</v>
-      </c>
-      <c r="F112" t="inlineStr">
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" t="inlineStr">
         <is>
           <t>あにー、りえ、ゆり</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t>しごおわ</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t>行くマス</t>
         </is>
@@ -8659,31 +9220,36 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
           <t>22:48:24</t>
         </is>
       </c>
-      <c r="C113" t="n">
+      <c r="D113" t="n">
         <v>26843</v>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>りえ</t>
         </is>
       </c>
-      <c r="E113" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" t="inlineStr">
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" t="inlineStr">
         <is>
           <t>あにー、りえ、ゆり</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>しごおわ</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t>行くマス</t>
         </is>
@@ -8697,31 +9263,36 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
           <t>22:48:24</t>
         </is>
       </c>
-      <c r="C114" t="n">
+      <c r="D114" t="n">
         <v>26843</v>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>ゆり</t>
         </is>
       </c>
-      <c r="E114" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" t="inlineStr">
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" t="inlineStr">
         <is>
           <t>あにー、りえ、ゆり</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t>しごおわ</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t>行くマス</t>
         </is>
@@ -8735,31 +9306,36 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
           <t>22:55:59</t>
         </is>
       </c>
-      <c r="C115" t="n">
+      <c r="D115" t="n">
         <v>26845</v>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>みなっち</t>
         </is>
       </c>
-      <c r="E115" t="n">
-        <v>1</v>
-      </c>
-      <c r="F115" t="inlineStr">
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" t="inlineStr">
         <is>
           <t>みなっち</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>遊びに</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -8773,31 +9349,36 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
           <t>23:22:10</t>
         </is>
       </c>
-      <c r="C116" t="n">
+      <c r="D116" t="n">
         <v>26849</v>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>しゅん</t>
         </is>
       </c>
-      <c r="E116" t="n">
-        <v>1</v>
-      </c>
-      <c r="F116" t="inlineStr">
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" t="inlineStr">
         <is>
           <t>しゅん</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>いきます</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t>久しぶりに</t>
         </is>
@@ -8811,31 +9392,36 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
           <t>00:11:14</t>
         </is>
       </c>
-      <c r="C117" t="n">
+      <c r="D117" t="n">
         <v>26851</v>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="E117" t="inlineStr">
         <is>
           <t>きむら</t>
         </is>
       </c>
-      <c r="E117" t="n">
-        <v>1</v>
-      </c>
-      <c r="F117" t="inlineStr">
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" t="inlineStr">
         <is>
           <t>きむら</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>今から</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t>おじやましますー</t>
         </is>
@@ -8849,31 +9435,36 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
           <t>00:13:48</t>
         </is>
       </c>
-      <c r="C118" t="n">
+      <c r="D118" t="n">
         <v>26853</v>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="E118" t="inlineStr">
         <is>
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E118" t="n">
+      <c r="F118" t="n">
         <v>3</v>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t>ひがん</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t>いま</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="I118" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -8887,31 +9478,36 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
           <t>00:44:59</t>
         </is>
       </c>
-      <c r="C119" t="n">
+      <c r="D119" t="n">
         <v>26855</v>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>ましゅ</t>
         </is>
       </c>
-      <c r="E119" t="n">
-        <v>1</v>
-      </c>
-      <c r="F119" t="inlineStr">
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" t="inlineStr">
         <is>
           <t>ましゅ、絶</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="H119" t="inlineStr">
         <is>
           <t>遊びに</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -8925,31 +9521,36 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
           <t>00:44:59</t>
         </is>
       </c>
-      <c r="C120" t="n">
+      <c r="D120" t="n">
         <v>26855</v>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="E120" t="inlineStr">
         <is>
           <t>絶</t>
         </is>
       </c>
-      <c r="E120" t="n">
-        <v>1</v>
-      </c>
-      <c r="F120" t="inlineStr">
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="inlineStr">
         <is>
           <t>ましゅ、絶</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="H120" t="inlineStr">
         <is>
           <t>遊びに</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="I120" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -8963,31 +9564,36 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
           <t>01:35:32</t>
         </is>
       </c>
-      <c r="C121" t="n">
+      <c r="D121" t="n">
         <v>26857</v>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="E121" t="inlineStr">
         <is>
           <t>りお</t>
         </is>
       </c>
-      <c r="E121" t="n">
-        <v>1</v>
-      </c>
-      <c r="F121" t="inlineStr">
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" t="inlineStr">
         <is>
           <t>りお、めい、まい</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="H121" t="inlineStr">
         <is>
           <t>しごおわ</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -9001,31 +9607,36 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
           <t>01:35:32</t>
         </is>
       </c>
-      <c r="C122" t="n">
+      <c r="D122" t="n">
         <v>26857</v>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="E122" t="inlineStr">
         <is>
           <t>めい</t>
         </is>
       </c>
-      <c r="E122" t="n">
-        <v>1</v>
-      </c>
-      <c r="F122" t="inlineStr">
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" t="inlineStr">
         <is>
           <t>りお、めい、まい</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="H122" t="inlineStr">
         <is>
           <t>しごおわ</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="I122" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -9039,31 +9650,36 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
           <t>01:35:32</t>
         </is>
       </c>
-      <c r="C123" t="n">
+      <c r="D123" t="n">
         <v>26857</v>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="E123" t="inlineStr">
         <is>
           <t>まい</t>
         </is>
       </c>
-      <c r="E123" t="n">
+      <c r="F123" t="n">
         <v>2</v>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>りお、めい、まい</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="H123" t="inlineStr">
         <is>
           <t>しごおわ</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="I123" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -9077,31 +9693,36 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
           <t>02:19:37</t>
         </is>
       </c>
-      <c r="C124" t="n">
+      <c r="D124" t="n">
         <v>26859</v>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>だいご</t>
         </is>
       </c>
-      <c r="E124" t="n">
-        <v>1</v>
-      </c>
-      <c r="F124" t="inlineStr">
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="inlineStr">
         <is>
           <t>だいご</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>よばれて</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="I124" t="inlineStr">
         <is>
           <t>きちゃよ</t>
         </is>
@@ -9115,31 +9736,36 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
           <t>02:59:37</t>
         </is>
       </c>
-      <c r="C125" t="n">
+      <c r="D125" t="n">
         <v>26861</v>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>ザッキー</t>
         </is>
       </c>
-      <c r="E125" t="n">
-        <v>1</v>
-      </c>
-      <c r="F125" t="inlineStr">
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" t="inlineStr">
         <is>
           <t>ザッキー、よっしー</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>初めて</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="I125" t="inlineStr">
         <is>
           <t>きました♪</t>
         </is>
@@ -9153,31 +9779,36 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
           <t>02:59:37</t>
         </is>
       </c>
-      <c r="C126" t="n">
+      <c r="D126" t="n">
         <v>26861</v>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="E126" t="inlineStr">
         <is>
           <t>よっしー</t>
         </is>
       </c>
-      <c r="E126" t="n">
-        <v>1</v>
-      </c>
-      <c r="F126" t="inlineStr">
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" t="inlineStr">
         <is>
           <t>ザッキー、よっしー</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="H126" t="inlineStr">
         <is>
           <t>初めて</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="I126" t="inlineStr">
         <is>
           <t>きました♪</t>
         </is>
@@ -9191,31 +9822,36 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
           <t>18:51:45</t>
         </is>
       </c>
-      <c r="C127" t="n">
+      <c r="D127" t="n">
         <v>26865</v>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>おじきち</t>
         </is>
       </c>
-      <c r="E127" t="n">
-        <v>1</v>
-      </c>
-      <c r="F127" t="inlineStr">
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" t="inlineStr">
         <is>
           <t>おじきち</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="I127" t="inlineStr">
         <is>
           <t>きたよ！</t>
         </is>
@@ -9229,31 +9865,36 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
           <t>18:57:32</t>
         </is>
       </c>
-      <c r="C128" t="n">
+      <c r="D128" t="n">
         <v>26867</v>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>まろ</t>
         </is>
       </c>
-      <c r="E128" t="n">
-        <v>1</v>
-      </c>
-      <c r="F128" t="inlineStr">
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" t="inlineStr">
         <is>
           <t>まろ、おとは</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="H128" t="inlineStr">
         <is>
           <t>はやめに</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="I128" t="inlineStr">
         <is>
           <t>きたよ</t>
         </is>
@@ -9267,31 +9908,36 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
           <t>18:57:32</t>
         </is>
       </c>
-      <c r="C129" t="n">
+      <c r="D129" t="n">
         <v>26867</v>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>おとは</t>
         </is>
       </c>
-      <c r="E129" t="n">
+      <c r="F129" t="n">
         <v>2</v>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>まろ、おとは</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>はやめに</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t>きたよ</t>
         </is>
@@ -9305,31 +9951,36 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
           <t>19:28:11</t>
         </is>
       </c>
-      <c r="C130" t="n">
+      <c r="D130" t="n">
         <v>26869</v>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>たつや</t>
         </is>
       </c>
-      <c r="E130" t="n">
-        <v>1</v>
-      </c>
-      <c r="F130" t="inlineStr">
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="inlineStr">
         <is>
           <t>たつや</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="I130" t="inlineStr">
         <is>
           <t>きたｚ</t>
         </is>
@@ -9343,31 +9994,36 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
           <t>19:28:38</t>
         </is>
       </c>
-      <c r="C131" t="n">
+      <c r="D131" t="n">
         <v>26870</v>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E131" t="n">
-        <v>1</v>
-      </c>
-      <c r="F131" t="inlineStr">
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" t="inlineStr">
         <is>
           <t>S、Y</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="H131" t="inlineStr">
         <is>
           <t>２回目</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="I131" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -9381,31 +10037,36 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
           <t>19:28:38</t>
         </is>
       </c>
-      <c r="C132" t="n">
+      <c r="D132" t="n">
         <v>26870</v>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E132" t="n">
-        <v>1</v>
-      </c>
-      <c r="F132" t="inlineStr">
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" t="inlineStr">
         <is>
           <t>S、Y</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="H132" t="inlineStr">
         <is>
           <t>２回目</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="I132" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -9419,31 +10080,36 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
           <t>19:28:53</t>
         </is>
       </c>
-      <c r="C133" t="n">
+      <c r="D133" t="n">
         <v>26871</v>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="E133" t="inlineStr">
         <is>
           <t>よっち</t>
         </is>
       </c>
-      <c r="E133" t="n">
+      <c r="F133" t="n">
         <v>2</v>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>よっち</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="I133" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -9457,31 +10123,36 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
           <t>19:49:47</t>
         </is>
       </c>
-      <c r="C134" t="n">
+      <c r="D134" t="n">
         <v>26875</v>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="E134" t="n">
+      <c r="F134" t="n">
         <v>5</v>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="H134" t="inlineStr">
         <is>
           <t>きょうも</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="I134" t="inlineStr">
         <is>
           <t>いるよ</t>
         </is>
@@ -9495,31 +10166,36 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
           <t>19:50:08</t>
         </is>
       </c>
-      <c r="C135" t="n">
+      <c r="D135" t="n">
         <v>26876</v>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>まっする</t>
         </is>
       </c>
-      <c r="E135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F135" t="inlineStr">
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" t="inlineStr">
         <is>
           <t>まっする</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="I135" t="inlineStr">
         <is>
           <t>きたんご</t>
         </is>
@@ -9533,31 +10209,36 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
           <t>20:30:43</t>
         </is>
       </c>
-      <c r="C136" t="n">
+      <c r="D136" t="n">
         <v>26879</v>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="E136" t="inlineStr">
         <is>
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E136" t="n">
+      <c r="F136" t="n">
         <v>4</v>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t>ひがん</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="H136" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
+      <c r="I136" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -9571,31 +10252,36 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
           <t>20:46:17</t>
         </is>
       </c>
-      <c r="C137" t="n">
+      <c r="D137" t="n">
         <v>26881</v>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="E137" t="inlineStr">
         <is>
           <t>まいなちゅ</t>
         </is>
       </c>
-      <c r="E137" t="n">
-        <v>1</v>
-      </c>
-      <c r="F137" t="inlineStr">
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" t="inlineStr">
         <is>
           <t>まいなちゅ、えぬ</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="H137" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="I137" t="inlineStr">
         <is>
           <t>きちゃ</t>
         </is>
@@ -9609,31 +10295,36 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
           <t>20:46:17</t>
         </is>
       </c>
-      <c r="C138" t="n">
+      <c r="D138" t="n">
         <v>26881</v>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="E138" t="inlineStr">
         <is>
           <t>えぬ</t>
         </is>
       </c>
-      <c r="E138" t="n">
-        <v>1</v>
-      </c>
-      <c r="F138" t="inlineStr">
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" t="inlineStr">
         <is>
           <t>まいなちゅ、えぬ</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="H138" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
+      <c r="I138" t="inlineStr">
         <is>
           <t>きちゃ</t>
         </is>
@@ -9647,31 +10338,36 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
           <t>20:46:44</t>
         </is>
       </c>
-      <c r="C139" t="n">
+      <c r="D139" t="n">
         <v>26882</v>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>こてっちゃん</t>
         </is>
       </c>
-      <c r="E139" t="n">
-        <v>1</v>
-      </c>
-      <c r="F139" t="inlineStr">
+      <c r="F139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" t="inlineStr">
         <is>
           <t>こてっちゃん</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
+      <c r="H139" t="inlineStr">
         <is>
           <t>ひさびさ土曜に</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
+      <c r="I139" t="inlineStr">
         <is>
           <t>きたよ！</t>
         </is>
@@ -9685,31 +10381,36 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
           <t>21:38:55</t>
         </is>
       </c>
-      <c r="C140" t="n">
+      <c r="D140" t="n">
         <v>26885</v>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="E140" t="inlineStr">
         <is>
           <t>みーみ</t>
         </is>
       </c>
-      <c r="E140" t="n">
-        <v>1</v>
-      </c>
-      <c r="F140" t="inlineStr">
+      <c r="F140" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" t="inlineStr">
         <is>
           <t>みーみ</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="H140" t="inlineStr">
         <is>
           <t>ひさびさ</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
+      <c r="I140" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -9723,31 +10424,36 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
           <t>22:17:43</t>
         </is>
       </c>
-      <c r="C141" t="n">
+      <c r="D141" t="n">
         <v>26887</v>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>あっくん</t>
         </is>
       </c>
-      <c r="E141" t="n">
-        <v>1</v>
-      </c>
-      <c r="F141" t="inlineStr">
+      <c r="F141" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" t="inlineStr">
         <is>
           <t>あっくん、まりん</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="H141" t="inlineStr">
         <is>
           <t>ひさしぶり</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="I141" t="inlineStr">
         <is>
           <t>きました♪</t>
         </is>
@@ -9761,31 +10467,36 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
           <t>22:17:43</t>
         </is>
       </c>
-      <c r="C142" t="n">
+      <c r="D142" t="n">
         <v>26887</v>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="E142" t="inlineStr">
         <is>
           <t>まりん</t>
         </is>
       </c>
-      <c r="E142" t="n">
-        <v>1</v>
-      </c>
-      <c r="F142" t="inlineStr">
+      <c r="F142" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" t="inlineStr">
         <is>
           <t>あっくん、まりん</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="H142" t="inlineStr">
         <is>
           <t>ひさしぶり</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="I142" t="inlineStr">
         <is>
           <t>きました♪</t>
         </is>
@@ -9799,31 +10510,36 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
           <t>22:48:19</t>
         </is>
       </c>
-      <c r="C143" t="n">
+      <c r="D143" t="n">
         <v>26889</v>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="E143" t="n">
-        <v>1</v>
-      </c>
-      <c r="F143" t="inlineStr">
+      <c r="F143" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>いま</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="I143" t="inlineStr">
         <is>
           <t>お土産持ってきた！</t>
         </is>
@@ -9837,31 +10553,36 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
           <t>23:09:30</t>
         </is>
       </c>
-      <c r="C144" t="n">
+      <c r="D144" t="n">
         <v>26891</v>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>NMGK</t>
         </is>
       </c>
-      <c r="E144" t="n">
-        <v>1</v>
-      </c>
-      <c r="F144" t="inlineStr">
+      <c r="F144" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" t="inlineStr">
         <is>
           <t>NMGK、彩</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="H144" t="inlineStr">
         <is>
           <t>二人で</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
+      <c r="I144" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -9875,31 +10596,36 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
           <t>23:09:30</t>
         </is>
       </c>
-      <c r="C145" t="n">
+      <c r="D145" t="n">
         <v>26891</v>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="E145" t="inlineStr">
         <is>
           <t>彩</t>
         </is>
       </c>
-      <c r="E145" t="n">
-        <v>1</v>
-      </c>
-      <c r="F145" t="inlineStr">
+      <c r="F145" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" t="inlineStr">
         <is>
           <t>NMGK、彩</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
+      <c r="H145" t="inlineStr">
         <is>
           <t>二人で</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
+      <c r="I145" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -9913,31 +10639,36 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
           <t>23:14:42</t>
         </is>
       </c>
-      <c r="C146" t="n">
+      <c r="D146" t="n">
         <v>26893</v>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="E146" t="inlineStr">
         <is>
           <t>だいさく</t>
         </is>
       </c>
-      <c r="E146" t="n">
-        <v>1</v>
-      </c>
-      <c r="F146" t="inlineStr">
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="inlineStr">
         <is>
           <t>だいさく、たくや</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="H146" t="inlineStr">
         <is>
           <t>今日は</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
+      <c r="I146" t="inlineStr">
         <is>
           <t>ふたりで！</t>
         </is>
@@ -9951,31 +10682,36 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
           <t>23:14:42</t>
         </is>
       </c>
-      <c r="C147" t="n">
+      <c r="D147" t="n">
         <v>26893</v>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="E147" t="inlineStr">
         <is>
           <t>たくや</t>
         </is>
       </c>
-      <c r="E147" t="n">
-        <v>1</v>
-      </c>
-      <c r="F147" t="inlineStr">
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="inlineStr">
         <is>
           <t>だいさく、たくや</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="H147" t="inlineStr">
         <is>
           <t>今日は</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="I147" t="inlineStr">
         <is>
           <t>ふたりで！</t>
         </is>
@@ -9989,31 +10725,36 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
           <t>00:00:10</t>
         </is>
       </c>
-      <c r="C148" t="n">
+      <c r="D148" t="n">
         <v>26895</v>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="E148" t="inlineStr">
         <is>
           <t>ましゅ</t>
         </is>
       </c>
-      <c r="E148" t="n">
+      <c r="F148" t="n">
         <v>2</v>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t>ましゅ、きむ、どえむちゃん</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="H148" t="inlineStr">
         <is>
           <t>三人で</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
+      <c r="I148" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -10027,31 +10768,36 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
           <t>00:00:10</t>
         </is>
       </c>
-      <c r="C149" t="n">
+      <c r="D149" t="n">
         <v>26895</v>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="E149" t="inlineStr">
         <is>
           <t>きむ</t>
         </is>
       </c>
-      <c r="E149" t="n">
+      <c r="F149" t="n">
         <v>2</v>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t>ましゅ、きむ、どえむちゃん</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="H149" t="inlineStr">
         <is>
           <t>三人で</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
+      <c r="I149" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -10065,31 +10811,36 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
           <t>00:00:10</t>
         </is>
       </c>
-      <c r="C150" t="n">
+      <c r="D150" t="n">
         <v>26895</v>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="E150" t="inlineStr">
         <is>
           <t>どえむちゃん</t>
         </is>
       </c>
-      <c r="E150" t="n">
-        <v>1</v>
-      </c>
-      <c r="F150" t="inlineStr">
+      <c r="F150" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" t="inlineStr">
         <is>
           <t>ましゅ、きむ、どえむちゃん</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="H150" t="inlineStr">
         <is>
           <t>三人で</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
+      <c r="I150" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -10103,31 +10854,36 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
           <t>00:42:06</t>
         </is>
       </c>
-      <c r="C151" t="n">
+      <c r="D151" t="n">
         <v>26897</v>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>女子三人衆</t>
         </is>
       </c>
-      <c r="E151" t="n">
-        <v>1</v>
-      </c>
-      <c r="F151" t="inlineStr">
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" t="inlineStr">
         <is>
           <t>女子三人衆</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
+      <c r="H151" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
+      <c r="I151" t="inlineStr">
         <is>
           <t>きました！！</t>
         </is>
@@ -10141,31 +10897,36 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
           <t>00:42:29</t>
         </is>
       </c>
-      <c r="C152" t="n">
+      <c r="D152" t="n">
         <v>26898</v>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="E152" t="inlineStr">
         <is>
           <t>かず</t>
         </is>
       </c>
-      <c r="E152" t="n">
-        <v>1</v>
-      </c>
-      <c r="F152" t="inlineStr">
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" t="inlineStr">
         <is>
           <t>かず、のんのん</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
+      <c r="H152" t="inlineStr">
         <is>
           <t>さっき</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
+      <c r="I152" t="inlineStr">
         <is>
           <t>きたよ</t>
         </is>
@@ -10179,31 +10940,36 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
           <t>00:42:29</t>
         </is>
       </c>
-      <c r="C153" t="n">
+      <c r="D153" t="n">
         <v>26898</v>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="E153" t="inlineStr">
         <is>
           <t>のんのん</t>
         </is>
       </c>
-      <c r="E153" t="n">
+      <c r="F153" t="n">
         <v>2</v>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="G153" t="inlineStr">
         <is>
           <t>かず、のんのん</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="H153" t="inlineStr">
         <is>
           <t>さっき</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
+      <c r="I153" t="inlineStr">
         <is>
           <t>きたよ</t>
         </is>
@@ -10217,31 +10983,36 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
           <t>00:42:42</t>
         </is>
       </c>
-      <c r="C154" t="n">
+      <c r="D154" t="n">
         <v>26899</v>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="E154" t="inlineStr">
         <is>
           <t>けん</t>
         </is>
       </c>
-      <c r="E154" t="n">
-        <v>1</v>
-      </c>
-      <c r="F154" t="inlineStr">
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" t="inlineStr">
         <is>
           <t>けん</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="H154" t="inlineStr">
         <is>
           <t>初めて</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
+      <c r="I154" t="inlineStr">
         <is>
           <t>きました</t>
         </is>
@@ -10255,31 +11026,36 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
           <t>01:04:50</t>
         </is>
       </c>
-      <c r="C155" t="n">
+      <c r="D155" t="n">
         <v>26903</v>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="E155" t="inlineStr">
         <is>
           <t>れー</t>
         </is>
       </c>
-      <c r="E155" t="n">
-        <v>1</v>
-      </c>
-      <c r="F155" t="inlineStr">
+      <c r="F155" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" t="inlineStr">
         <is>
           <t>れー、ぷらぐいん</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
+      <c r="H155" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
+      <c r="I155" t="inlineStr">
         <is>
           <t>きまいた</t>
         </is>
@@ -10293,31 +11069,36 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
           <t>01:04:50</t>
         </is>
       </c>
-      <c r="C156" t="n">
+      <c r="D156" t="n">
         <v>26903</v>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="E156" t="inlineStr">
         <is>
           <t>ぷらぐいん</t>
         </is>
       </c>
-      <c r="E156" t="n">
-        <v>1</v>
-      </c>
-      <c r="F156" t="inlineStr">
+      <c r="F156" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" t="inlineStr">
         <is>
           <t>れー、ぷらぐいん</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="H156" t="inlineStr">
         <is>
           <t>今</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="I156" t="inlineStr">
         <is>
           <t>きまいた</t>
         </is>
@@ -10331,31 +11112,36 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
           <t>01:31:58</t>
         </is>
       </c>
-      <c r="C157" t="n">
+      <c r="D157" t="n">
         <v>26905</v>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="E157" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="E157" t="n">
-        <v>1</v>
-      </c>
-      <c r="F157" t="inlineStr">
+      <c r="F157" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" t="inlineStr">
         <is>
           <t>K、N</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
+      <c r="H157" t="inlineStr">
         <is>
           <t>今日も</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
+      <c r="I157" t="inlineStr">
         <is>
           <t>きたよ！</t>
         </is>
@@ -10369,31 +11155,36 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
           <t>01:31:58</t>
         </is>
       </c>
-      <c r="C158" t="n">
+      <c r="D158" t="n">
         <v>26905</v>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="E158" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E158" t="n">
+      <c r="F158" t="n">
         <v>2</v>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="G158" t="inlineStr">
         <is>
           <t>K、N</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
+      <c r="H158" t="inlineStr">
         <is>
           <t>今日も</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
+      <c r="I158" t="inlineStr">
         <is>
           <t>きたよ！</t>
         </is>
@@ -10407,31 +11198,36 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
           <t>01:32:06</t>
         </is>
       </c>
-      <c r="C159" t="n">
+      <c r="D159" t="n">
         <v>26906</v>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="E159" t="inlineStr">
         <is>
           <t>ぺぺ</t>
         </is>
       </c>
-      <c r="E159" t="n">
-        <v>1</v>
-      </c>
-      <c r="F159" t="inlineStr">
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" t="inlineStr">
         <is>
           <t>ぺぺ</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="H159" t="inlineStr">
         <is>
           <t>このあといきます！</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
+      <c r="I159" t="inlineStr">
         <is>
           <t>初めまして、よろしくお願いします！</t>
         </is>
@@ -10445,31 +11241,36 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
           <t>01:32:29</t>
         </is>
       </c>
-      <c r="C160" t="n">
+      <c r="D160" t="n">
         <v>26907</v>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="E160" t="inlineStr">
         <is>
           <t>みずき</t>
         </is>
       </c>
-      <c r="E160" t="n">
-        <v>1</v>
-      </c>
-      <c r="F160" t="inlineStr">
+      <c r="F160" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" t="inlineStr">
         <is>
           <t>みずき、りく、りん</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
+      <c r="H160" t="inlineStr">
         <is>
           <t>女子三人</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
+      <c r="I160" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -10483,31 +11284,36 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
           <t>01:32:29</t>
         </is>
       </c>
-      <c r="C161" t="n">
+      <c r="D161" t="n">
         <v>26907</v>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>りく</t>
         </is>
       </c>
-      <c r="E161" t="n">
-        <v>1</v>
-      </c>
-      <c r="F161" t="inlineStr">
+      <c r="F161" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" t="inlineStr">
         <is>
           <t>みずき、りく、りん</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="H161" t="inlineStr">
         <is>
           <t>女子三人</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
+      <c r="I161" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -10521,31 +11327,36 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
           <t>01:32:29</t>
         </is>
       </c>
-      <c r="C162" t="n">
+      <c r="D162" t="n">
         <v>26907</v>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="E162" t="inlineStr">
         <is>
           <t>りん</t>
         </is>
       </c>
-      <c r="E162" t="n">
+      <c r="F162" t="n">
         <v>2</v>
       </c>
-      <c r="F162" t="inlineStr">
+      <c r="G162" t="inlineStr">
         <is>
           <t>みずき、りく、りん</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
+      <c r="H162" t="inlineStr">
         <is>
           <t>女子三人</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
+      <c r="I162" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -10559,31 +11370,36 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
           <t>02:19:30</t>
         </is>
       </c>
-      <c r="C163" t="n">
+      <c r="D163" t="n">
         <v>26911</v>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="E163" t="inlineStr">
         <is>
           <t>しん</t>
         </is>
       </c>
-      <c r="E163" t="n">
-        <v>1</v>
-      </c>
-      <c r="F163" t="inlineStr">
+      <c r="F163" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" t="inlineStr">
         <is>
           <t>しん</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="H163" t="inlineStr">
         <is>
           <t>いま</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="I163" t="inlineStr">
         <is>
           <t>きたんご</t>
         </is>
@@ -13388,4 +14204,126 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>曜日</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>投稿件数</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>延べ来店人数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>21</v>
+      </c>
+      <c r="C7" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>14</v>
+      </c>
+      <c r="C8" t="n">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -11,6 +11,9 @@
     <sheet name="来店履歴" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="来店回数" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="曜日別" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="時間帯別" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="月次推移" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="同伴ネットワーク" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14326,4 +14329,1165 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>時間帯</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>投稿件数</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>延べ来店人数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>00時台</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>01時台</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>02時台</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>03時台</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>04時台</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>05時台</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>06時台</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>07時台</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>08時台</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>09時台</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10時台</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>11時台</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12時台</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>13時台</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>14時台</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15時台</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>16時台</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>17時台</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>18時台</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>19時台</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20時台</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>21時台</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>22時台</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>14</v>
+      </c>
+      <c r="C24" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>23時台</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" t="n">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>投稿件数</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>延べ来店人数</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ユニーク人数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>120</v>
+      </c>
+      <c r="C2" t="n">
+        <v>162</v>
+      </c>
+      <c r="D2" t="n">
+        <v>138</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>人物A</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>人物B</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>同伴回数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NMGK</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T山</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ふくてゃ</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>zin</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>あゆ</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>あっくん</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>まりん</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>あにー</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ゆり</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>あにー</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>りえ</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>あや</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>のり</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>いぬ</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ももたろ</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>いぬ</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>マッチョ</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>えぬ</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>まいなちゅ</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>おとは</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>まろ</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>かず</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>のんのん</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>かずき</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>フジ</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>かな</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>よしやん</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>きむ</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>どえむちゃん</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>きむ</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>きむ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>りさ</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>げん</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ともち</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ごん</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ぶりちゃん</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>たかやま</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>りりこ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>たく</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>りゅう</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>たくや</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>だいさく</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ちぇちぇ</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ゆず</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>どえむちゃん</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ひろとも</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ゆうき</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ぷらぐいん</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>れー</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>まい</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>めい</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>まい</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>りお</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>絶</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>みずき</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>りく</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>みずき</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>みれい</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>キム</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>めい</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>りお</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ももたろ</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>マッチョ</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ゆうたん</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>カモリ</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ゆり</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>りえ</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>よっしー</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ザッキー</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>りく</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>アキ</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>コオリ</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4380,6 +4380,570 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>26915</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>19:06:44</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>たいせい</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2回目</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>きたよ</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>26916</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>19:07:28</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>オープン凸</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>きた</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>26919</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>19:31:15</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>くま、まーくん、とおちゃん</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>3人で</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>26921</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>19:46:02</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>みかん</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>もうちょっと</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>あと少しで行きます</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>26922</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>20:04:46</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>なお</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>きたよ</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>26923</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>20:05:25</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ナカヤマヤ</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>ずっと</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>気になってて</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>26927</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>20:13:52</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>しーたん</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>今から行きます</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>お願い致します</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>26929</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>20:40:35</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>みなつちん</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>後半に入って仕事終わってから</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>いぐぅぅ</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>26931</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>21:13:01</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>フリーで</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>26933</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>21:53:50</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>キムと奴隷</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>来店します</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>26937</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>22:25:24</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>すーたく、ことり</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>きたでー</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>26939</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>22:47:38</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>マイナス</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>きたった</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>26941</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>23:38:44</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>すず</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>横浜から</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>お初</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>26942</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>00:46:02</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ゆきんこ、いぬ、てっちゃん、ながとも</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>きたぜ</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>26945</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>01:02:48</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ゆうくん</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>呼ばれて</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>26947</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>01:21:44</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>みなっち</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>ただいま</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>参上</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>26949</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>04:07:48</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>新妻マゾヒストのミコト</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの月曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>本日8月17日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+新妻マゾヒストのミコト
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>img20260817040748.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4391,7 +4955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I163"/>
+  <dimension ref="A1:I185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11405,6 +11969,952 @@
       <c r="I163" t="inlineStr">
         <is>
           <t>きたんご</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>19:06:44</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>26915</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>たいせい</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>2</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>たいせい</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2回目</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>きたよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>19:07:28</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>26916</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>5</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>オープン凸</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>きた</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>19:31:15</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>26919</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>くま</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>くま、まーくん、とおちゃん</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>3人で</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>19:31:15</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>26919</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>まーくん</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>くま、まーくん、とおちゃん</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>3人で</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>19:31:15</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>26919</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>とおちゃん</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>1</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>くま、まーくん、とおちゃん</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>3人で</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>19:46:02</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>26921</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>みかん</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>みかん</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>もうちょっと</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>あと少しで行きます</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>20:04:46</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>26922</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>なお</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>2</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>なお</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>きたよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>20:05:25</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>26923</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>ナカヤマヤ</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>ナカヤマヤ</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>ずっと</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>気になってて</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>20:13:52</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>26927</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>しーたん</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>しーたん</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>今から行きます</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>お願い致します</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>20:40:35</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>26929</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>みなつちん</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>1</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>みなつちん</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>後半に入って仕事終わってから</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>いぐぅぅ</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>21:13:01</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>26931</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>3</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>フリーで</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>21:53:50</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>26933</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>キムと奴隷</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>キムと奴隷</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>来店します</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>22:25:24</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>26937</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>すーたく</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>すーたく、ことり</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>きたでー</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>22:25:24</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>26937</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>ことり</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>すーたく、ことり</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>きたでー</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>22:47:38</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>26939</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>マイナス</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>マイナス</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>きたった</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>23:38:44</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>26941</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>すず</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>すず</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>横浜から</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>お初</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>00:46:02</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>26942</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>ゆきんこ</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>ゆきんこ、いぬ、てっちゃん、ながとも</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>きたぜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>00:46:02</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>26942</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>いぬ</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>2</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>ゆきんこ、いぬ、てっちゃん、ながとも</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>きたぜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>00:46:02</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>26942</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>てっちゃん</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>ゆきんこ、いぬ、てっちゃん、ながとも</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>きたぜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>00:46:02</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>26942</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>ながとも</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>ゆきんこ、いぬ、てっちゃん、ながとも</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>きたぜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>01:02:48</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>26945</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>ゆうくん</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>ゆうくん</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>呼ばれて</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>01:21:44</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>26947</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>みなっち</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>2</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>みなっち</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>ただいま</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>参上</t>
         </is>
       </c>
     </row>
@@ -11419,7 +12929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D139"/>
+  <dimension ref="A1:D155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11447,7 +12957,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ゆずき</t>
+          <t>ひがん</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -11455,27 +12965,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ひがん</t>
+          <t>ゆずき</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -11507,15 +13017,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -11527,7 +13037,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -11535,19 +13045,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -11555,19 +13065,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -11575,19 +13085,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -11595,19 +13105,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -11615,19 +13125,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>たいせい</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -11635,7 +13145,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -11647,7 +13157,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -11655,19 +13165,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -11675,19 +13185,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>よっち</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -11707,7 +13217,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -11715,7 +13225,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11727,7 +13237,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>タツヤ</t>
+          <t>みなっち</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -11735,19 +13245,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -11755,19 +13265,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>マッスル</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -11775,99 +13285,99 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>よっち</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>タツヤ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>マッスル</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -11887,7 +13397,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -11895,19 +13405,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -11915,19 +13425,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -11947,7 +13457,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -11955,19 +13465,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -11975,19 +13485,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -11995,19 +13505,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TKC</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -12015,19 +13525,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -12035,19 +13545,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -12067,7 +13577,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -12075,19 +13585,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>nuri</t>
+          <t>TKC</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -12095,19 +13605,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>zin</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -12115,19 +13625,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -12135,19 +13645,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -12155,19 +13665,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>nuri</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -12175,19 +13685,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>zin</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -12195,19 +13705,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>−</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -12227,7 +13737,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -12235,19 +13745,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -12255,19 +13765,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>おじきち</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -12275,19 +13785,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -12295,19 +13805,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -12315,19 +13825,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>かける</t>
+          <t>おじきち</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -12335,19 +13845,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>おちんぽベルセルク</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -12355,19 +13865,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -12375,19 +13885,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>かける</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -12395,19 +13905,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -12415,19 +13925,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -12435,19 +13945,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>けん</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -12455,19 +13965,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -12475,19 +13985,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>こてっちゃん</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -12495,19 +14005,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -12515,19 +14025,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>しゅん</t>
+          <t>けん</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -12535,19 +14045,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>しん</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -12555,19 +14065,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>こてっちゃん</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -12575,19 +14085,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>たいせい</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -12595,19 +14105,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -12627,7 +14137,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>しゅん</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -12635,19 +14145,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>しん</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -12655,19 +14165,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>しーたん</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -12675,19 +14185,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>たつや</t>
+          <t>すず</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -12695,19 +14205,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -12727,7 +14237,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>だいご</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -12735,19 +14245,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -12755,19 +14265,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -12775,19 +14285,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -12795,19 +14305,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -12815,19 +14325,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>でで</t>
+          <t>たつや</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -12835,19 +14345,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -12855,19 +14365,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>だいご</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -12875,19 +14385,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -12895,19 +14405,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -12915,19 +14425,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -12935,19 +14445,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -12955,19 +14465,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -12987,7 +14497,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>はなまる</t>
+          <t>でで</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -12995,19 +14505,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -13015,19 +14525,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -13035,19 +14545,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -13067,7 +14577,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -13075,19 +14585,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -13107,7 +14617,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -13115,19 +14625,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ぽちゃりす組</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -13135,19 +14645,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -13155,19 +14665,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>はなまる</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -13175,19 +14685,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -13195,19 +14705,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>まっする</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -13215,19 +14725,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -13235,19 +14745,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -13255,19 +14765,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -13287,7 +14797,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>みなっち</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -13295,19 +14805,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>ぽちゃりす組</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -13315,19 +14825,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -13347,7 +14857,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>まいまいん</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -13355,19 +14865,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>やえ</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -13375,19 +14885,19 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>まっする</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -13395,19 +14905,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -13415,19 +14925,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -13435,19 +14945,19 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -13455,19 +14965,19 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -13475,19 +14985,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -13495,19 +15005,19 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>よしおたん</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -13515,19 +15025,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -13535,19 +15045,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -13567,7 +15077,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -13587,7 +15097,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>やえ</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -13595,19 +15105,19 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>ゆうくん</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -13615,19 +15125,19 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -13635,19 +15145,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -13655,19 +15165,19 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -13675,19 +15185,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -13707,7 +15217,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -13715,19 +15225,19 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -13735,19 +15245,19 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>るい</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -13755,19 +15265,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>よしおたん</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -13775,19 +15285,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -13795,19 +15305,19 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -13815,19 +15325,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -13835,19 +15345,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -13855,19 +15365,19 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>カー</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -13875,19 +15385,19 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -13895,19 +15405,19 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -13915,19 +15425,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -13935,19 +15445,19 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -13955,19 +15465,19 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -13975,19 +15485,19 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -13995,19 +15505,19 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>るい</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -14015,19 +15525,19 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -14035,19 +15545,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -14055,19 +15565,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>マナティ</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -14075,19 +15585,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>マロ</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -14095,19 +15605,19 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -14115,19 +15625,19 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>カー</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -14147,7 +15657,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -14155,19 +15665,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -14175,30 +15685,350 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>コオリ</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>コテッチャン</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ザッキー</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ダイチ</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>テクノとポチ</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ナカヤマヤ</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>フジ</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ボンタ</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>マイナス</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>マッチョ</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>マナティ</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>マロ</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>女子三人衆</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
           <t>絶</t>
         </is>
       </c>
-      <c r="B139" t="n">
-        <v>1</v>
-      </c>
-      <c r="C139" t="inlineStr">
+      <c r="B155" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D155" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
@@ -14242,10 +16072,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -14320,10 +16150,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -14364,10 +16194,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -14377,10 +16207,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -14611,10 +16441,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
@@ -14624,10 +16454,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -14637,10 +16467,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -14650,10 +16480,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -14663,10 +16493,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -14712,13 +16542,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="C2" t="n">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="D2" t="n">
-        <v>138</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -14732,7 +16562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14955,7 +16785,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -14970,7 +16800,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -14980,12 +16810,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -14995,12 +16825,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -15010,12 +16840,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -15025,12 +16855,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -15040,12 +16870,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -15055,12 +16885,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -15070,12 +16900,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -15085,12 +16915,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -15100,12 +16930,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -15115,12 +16945,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -15130,12 +16960,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -15145,12 +16975,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -15160,12 +16990,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -15175,12 +17005,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -15190,12 +17020,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -15205,12 +17035,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -15220,12 +17050,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -15235,12 +17065,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -15250,12 +17080,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -15265,12 +17095,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ゆずき</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -15280,12 +17110,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -15295,12 +17125,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -15310,12 +17140,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -15325,12 +17155,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -15340,12 +17170,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -15355,12 +17185,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -15370,12 +17200,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -15385,12 +17215,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -15400,12 +17230,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -15415,12 +17245,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>ゆずき</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -15430,12 +17260,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -15445,12 +17275,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -15460,12 +17290,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>絶</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -15475,15 +17305,165 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>みずき</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>りく</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>みずき</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>みれい</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>キム</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>めい</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>りお</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ももたろ</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>マッチョ</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ゆうたん</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>カモリ</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ゆり</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>りえ</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>よっしー</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ザッキー</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>りく</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>アキ</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>コオリ</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>テクノ</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>ミコト</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C60" t="n">
         <v>1</v>
       </c>
     </row>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4399,7 +4399,6 @@
           <t>たいせい</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>2回目</t>
@@ -4410,7 +4409,6 @@
           <t>きたよ</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -4431,7 +4429,6 @@
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>オープン凸</t>
@@ -4442,7 +4439,6 @@
           <t>きた</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -4463,7 +4459,6 @@
           <t>くま、まーくん、とおちゃん</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>3人で</t>
@@ -4474,7 +4469,6 @@
           <t>初めて</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -4495,7 +4489,6 @@
           <t>みかん</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>もうちょっと</t>
@@ -4506,7 +4499,6 @@
           <t>あと少しで行きます</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -4527,7 +4519,6 @@
           <t>なお</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>すこし</t>
@@ -4538,7 +4529,6 @@
           <t>きたよ</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -4559,7 +4549,6 @@
           <t>ナカヤマヤ</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>ずっと</t>
@@ -4570,7 +4559,6 @@
           <t>気になってて</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -4591,7 +4579,6 @@
           <t>しーたん</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>今から行きます</t>
@@ -4602,7 +4589,6 @@
           <t>お願い致します</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -4623,7 +4609,6 @@
           <t>みなつちん</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>後半に入って仕事終わってから</t>
@@ -4634,7 +4619,6 @@
           <t>いぐぅぅ</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -4655,7 +4639,6 @@
           <t>テクノ</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>今日は</t>
@@ -4666,7 +4649,6 @@
           <t>フリーで</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -4687,7 +4669,6 @@
           <t>キムと奴隷</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>今日も</t>
@@ -4698,7 +4679,6 @@
           <t>来店します</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -4719,7 +4699,6 @@
           <t>すーたく、ことり</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>いま</t>
@@ -4730,7 +4709,6 @@
           <t>きたでー</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -4751,7 +4729,6 @@
           <t>マイナス</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>今</t>
@@ -4762,7 +4739,6 @@
           <t>きたった</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -4783,7 +4759,6 @@
           <t>すず</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>横浜から</t>
@@ -4794,7 +4769,6 @@
           <t>お初</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -4815,7 +4789,6 @@
           <t>ゆきんこ、いぬ、てっちゃん、ながとも</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>みんなで</t>
@@ -4826,7 +4799,6 @@
           <t>きたぜ</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -4847,7 +4819,6 @@
           <t>ゆうくん</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>呼ばれて</t>
@@ -4858,7 +4829,6 @@
           <t>きたよー</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -4879,7 +4849,6 @@
           <t>みなっち</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>ただいま</t>
@@ -4890,7 +4859,6 @@
           <t>参上</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -4944,6 +4912,346 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>26951</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>19:21:57</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>まいなす</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>早めに</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>来たよー♪</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>26953</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>19:44:27</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>なお</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>長めにいますー</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>26955</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>20:02:03</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>あや</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>きたよ！</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>26956</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>20:03:40</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>たかやま</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>今日は夜まで</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>のんびりと</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>26959</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>21:07:46</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>にこちん</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>11時頃</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>目標に行きます。</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>26961</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>23:42:16</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>れいら</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>しごおわ</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>来たよー</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>26963</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>23:57:47</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>さくら</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>きましたー！</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>26964</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>23:58:16</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>zin</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>ちょい</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>26965</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>01:54:10</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>すーさん</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>来たぜ</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>26969</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>03:32:35</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>天然の100人ネキ　ねむ</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの火曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>本日8月17日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+天然の100人ネキ　ねむ
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>img20260818033235.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4955,7 +5263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I185"/>
+  <dimension ref="A1:I194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12915,6 +13223,393 @@
       <c r="I185" t="inlineStr">
         <is>
           <t>参上</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>19:21:57</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>26951</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>まいなす</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>まいなす</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>早めに</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>来たよー♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>19:44:27</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>26953</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>なお</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>3</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>なお</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>長めにいますー</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>20:02:03</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>26955</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>あや</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>2</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>あや</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>きたよ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>20:03:40</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>26956</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>たかやま</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>2</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>たかやま</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>今日は夜まで</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>のんびりと</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>21:07:46</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>26959</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>にこちん</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>にこちん</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>11時頃</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>目標に行きます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>23:42:16</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>26961</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>れいら</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>れいら</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>しごおわ</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>来たよー</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>23:57:47</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>26963</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>さくら</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>さくら</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>きましたー！</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>23:58:16</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>26964</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>zin</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>2</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>zin</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>ちょい</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>01:54:10</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>26965</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>すーさん</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>すーさん</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>来たぜ</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>遊びに</t>
         </is>
       </c>
     </row>
@@ -12929,7 +13624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D155"/>
+  <dimension ref="A1:D160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13017,7 +13712,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -13025,27 +13720,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -13057,7 +13752,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -13065,19 +13760,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>zin</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -13085,7 +13780,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -13097,7 +13792,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -13105,19 +13800,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -13130,14 +13825,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>たいせい</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -13145,19 +13840,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -13165,19 +13860,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -13197,7 +13892,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>たいせい</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -13210,14 +13905,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -13225,19 +13920,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>みなっち</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -13245,19 +13940,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -13265,19 +13960,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -13285,19 +13980,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>よっち</t>
+          <t>みなっち</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -13310,14 +14005,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -13330,14 +14025,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>タツヤ</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -13345,19 +14040,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>マッスル</t>
+          <t>よっち</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -13365,43 +14060,43 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>タツヤ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -13410,34 +14105,34 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>マッスル</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -13445,19 +14140,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -13465,19 +14160,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -13485,19 +14180,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -13505,19 +14200,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -13525,19 +14220,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -13545,19 +14240,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -13565,19 +14260,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -13585,19 +14280,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TKC</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -13605,19 +14300,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -13625,19 +14320,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -13657,7 +14352,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>TKC</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -13677,7 +14372,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>nuri</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -13685,19 +14380,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>zin</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -13705,19 +14400,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -13725,19 +14420,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>nuri</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -13745,19 +14440,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>−</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -13765,19 +14460,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -13785,19 +14480,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -13805,19 +14500,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -13825,19 +14520,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>おじきち</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -13857,7 +14552,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
+          <t>おじきち</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -13865,19 +14560,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>おちんぽベルセルク</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -13897,7 +14592,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>かける</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -13905,19 +14600,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>かける</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -13925,19 +14620,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -13945,19 +14640,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -13977,7 +14672,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -13985,19 +14680,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -14005,19 +14700,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -14025,19 +14720,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>けん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -14057,7 +14752,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>けん</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -14065,19 +14760,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>こてっちゃん</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -14085,19 +14780,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>こてっちゃん</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -14105,19 +14800,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -14125,19 +14820,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>しゅん</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -14157,7 +14852,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>しん</t>
+          <t>さくら</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -14165,19 +14860,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>しーたん</t>
+          <t>しゅん</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -14185,19 +14880,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>すず</t>
+          <t>しん</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -14217,7 +14912,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>しーたん</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -14225,19 +14920,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>すず</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -14257,7 +14952,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -14265,19 +14960,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -14285,19 +14980,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -14305,19 +15000,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -14325,19 +15020,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>たつや</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -14345,19 +15040,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -14365,19 +15060,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>だいご</t>
+          <t>たつや</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -14397,7 +15092,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -14405,19 +15100,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>だいご</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -14425,19 +15120,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -14445,19 +15140,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -14465,19 +15160,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -14485,19 +15180,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>でで</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -14505,19 +15200,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -14525,19 +15220,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>でで</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -14545,19 +15240,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -14565,19 +15260,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -14585,19 +15280,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -14605,19 +15300,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -14625,19 +15320,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -14645,19 +15340,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -14665,19 +15360,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>はなまる</t>
+          <t>にこちん</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -14685,19 +15380,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -14705,19 +15400,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -14725,19 +15420,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>はなまる</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -14745,19 +15440,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -14765,19 +15460,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -14785,19 +15480,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -14805,19 +15500,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ぽちゃりす組</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -14825,19 +15520,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -14845,19 +15540,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -14865,19 +15560,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>ぽちゃりす組</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -14897,7 +15592,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>まっする</t>
+          <t>まいなす</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -14905,19 +15600,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -14937,7 +15632,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>まいまいん</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -14945,19 +15640,19 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -14965,19 +15660,19 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>みかん</t>
+          <t>まっする</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -14985,19 +15680,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -15005,19 +15700,19 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>みなつちん</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -15025,19 +15720,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -15045,19 +15740,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -15065,19 +15760,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -15085,19 +15780,19 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>やえ</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -15105,19 +15800,19 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ゆうくん</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -15125,19 +15820,19 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -15145,19 +15840,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -15165,19 +15860,19 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>やえ</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -15185,19 +15880,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>ゆうくん</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -15205,19 +15900,19 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -15225,19 +15920,19 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -15245,19 +15940,19 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -15265,19 +15960,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>よしおたん</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -15285,19 +15980,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -15317,7 +16012,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -15325,19 +16020,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -15357,7 +16052,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>よしおたん</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -15365,19 +16060,19 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -15385,19 +16080,19 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -15405,19 +16100,19 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -15425,19 +16120,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -15445,19 +16140,19 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -15465,19 +16160,19 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -15485,19 +16180,19 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -15517,7 +16212,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>るい</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -15525,19 +16220,19 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -15545,19 +16240,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -15565,19 +16260,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -15597,7 +16292,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>るい</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -15617,7 +16312,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>れいら</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -15625,19 +16320,19 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>カー</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -15645,19 +16340,19 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -15665,19 +16360,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -15685,19 +16380,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -15705,19 +16400,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -15737,7 +16432,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>カー</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -15745,19 +16440,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -15765,19 +16460,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -15785,19 +16480,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -15805,19 +16500,19 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>コテッチャン</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -15825,19 +16520,19 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -15845,19 +16540,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>マイナス</t>
+          <t>ダイチ</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -15865,19 +16560,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>テクノとポチ</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -15885,19 +16580,19 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>マナティ</t>
+          <t>ナカヤマヤ</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -15905,19 +16600,19 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>マロ</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -15925,19 +16620,19 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>ボンタ</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -15945,19 +16640,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>マイナス</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -15965,19 +16660,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -15985,19 +16680,19 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>マナティ</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -16005,30 +16700,130 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
+          <t>マロ</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>女子三人衆</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
           <t>絶</t>
         </is>
       </c>
-      <c r="B155" t="n">
-        <v>1</v>
-      </c>
-      <c r="C155" t="inlineStr">
+      <c r="B160" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
@@ -16072,10 +16867,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -16085,10 +16880,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -16207,10 +17002,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -16441,10 +17236,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C21" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22">
@@ -16454,10 +17249,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
@@ -16467,10 +17262,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -16493,10 +17288,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -16542,13 +17337,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C2" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="D2" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4931,7 +4931,6 @@
           <t>まいなす</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>早めに</t>
@@ -4942,7 +4941,6 @@
           <t>来たよー♪</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -4963,7 +4961,6 @@
           <t>なお</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>今日は</t>
@@ -4974,7 +4971,6 @@
           <t>長めにいますー</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -4995,7 +4991,6 @@
           <t>あや</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>遊びに</t>
@@ -5006,7 +5001,6 @@
           <t>きたよ！</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -5027,7 +5021,6 @@
           <t>たかやま</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>今日は夜まで</t>
@@ -5038,7 +5031,6 @@
           <t>のんびりと</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -5059,7 +5051,6 @@
           <t>にこちん</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>11時頃</t>
@@ -5070,7 +5061,6 @@
           <t>目標に行きます。</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -5091,7 +5081,6 @@
           <t>れいら</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>しごおわ</t>
@@ -5102,7 +5091,6 @@
           <t>来たよー</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -5123,7 +5111,6 @@
           <t>さくら</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>遊びに</t>
@@ -5134,7 +5121,6 @@
           <t>きましたー！</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -5155,7 +5141,6 @@
           <t>zin</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>ちょい</t>
@@ -5166,7 +5151,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -5187,7 +5171,6 @@
           <t>すーさん</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>来たぜ</t>
@@ -5198,7 +5181,6 @@
           <t>遊びに</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -5252,6 +5234,474 @@
         </is>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>26971</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>19:06:32</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>キムと新しい奴隷ちゃん</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>今夜もっと</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>来店します</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>26973</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>19:17:35</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>しごおわ</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>来たよ！</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>26975</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>20:36:42</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>よしお</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>来たわよ</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>26979</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>20:54:08</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>コテッチャン</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>来たよ！</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>26981</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>21:04:36</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>制服見に</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>きたぜ</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>26982</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>21:05:16</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ちっち</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>火曜日</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>初</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>26986</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>21:09:36</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>zin</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>東京喰種</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>干からびる</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>26988</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>22:37:31</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>たつや</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>９が月半ぶりに</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>来ちゃった</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>26989</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>22:40:11</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>飲み終わり</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>飛んできた</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>26992</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>23:49:16</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>マサ、タカス</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2人で</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>４件目</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>26994</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>00:13:50</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ろくじ</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>朝まで</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>26996</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>01:05:08</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>まいまい、しずか</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>きたよん</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>26999</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>02:25:58</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>ましゅ、</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>27001</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>03:54:23</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>えちえち裏垢女子のモカチ</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの水曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>本日8月19日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+えちえち裏垢女子のモカチ
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>img20260819035423.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5263,7 +5713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I194"/>
+  <dimension ref="A1:I209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13610,6 +14060,651 @@
       <c r="I194" t="inlineStr">
         <is>
           <t>遊びに</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>19:06:32</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>26971</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>キムと新しい奴隷ちゃん</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>キムと新しい奴隷ちゃん</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>今夜もっと</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>来店します</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>19:17:35</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>26973</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>6</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>しごおわ</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>来たよ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>20:36:42</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>26975</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>よしお</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>よしお</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>来たわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>20:54:08</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>26979</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>コテッチャン</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>2</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>コテッチャン</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>来たよ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>21:04:36</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>26981</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>6</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>制服見に</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>きたぜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>21:05:16</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>26982</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>ちっち</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>ちっち</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>火曜日</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>初</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>21:09:36</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>26986</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>zin</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>3</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>zin</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>東京喰種</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>干からびる</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>22:37:31</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>26988</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>たつや</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>2</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>たつや</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>９が月半ぶりに</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>来ちゃった</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>22:40:11</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>26989</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>4</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>飲み終わり</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>飛んできた</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>23:49:16</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>26992</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>マサ</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>マサ、タカス</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>2人で</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>４件目</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>23:49:16</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>26992</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>タカス</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>マサ、タカス</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>2人で</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>４件目</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>00:13:50</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>26994</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>ろくじ</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>ろくじ</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>朝まで</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>01:05:08</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>26996</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>5</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>まいまい、しずか</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>きたよん</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>01:05:08</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>26996</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>しずか</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>まいまい、しずか</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>きたよん</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>02:25:58</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>26999</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>3</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>ましゅ、</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>来ました</t>
         </is>
       </c>
     </row>
@@ -13624,7 +14719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D160"/>
+  <dimension ref="A1:D167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13656,7 +14751,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13665,7 +14760,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -13676,7 +14771,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -13685,7 +14780,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -13696,7 +14791,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -13705,34 +14800,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>zin</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -13740,23 +14835,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -13765,34 +14860,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>zin</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -13800,19 +14895,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -13820,19 +14915,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -13840,19 +14935,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -13860,19 +14955,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -13880,19 +14975,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>たいせい</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -13900,7 +14995,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -13912,7 +15007,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>たいせい</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -13920,19 +15015,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -13945,14 +15040,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>たつや</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -13960,19 +15055,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -13980,7 +15075,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -13992,7 +15087,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>みなっち</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -14005,14 +15100,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>みなっち</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -14020,19 +15115,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -14040,19 +15135,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>よっち</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -14060,19 +15155,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>よっち</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -14080,19 +15175,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>タツヤ</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -14100,19 +15195,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>マッスル</t>
+          <t>コテッチャン</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -14120,59 +15215,59 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>タツヤ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>マッスル</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -14180,19 +15275,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -14200,19 +15295,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -14220,19 +15315,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -14240,19 +15335,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -14260,19 +15355,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -14280,19 +15375,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -14300,19 +15395,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -14320,19 +15415,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -14352,7 +15447,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TKC</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -14360,19 +15455,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -14380,19 +15475,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>TKC</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -14400,19 +15495,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -14420,19 +15515,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>nuri</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -14440,19 +15535,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -14460,19 +15555,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>nuri</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -14480,19 +15575,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>−</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -14500,19 +15595,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -14520,19 +15615,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -14540,19 +15635,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>おじきち</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -14560,19 +15655,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -14580,19 +15675,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>おじきち</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -14600,19 +15695,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>かける</t>
+          <t>おちんぽベルセルク</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -14620,19 +15715,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -14640,19 +15735,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>かける</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -14660,19 +15755,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -14680,19 +15775,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -14700,19 +15795,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -14720,19 +15815,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -14740,19 +15835,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>けん</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -14760,19 +15855,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -14780,19 +15875,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>こてっちゃん</t>
+          <t>けん</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -14800,19 +15895,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -14820,19 +15915,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>こてっちゃん</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -14840,19 +15935,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -14860,19 +15955,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>しゅん</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -14892,7 +15987,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>しん</t>
+          <t>さくら</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -14900,19 +15995,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>しーたん</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -14920,19 +16015,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>すず</t>
+          <t>しゅん</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -14940,19 +16035,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>しん</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -14960,19 +16055,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>しーたん</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -14980,19 +16075,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>すず</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -15012,7 +16107,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -15020,19 +16115,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -15040,19 +16135,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -15060,19 +16155,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>たつや</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -15080,19 +16175,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -15100,19 +16195,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>だいご</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -15132,7 +16227,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -15140,19 +16235,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>だいご</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -15160,19 +16255,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -15180,19 +16275,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -15200,19 +16295,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -15220,19 +16315,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>でで</t>
+          <t>ちっち</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -15240,19 +16335,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -15260,19 +16355,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -15280,19 +16375,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>でで</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -15300,19 +16395,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -15320,19 +16415,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -15352,7 +16447,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -15360,19 +16455,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>にこちん</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -15380,19 +16475,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -15400,19 +16495,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -15420,19 +16515,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>はなまる</t>
+          <t>にこちん</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -15440,19 +16535,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -15460,19 +16555,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -15480,19 +16575,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>はなまる</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -15500,19 +16595,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -15520,19 +16615,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -15540,19 +16635,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -15560,19 +16655,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ぽちゃりす組</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -15580,19 +16675,19 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>まいなす</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -15600,19 +16695,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -15620,19 +16715,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>ぽちゃりす組</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -15652,7 +16747,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>まいなす</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -15660,19 +16755,19 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>まっする</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -15692,7 +16787,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>まいまいん</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -15700,19 +16795,19 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -15720,19 +16815,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>まっする</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -15740,19 +16835,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>みかん</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -15760,19 +16855,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -15780,19 +16875,19 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>みなつちん</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -15812,7 +16907,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -15820,19 +16915,19 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -15840,19 +16935,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -15860,19 +16955,19 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>やえ</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -15880,19 +16975,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ゆうくん</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -15900,19 +16995,19 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -15932,7 +17027,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>やえ</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -15940,19 +17035,19 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ゆうくん</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -15972,7 +17067,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -15980,19 +17075,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -16000,19 +17095,19 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -16020,19 +17115,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -16040,19 +17135,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>よしおたん</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -16072,7 +17167,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -16080,19 +17175,19 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -16100,19 +17195,19 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>よしお</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -16120,19 +17215,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>よしおたん</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -16140,19 +17235,19 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -16160,19 +17255,19 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -16180,19 +17275,19 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -16200,19 +17295,19 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -16220,19 +17315,19 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -16240,19 +17335,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -16260,19 +17355,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -16292,7 +17387,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>るい</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -16300,19 +17395,19 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>れいら</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -16320,19 +17415,19 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -16340,19 +17435,19 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -16360,19 +17455,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>るい</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -16380,19 +17475,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>れいら</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -16400,19 +17495,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -16420,19 +17515,19 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>カー</t>
+          <t>ろくじ</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -16440,19 +17535,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -16460,19 +17555,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -16480,19 +17575,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -16500,19 +17595,19 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -16532,7 +17627,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>カー</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -16540,19 +17635,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -16560,19 +17655,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -16580,19 +17675,19 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -16600,19 +17695,19 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -16620,19 +17715,19 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -16640,19 +17735,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>マイナス</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -16660,19 +17755,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ダイチ</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -16680,19 +17775,19 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>マナティ</t>
+          <t>テクノとポチ</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -16712,7 +17807,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>マロ</t>
+          <t>ナカヤマヤ</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -16720,19 +17815,19 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -16740,19 +17835,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>ボンタ</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -16760,19 +17855,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>マイナス</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -16792,7 +17887,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>マサ</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -16800,30 +17895,170 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
+          <t>マッチョ</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>マナティ</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>1</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>マロ</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>女子三人衆</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>1</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
           <t>絶</t>
         </is>
       </c>
-      <c r="B160" t="n">
-        <v>1</v>
-      </c>
-      <c r="C160" t="inlineStr">
+      <c r="B167" t="n">
+        <v>1</v>
+      </c>
+      <c r="C167" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D167" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
@@ -16880,10 +18115,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -16893,10 +18128,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -16989,10 +18224,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -17002,10 +18237,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -17015,10 +18250,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -17236,10 +18471,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C21" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
@@ -17249,10 +18484,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C22" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -17262,10 +18497,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
@@ -17275,10 +18510,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
@@ -17288,10 +18523,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -17337,13 +18572,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="C2" t="n">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="D2" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -17357,7 +18592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17845,12 +19080,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -17860,12 +19095,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -17875,12 +19110,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -17890,12 +19125,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -17905,12 +19140,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -17925,7 +19160,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -17935,12 +19170,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -17950,12 +19185,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -17965,12 +19200,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -17980,12 +19215,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -17995,12 +19230,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -18010,12 +19245,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -18030,7 +19265,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -18040,12 +19275,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ゆずき</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -18060,7 +19295,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>ゆずき</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -18075,7 +19310,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -18085,12 +19320,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -18100,12 +19335,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>絶</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -18120,7 +19355,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -18130,12 +19365,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -18145,12 +19380,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -18160,12 +19395,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -18175,12 +19410,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -18190,12 +19425,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -18205,12 +19440,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -18220,12 +19455,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -18235,12 +19470,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -18250,15 +19485,45 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>アキ</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>コオリ</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>タカス</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>マサ</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>テクノ</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>ミコト</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="C62" t="n">
         <v>1</v>
       </c>
     </row>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H168"/>
+  <dimension ref="A1:H174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5253,7 +5253,6 @@
           <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>今夜もっと</t>
@@ -5264,7 +5263,6 @@
           <t>来店します</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -5285,7 +5283,6 @@
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>しごおわ</t>
@@ -5296,7 +5293,6 @@
           <t>来たよ！</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -5317,7 +5313,6 @@
           <t>よしお</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>今</t>
@@ -5328,7 +5323,6 @@
           <t>来たわよ</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -5349,7 +5343,6 @@
           <t>コテッチャン</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>今</t>
@@ -5360,7 +5353,6 @@
           <t>来たよ！</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -5381,7 +5373,6 @@
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>制服見に</t>
@@ -5392,7 +5383,6 @@
           <t>きたぜ</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -5413,7 +5403,6 @@
           <t>ちっち</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>火曜日</t>
@@ -5424,7 +5413,6 @@
           <t>初</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -5445,7 +5433,6 @@
           <t>zin</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>東京喰種</t>
@@ -5456,7 +5443,6 @@
           <t>干からびる</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -5477,7 +5463,6 @@
           <t>たつや</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>９が月半ぶりに</t>
@@ -5488,7 +5473,6 @@
           <t>来ちゃった</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -5509,7 +5493,6 @@
           <t>テクノ</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>飲み終わり</t>
@@ -5520,7 +5503,6 @@
           <t>飛んできた</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -5541,7 +5523,6 @@
           <t>マサ、タカス</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>2人で</t>
@@ -5552,7 +5533,6 @@
           <t>４件目</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -5573,7 +5553,6 @@
           <t>ろくじ</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>朝まで</t>
@@ -5584,7 +5563,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -5605,7 +5583,6 @@
           <t>まいまい、しずか</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>遊びに</t>
@@ -5616,7 +5593,6 @@
           <t>きたよん</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -5637,7 +5613,6 @@
           <t>ましゅ、</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>今日も</t>
@@ -5648,7 +5623,6 @@
           <t>来ました</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -5702,6 +5676,218 @@
         </is>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>27004</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>19:15:51</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>たかやまん、ふくてゃ</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>きたんご</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>27006</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>19:27:52</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>きちゃ</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>27008</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>22:16:45</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>みるこ</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>出張前に</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>きた！！</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>27010</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>23:16:55</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ひったん、S</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>きた！</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>27012</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>01:49:05</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>にょ</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>きちゃ</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>27014</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>07:25:23</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>ツッコミはお任せのSHIZU</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの木曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>本日8月20日の営業時間は♪
+オープン17:00！ラスト5:00なのよ☆
+担当は
+ツッコミはお任せのSHIZU
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>img20260820072523.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5713,7 +5899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I209"/>
+  <dimension ref="A1:I216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14705,6 +14891,307 @@
       <c r="I209" t="inlineStr">
         <is>
           <t>来ました</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>19:15:51</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>27004</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>たかやまん</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>1</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>たかやまん、ふくてゃ</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>きたんご</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>19:15:51</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>27004</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>ふくてゃ</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>2</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>たかやまん、ふくてゃ</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>きたんご</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>19:27:52</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>27006</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>7</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>きちゃ</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>22:16:45</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>27008</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>みるこ</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>みるこ</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>出張前に</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>きた！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>23:16:55</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>27010</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>ひったん</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>ひったん、S</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>きた！</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>23:16:55</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>27010</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>2</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>ひったん、S</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>きた！</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>01:49:05</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>27012</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>にょ</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>1</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>にょ</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>きちゃ</t>
         </is>
       </c>
     </row>
@@ -14719,7 +15206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D167"/>
+  <dimension ref="A1:D171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14747,27 +15234,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ひがん</t>
+          <t>ゆずき</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ゆずき</t>
+          <t>ひがん</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -14775,7 +15262,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -14907,7 +15394,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -14915,19 +15402,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -14935,19 +15422,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -14955,19 +15442,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -14975,19 +15462,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -14995,19 +15482,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>たいせい</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -15015,7 +15502,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -15027,7 +15514,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>たいせい</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -15035,19 +15522,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>たつや</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -15055,19 +15542,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>たつや</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -15075,19 +15562,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -15095,19 +15582,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>みなっち</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -15115,19 +15602,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -15135,19 +15622,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>みなっち</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -15155,19 +15642,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>よっち</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -15175,19 +15662,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -15195,19 +15682,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>よっち</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -15215,19 +15702,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>タツヤ</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -15235,19 +15722,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>マッスル</t>
+          <t>コテッチャン</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -15255,59 +15742,59 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>タツヤ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>マッスル</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -15315,19 +15802,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -15335,19 +15822,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -15355,19 +15842,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -15375,19 +15862,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -15395,19 +15882,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -15415,19 +15902,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -15435,19 +15922,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -15455,19 +15942,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -15487,7 +15974,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TKC</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -15495,19 +15982,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>TKC</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -15515,19 +16002,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -15535,19 +16022,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -15555,19 +16042,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>nuri</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -15575,19 +16062,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>nuri</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -15595,19 +16082,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>−</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -15615,19 +16102,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -15635,19 +16122,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -15655,19 +16142,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -15675,19 +16162,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>おじきち</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -15707,7 +16194,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
+          <t>おじきち</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -15715,19 +16202,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>おちんぽベルセルク</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -15747,7 +16234,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>かける</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -15755,19 +16242,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>かける</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -15775,19 +16262,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -15795,19 +16282,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -15827,7 +16314,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -15835,19 +16322,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -15855,19 +16342,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -15875,19 +16362,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>けん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -15907,7 +16394,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>けん</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -15915,19 +16402,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>こてっちゃん</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -15935,19 +16422,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>こてっちゃん</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -15955,19 +16442,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -15975,19 +16462,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -15995,19 +16482,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>さくら</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -16015,19 +16502,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>しゅん</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -16035,19 +16522,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>しん</t>
+          <t>しゅん</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -16055,19 +16542,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>しーたん</t>
+          <t>しん</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -16087,7 +16574,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>すず</t>
+          <t>しーたん</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -16107,7 +16594,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>すず</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -16115,19 +16602,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -16135,19 +16622,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -16155,19 +16642,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -16175,19 +16662,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -16195,19 +16682,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>たかやまん</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -16215,19 +16702,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -16235,19 +16722,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>だいご</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -16267,7 +16754,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -16275,19 +16762,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>だいご</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -16295,19 +16782,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -16315,19 +16802,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ちっち</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -16335,19 +16822,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -16355,19 +16842,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>ちっち</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -16375,19 +16862,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>でで</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -16395,19 +16882,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -16415,19 +16902,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>でで</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -16435,19 +16922,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -16455,19 +16942,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -16475,19 +16962,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -16495,19 +16982,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -16515,19 +17002,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>にこちん</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -16535,19 +17022,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -16555,19 +17042,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>にこちん</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -16575,19 +17062,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>はなまる</t>
+          <t>にょ</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -16595,19 +17082,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -16615,19 +17102,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -16635,19 +17122,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>はなまる</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -16655,19 +17142,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -16675,19 +17162,19 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -16695,19 +17182,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -16715,19 +17202,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ぽちゃりす組</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -16735,19 +17222,19 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>まいなす</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -16755,19 +17242,19 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -16775,19 +17262,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>ぽちゃりす組</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -16807,7 +17294,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>まいなす</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -16815,19 +17302,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>まっする</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -16847,7 +17334,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>まいまいん</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -16855,19 +17342,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -16875,19 +17362,19 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>まっする</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -16895,19 +17382,19 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>みかん</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -16915,19 +17402,19 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -16935,19 +17422,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>みなつちん</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -16967,7 +17454,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -16975,19 +17462,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -16995,19 +17482,19 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -17015,19 +17502,19 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>やえ</t>
+          <t>みるこ</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -17035,19 +17522,19 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ゆうくん</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -17055,19 +17542,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -17075,19 +17562,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -17095,19 +17582,19 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>やえ</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -17115,19 +17602,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>ゆうくん</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -17135,19 +17622,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -17155,19 +17642,19 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -17175,19 +17662,19 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -17195,19 +17682,19 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>よしお</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -17215,19 +17702,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>よしおたん</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -17247,7 +17734,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -17255,19 +17742,19 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -17275,19 +17762,19 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>よしお</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -17295,19 +17782,19 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>よしおたん</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -17315,19 +17802,19 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -17335,19 +17822,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -17355,19 +17842,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -17375,19 +17862,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -17395,19 +17882,19 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -17415,19 +17902,19 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -17435,19 +17922,19 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -17467,7 +17954,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>るい</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -17475,19 +17962,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>れいら</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -17495,19 +17982,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -17515,19 +18002,19 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ろくじ</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -17535,19 +18022,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>るい</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -17555,19 +18042,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>れいら</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -17575,19 +18062,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -17595,19 +18082,19 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>ろくじ</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -17615,19 +18102,19 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>カー</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -17635,19 +18122,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -17667,7 +18154,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -17675,19 +18162,19 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>キムと新しい奴隷ちゃん</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -17695,19 +18182,19 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>カー</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -17715,19 +18202,19 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -17735,19 +18222,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -17755,19 +18242,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -17775,19 +18262,19 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -17795,19 +18282,19 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -17815,19 +18302,19 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -17835,19 +18322,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>ダイチ</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -17855,19 +18342,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>マイナス</t>
+          <t>テクノとポチ</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -17875,19 +18362,19 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>ナカヤマヤ</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -17895,19 +18382,19 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -17915,19 +18402,19 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>マナティ</t>
+          <t>ボンタ</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -17935,19 +18422,19 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>マロ</t>
+          <t>マイナス</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -17955,19 +18442,19 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>マサ</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -17975,19 +18462,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -17995,19 +18482,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>マナティ</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -18015,19 +18502,19 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>マロ</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -18035,30 +18522,110 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>1</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>1</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>女子三人衆</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>1</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
           <t>絶</t>
         </is>
       </c>
-      <c r="B167" t="n">
-        <v>1</v>
-      </c>
-      <c r="C167" t="inlineStr">
+      <c r="B171" t="n">
+        <v>1</v>
+      </c>
+      <c r="C171" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D171" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
@@ -18128,10 +18695,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -18141,10 +18708,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -18237,10 +18804,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -18471,10 +19038,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C21" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
@@ -18510,10 +19077,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
@@ -18523,10 +19090,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -18572,13 +19139,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C2" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="D2" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -18592,7 +19159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18720,12 +19287,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -18735,12 +19302,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>zin</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -18750,12 +19317,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>zin</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -18765,12 +19332,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -18785,7 +19352,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -18795,12 +19362,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -18810,12 +19377,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -18830,7 +19397,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -18845,7 +19412,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -18860,7 +19427,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -18875,7 +19442,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -18885,12 +19452,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -18900,12 +19467,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -18915,12 +19482,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -18930,12 +19497,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -18945,12 +19512,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -18960,12 +19527,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -18980,7 +19547,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -18995,7 +19562,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -19005,12 +19572,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -19025,7 +19592,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -19035,12 +19602,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -19050,12 +19617,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -19065,12 +19632,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -19080,12 +19647,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -19095,12 +19662,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -19110,12 +19677,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -19125,12 +19692,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>たかやまん</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -19140,12 +19707,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -19155,12 +19722,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -19170,12 +19737,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -19185,12 +19752,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -19200,12 +19767,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -19215,12 +19782,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -19230,12 +19797,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -19245,12 +19812,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -19260,12 +19827,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -19275,12 +19842,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -19290,12 +19857,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ゆずき</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -19305,12 +19872,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -19325,7 +19892,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>ゆずき</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -19335,12 +19902,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -19350,12 +19917,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -19365,12 +19932,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>絶</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -19380,12 +19947,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -19395,12 +19962,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -19410,12 +19977,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -19425,12 +19992,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -19440,12 +20007,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -19455,12 +20022,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -19470,12 +20037,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -19485,12 +20052,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -19500,12 +20067,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -19515,15 +20082,45 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>アキ</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>コオリ</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>タカス</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>マサ</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>テクノ</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>ミコト</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C64" t="n">
         <v>1</v>
       </c>
     </row>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H174"/>
+  <dimension ref="A1:H203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5695,7 +5695,6 @@
           <t>たかやまん、ふくてゃ</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>今</t>
@@ -5706,7 +5705,6 @@
           <t>きたんご</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -5727,7 +5725,6 @@
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>今</t>
@@ -5738,7 +5735,6 @@
           <t>きちゃ</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -5759,7 +5755,6 @@
           <t>みるこ</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>出張前に</t>
@@ -5770,7 +5765,6 @@
           <t>きた！！</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -5791,7 +5785,6 @@
           <t>ひったん、S</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>今</t>
@@ -5802,7 +5795,6 @@
           <t>きた！</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -5823,7 +5815,6 @@
           <t>にょ</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>今</t>
@@ -5834,7 +5825,6 @@
           <t>きちゃ</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -5888,6 +5878,957 @@
         </is>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>27018</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>15:06:06</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ロタポジ</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>大宮店から！！</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>大宮店から、宇津宮店へインッします！
+よろしくお願いしますー！</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>27019</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>15:07:16</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>赤ちゃん</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>前橋店より</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>参戦します！</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>27020</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>15:42:57</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>★Zakk★</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>大宮から</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>17時オープンダッシュで遊びに行きますよ♪</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>27025</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>16:14:21</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>もかちんぽぽ</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>19時くらいに</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>あそびにいきまうす</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>27027</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>17:13:27</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>マロ</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>ピザ持って</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>コレから行きます！</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>27028</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>17:14:54</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>たいせい</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>ジム帰りに</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>少しだけ</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>27031</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>17:42:23</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>れいら</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>早めに</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>みんなに会いにきました</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>27033</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>17:43:34</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>みなっち</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>６時ごろに</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>縄もってぐー</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>27035</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>17:52:43</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>ひがんたん</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>27037</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>18:07:27</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Bee</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>弟子に会いに</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>きた</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>27039</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>18:49:34</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>しーたん</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>今から行きます</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>おみやげ持って行きます</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>27041</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>19:01:52</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>まいなちゅ</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>イベント</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>きました！！</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>27043</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>19:14:29</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>これから</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>行きますー</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>27045</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>19:44:31</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>愛とスケベの戦士</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>イキマス</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>グレートBAMBITCHマン！
+参上！</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>27046</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>19:45:32</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>きたよーん</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>27048</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>19:50:22</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>キムとどえむちゃん</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>二人で</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>伺います</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>27049</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>19:51:03</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>でで</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>イベント</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>楽しみに来た！</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>27053</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>20:06:03</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>ちゃそたけ</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>イベント</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>きちゃ！</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>27055</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>20:11:58</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>ゆうや</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>27057</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>22:11:32</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ゆずきん</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>27059</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>22:30:41</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>よっしー</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>23時くらいに</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>行きます！明日仕事あるので2時間くらいお店にいようと思います！</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>27060</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>22:40:05</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>ゆう、みちゃ、りょう</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>27063</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>23:20:22</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>うらら</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>ひさしぶりに</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>27065</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>23:29:16</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>ユッキー</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>三回目</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>27067</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>23:51:59</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>なまがき</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>27069</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>01:56:05</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>カズ、ダイゴ、ましゅ</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>27071</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>02:00:45</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>ぶりちゃん</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>ひとりで</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>27073</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>02:41:49</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>たかやまん、ふくてゃ</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>ふたりで</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>27075</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>03:55:24</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>ツッコミはお任せのSHIZU / 天然の100人ネキねむ</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの週末営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>本日8月21日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+ツッコミはお任せのSHIZU
+天然の100人ネキねむ
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>img20260821035524.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5899,7 +6840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I216"/>
+  <dimension ref="A1:I249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15192,6 +16133,1427 @@
       <c r="I216" t="inlineStr">
         <is>
           <t>きちゃ</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>15:06:06</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>27018</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>ロタポジ</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>1</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>ロタポジ</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>大宮店から！！</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>大宮店から、宇津宮店へインッします！
+よろしくお願いしますー！</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>15:07:16</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>27019</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>赤ちゃん</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>1</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>赤ちゃん</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>前橋店より</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>参戦します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>15:42:57</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>27020</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>★Zakk★</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>★Zakk★</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>大宮から</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>17時オープンダッシュで遊びに行きますよ♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>16:14:21</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>27025</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>もかちんぽぽ</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>1</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>もかちんぽぽ</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>19時くらいに</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>あそびにいきまうす</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>17:13:27</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>27027</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>マロ</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>2</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>マロ</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>ピザ持って</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>コレから行きます！</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>17:14:54</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>27028</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>たいせい</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>3</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>たいせい</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>ジム帰りに</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>少しだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>17:42:23</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>27031</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>れいら</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>2</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>れいら</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>早めに</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>みんなに会いにきました</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>17:43:34</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>27033</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>みなっち</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>3</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>みなっち</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>６時ごろに</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>縄もってぐー</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>17:52:43</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>27035</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>ひがんたん</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>ひがんたん</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>18:07:27</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>27037</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Bee</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>2</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Bee</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>弟子に会いに</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>きた</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>18:49:34</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>27039</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>しーたん</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>2</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>しーたん</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>今から行きます</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>おみやげ持って行きます</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>19:01:52</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>27041</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>まいなちゅ</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>2</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>まいなちゅ</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>イベント</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>きました！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>19:14:29</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>27043</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>2</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>これから</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>行きますー</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>19:44:31</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>27045</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>愛とスケベの戦士</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>愛とスケベの戦士</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>イキマス</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>グレートBAMBITCHマン！
+参上！</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>19:45:32</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>27046</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>6</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>きたよーん</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>19:50:22</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>27048</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>キムとどえむちゃん</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>1</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>キムとどえむちゃん</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>二人で</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>伺います</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>19:51:03</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>27049</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>でで</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>2</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>でで</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>イベント</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>楽しみに来た！</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>20:06:03</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>27053</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>ちゃそたけ</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>1</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>ちゃそたけ</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>イベント</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>きちゃ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>20:11:58</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>27055</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>ゆうや</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>1</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>ゆうや</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>22:11:32</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>27057</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>ゆずきん</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>1</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>ゆずきん</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>22:30:41</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>27059</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>よっしー</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>2</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>よっしー</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>23時くらいに</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>行きます！明日仕事あるので2時間くらいお店にいようと思います！</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>22:40:05</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>27060</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>ゆう</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>1</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>ゆう、みちゃ、りょう</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>22:40:05</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>27060</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>みちゃ</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>1</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>ゆう、みちゃ、りょう</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>22:40:05</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>27060</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>りょう</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>2</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>ゆう、みちゃ、りょう</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>23:20:22</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>27063</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>うらら</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>1</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>うらら</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>ひさしぶりに</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>23:29:16</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>27065</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>ユッキー</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>1</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>ユッキー</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>三回目</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>23:51:59</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>27067</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>なまがき</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>1</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>なまがき</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>01:56:05</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>27069</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>カズ</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>2</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>カズ、ダイゴ、ましゅ</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>01:56:05</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>27069</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>ダイゴ</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>1</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>カズ、ダイゴ、ましゅ</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>01:56:05</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>27069</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>4</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>カズ、ダイゴ、ましゅ</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>02:00:45</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>27071</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>ぶりちゃん</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>2</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>ぶりちゃん</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>ひとりで</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>02:41:49</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>27073</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>たかやまん</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>2</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>たかやまん、ふくてゃ</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>ふたりで</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>02:41:49</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>27073</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>ふくてゃ</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>3</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>たかやまん、ふくてゃ</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>ふたりで</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>きました</t>
         </is>
       </c>
     </row>
@@ -15206,7 +17568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D171"/>
+  <dimension ref="A1:D187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15278,7 +17640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -15287,14 +17649,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -15302,27 +17664,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>zin</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -15334,7 +17696,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>zin</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -15342,19 +17704,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>たいせい</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -15362,23 +17724,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -15387,54 +17749,54 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>みなっち</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -15442,19 +17804,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -15467,14 +17829,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -15482,19 +17844,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -15502,19 +17864,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>たいせい</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -15522,19 +17884,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -15542,7 +17904,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -15554,7 +17916,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>たつや</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -15562,19 +17924,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -15594,7 +17956,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>しーたん</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -15602,19 +17964,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -15622,19 +17984,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>みなっち</t>
+          <t>たかやまん</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -15642,19 +18004,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>たつや</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -15662,19 +18024,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>でで</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -15682,19 +18044,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>よっち</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -15702,19 +18064,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -15722,19 +18084,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -15742,19 +18104,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>タツヤ</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -15762,19 +18124,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>マッスル</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -15782,7 +18144,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -15794,15 +18156,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -15814,227 +18176,227 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>よっち</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>れいら</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>コテッチャン</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>タツヤ</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>マッスル</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TKC</t>
+          <t>マロ</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>彩</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -16042,19 +18404,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -16062,19 +18424,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>nuri</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -16094,7 +18456,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -16102,19 +18464,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -16122,19 +18484,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -16142,19 +18504,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -16162,19 +18524,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -16194,7 +18556,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>おじきち</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -16214,7 +18576,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
+          <t>TKC</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -16234,7 +18596,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -16242,19 +18604,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>かける</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -16262,19 +18624,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -16282,19 +18644,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>nuri</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -16302,19 +18664,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>−</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -16322,19 +18684,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>★Zakk★</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -16342,19 +18704,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -16362,19 +18724,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -16382,19 +18744,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>けん</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -16402,19 +18764,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>うらら</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -16422,19 +18784,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>こてっちゃん</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -16454,7 +18816,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>おじきち</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -16462,19 +18824,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>おちんぽベルセルク</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -16494,7 +18856,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -16502,19 +18864,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>かける</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -16522,19 +18884,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>しゅん</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -16542,19 +18904,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>しん</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -16562,19 +18924,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>しーたん</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -16582,19 +18944,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>すず</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -16602,19 +18964,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -16622,19 +18984,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -16642,19 +19004,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>けん</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -16674,7 +19036,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -16682,19 +19044,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>たかやまん</t>
+          <t>こてっちゃん</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -16702,19 +19064,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -16722,19 +19084,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -16742,19 +19104,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>さくら</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -16762,19 +19124,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>だいご</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -16782,19 +19144,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>しゅん</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -16802,19 +19164,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>しん</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -16822,19 +19184,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>すず</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -16842,19 +19204,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ちっち</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -16862,19 +19224,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -16882,19 +19244,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -16902,19 +19264,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>でで</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -16922,19 +19284,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -16942,19 +19304,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -16962,19 +19324,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -16994,7 +19356,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>だいご</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -17002,19 +19364,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -17022,19 +19384,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -17042,19 +19404,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>にこちん</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -17062,19 +19424,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>にょ</t>
+          <t>ちっち</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -17082,19 +19444,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>ちゃそたけ</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -17102,19 +19464,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -17122,19 +19484,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>はなまる</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -17142,19 +19504,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -17162,19 +19524,19 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -17182,19 +19544,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -17214,7 +19576,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -17222,19 +19584,19 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -17254,7 +19616,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -17262,19 +19624,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ぽちゃりす組</t>
+          <t>なまがき</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -17282,19 +19644,19 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>まいなす</t>
+          <t>にこちん</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -17314,7 +19676,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>にょ</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -17322,19 +19684,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -17342,19 +19704,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -17362,19 +19724,19 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>まっする</t>
+          <t>はなまる</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -17382,19 +19744,19 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>ひがんたん</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -17402,19 +19764,19 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -17422,19 +19784,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -17442,19 +19804,19 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>みかん</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -17462,19 +19824,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -17494,7 +19856,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>みなつちん</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -17514,7 +19876,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>みるこ</t>
+          <t>ぽちゃりす組</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -17522,19 +19884,19 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>まいなす</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -17542,19 +19904,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>まいまいん</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -17562,19 +19924,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -17582,19 +19944,19 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>やえ</t>
+          <t>まっする</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -17602,19 +19964,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ゆうくん</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -17622,19 +19984,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -17642,19 +20004,19 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -17662,19 +20024,19 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -17682,19 +20044,19 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -17702,19 +20064,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -17722,19 +20084,19 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -17742,19 +20104,19 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>みるこ</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -17762,19 +20124,19 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>よしお</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -17782,19 +20144,19 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>よしおたん</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -17802,19 +20164,19 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>もかちんぽぽ</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -17822,19 +20184,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -17842,19 +20204,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>やえ</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -17862,19 +20224,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -17882,19 +20244,19 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>ゆうくん</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -17902,19 +20264,19 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -17922,19 +20284,19 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -17942,19 +20304,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>ゆうや</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -17962,19 +20324,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -17982,19 +20344,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -18002,19 +20364,19 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>ゆずきん</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -18022,19 +20384,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>るい</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -18042,19 +20404,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>れいら</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -18062,19 +20424,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -18082,19 +20444,19 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ろくじ</t>
+          <t>よしお</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -18102,19 +20464,19 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>よしおたん</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -18122,19 +20484,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -18142,19 +20504,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -18162,19 +20524,19 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -18182,19 +20544,19 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>カー</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -18202,19 +20564,19 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -18222,19 +20584,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -18242,19 +20604,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>キムと新しい奴隷ちゃん</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -18262,19 +20624,19 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -18282,19 +20644,19 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -18302,19 +20664,19 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>るい</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -18322,19 +20684,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -18342,19 +20704,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>ろくじ</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -18362,19 +20724,19 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -18382,19 +20744,19 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -18402,19 +20764,19 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -18434,7 +20796,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>マイナス</t>
+          <t>カー</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -18442,19 +20804,19 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -18462,19 +20824,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>キムとどえむちゃん</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -18482,19 +20844,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>マナティ</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -18502,19 +20864,19 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>マロ</t>
+          <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -18522,19 +20884,19 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -18542,19 +20904,19 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -18562,19 +20924,19 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -18582,19 +20944,19 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -18602,32 +20964,352 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
+          <t>ダイチ</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>1</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>テクノとポチ</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ナカヤマヤ</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>1</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>フジ</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>1</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>ボンタ</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>マイナス</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>1</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>マサ</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>1</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>マッチョ</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>1</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>マナティ</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>1</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>1</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>ユッキー</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>1</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>ロタポジ</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>1</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>女子三人衆</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>1</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>愛とスケベの戦士</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>1</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
           <t>絶</t>
         </is>
       </c>
-      <c r="B171" t="n">
-        <v>1</v>
-      </c>
-      <c r="C171" t="inlineStr">
+      <c r="B186" t="n">
+        <v>1</v>
+      </c>
+      <c r="C186" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="D186" t="inlineStr">
         <is>
           <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>赤ちゃん</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -18708,10 +21390,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -18721,10 +21403,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -18804,10 +21486,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -18817,10 +21499,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -18986,10 +21668,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -18999,10 +21681,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -19012,10 +21694,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -19025,10 +21707,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -19038,10 +21720,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C21" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22">
@@ -19051,10 +21733,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C22" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -19077,10 +21759,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -19090,10 +21772,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -19139,13 +21821,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="C2" t="n">
-        <v>215</v>
+        <v>248</v>
       </c>
       <c r="D2" t="n">
-        <v>170</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -19159,7 +21841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19182,16 +21864,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>たかやまん</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -19202,7 +21884,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -19212,7 +21894,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -19227,12 +21909,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -19242,12 +21924,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>N</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>−</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -19257,12 +21939,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>−</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -19272,12 +21954,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>彩</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -19292,7 +21974,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -19302,12 +21984,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -19317,12 +21999,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>zin</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -19332,12 +22014,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>zin</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -19347,12 +22029,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -19367,7 +22049,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -19377,12 +22059,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -19392,12 +22074,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -19412,7 +22094,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -19427,7 +22109,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -19442,7 +22124,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -19457,7 +22139,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -19467,12 +22149,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -19482,12 +22164,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -19497,12 +22179,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -19512,12 +22194,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -19527,12 +22209,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -19542,12 +22224,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -19562,7 +22244,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -19577,7 +22259,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -19587,12 +22269,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -19607,7 +22289,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -19617,12 +22299,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -19632,12 +22314,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -19647,12 +22329,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -19662,12 +22344,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -19677,12 +22359,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -19692,12 +22374,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>たかやまん</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -19937,7 +22619,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -19947,12 +22629,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -19962,12 +22644,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>絶</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -19977,12 +22659,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -19992,12 +22674,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -20007,12 +22689,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -20022,12 +22704,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -20037,12 +22719,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -20052,12 +22734,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -20067,12 +22749,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -20082,12 +22764,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -20097,12 +22779,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -20112,15 +22794,105 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>ゆり</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>りえ</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>よっしー</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ザッキー</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>りく</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>アキ</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>コオリ</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>カズ</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ダイゴ</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>タカス</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>マサ</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>テクノ</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>ミコト</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="C70" t="n">
         <v>1</v>
       </c>
     </row>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H203"/>
+  <dimension ref="A1:H218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5897,7 +5897,6 @@
           <t>ロタポジ</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>大宮店から！！</t>
@@ -5909,7 +5908,6 @@
 よろしくお願いしますー！</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -5930,7 +5928,6 @@
           <t>赤ちゃん</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>前橋店より</t>
@@ -5941,7 +5938,6 @@
           <t>参戦します！</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -5962,7 +5958,6 @@
           <t>★Zakk★</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>大宮から</t>
@@ -5973,7 +5968,6 @@
           <t>17時オープンダッシュで遊びに行きますよ♪</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -5994,7 +5988,6 @@
           <t>もかちんぽぽ</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>19時くらいに</t>
@@ -6005,7 +5998,6 @@
           <t>あそびにいきまうす</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -6026,7 +6018,6 @@
           <t>マロ</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>ピザ持って</t>
@@ -6037,7 +6028,6 @@
           <t>コレから行きます！</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -6058,7 +6048,6 @@
           <t>たいせい</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>ジム帰りに</t>
@@ -6069,7 +6058,6 @@
           <t>少しだけ</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -6090,7 +6078,6 @@
           <t>れいら</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>早めに</t>
@@ -6101,7 +6088,6 @@
           <t>みんなに会いにきました</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -6122,7 +6108,6 @@
           <t>みなっち</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>６時ごろに</t>
@@ -6133,7 +6118,6 @@
           <t>縄もってぐー</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -6154,7 +6138,6 @@
           <t>ひがんたん</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>遊びに</t>
@@ -6165,7 +6148,6 @@
           <t>きたよー</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -6186,7 +6168,6 @@
           <t>Bee</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>弟子に会いに</t>
@@ -6197,7 +6178,6 @@
           <t>きた</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -6218,7 +6198,6 @@
           <t>しーたん</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>今から行きます</t>
@@ -6229,7 +6208,6 @@
           <t>おみやげ持って行きます</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -6250,7 +6228,6 @@
           <t>まいなちゅ</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
           <t>イベント</t>
@@ -6261,7 +6238,6 @@
           <t>きました！！</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -6282,7 +6258,6 @@
           <t>彩</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
           <t>これから</t>
@@ -6293,7 +6268,6 @@
           <t>行きますー</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -6314,7 +6288,6 @@
           <t>愛とスケベの戦士</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
           <t>イキマス</t>
@@ -6326,7 +6299,6 @@
 参上！</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -6347,7 +6319,6 @@
           <t>まいまい</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
           <t>遊びに</t>
@@ -6358,7 +6329,6 @@
           <t>きたよーん</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -6379,7 +6349,6 @@
           <t>キムとどえむちゃん</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
           <t>二人で</t>
@@ -6390,7 +6359,6 @@
           <t>伺います</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -6411,7 +6379,6 @@
           <t>でで</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
           <t>イベント</t>
@@ -6422,7 +6389,6 @@
           <t>楽しみに来た！</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -6443,7 +6409,6 @@
           <t>ちゃそたけ</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
           <t>イベント</t>
@@ -6454,7 +6419,6 @@
           <t>きちゃ！</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -6475,7 +6439,6 @@
           <t>ゆうや</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -6486,7 +6449,6 @@
           <t>来ました！</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -6507,7 +6469,6 @@
           <t>ゆずきん</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
           <t>いま</t>
@@ -6518,7 +6479,6 @@
           <t>きました♪</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -6539,7 +6499,6 @@
           <t>よっしー</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
           <t>23時くらいに</t>
@@ -6550,7 +6509,6 @@
           <t>行きます！明日仕事あるので2時間くらいお店にいようと思います！</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -6571,7 +6529,6 @@
           <t>ゆう、みちゃ、りょう</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -6582,7 +6539,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -6603,7 +6559,6 @@
           <t>うらら</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
           <t>ひさしぶりに</t>
@@ -6614,7 +6569,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -6635,7 +6589,6 @@
           <t>ユッキー</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
           <t>三回目</t>
@@ -6646,7 +6599,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -6667,7 +6619,6 @@
           <t>なまがき</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
           <t>いま</t>
@@ -6678,7 +6629,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -6699,7 +6649,6 @@
           <t>カズ、ダイゴ、ましゅ</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
           <t>さっき</t>
@@ -6710,7 +6659,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -6731,7 +6679,6 @@
           <t>ぶりちゃん</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
           <t>今日は</t>
@@ -6742,7 +6689,6 @@
           <t>ひとりで</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -6763,7 +6709,6 @@
           <t>たかやまん、ふくてゃ</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
           <t>ふたりで</t>
@@ -6774,7 +6719,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -6829,6 +6773,507 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>27077</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>17:52:44</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>てつじ</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>縄持って</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>行きます</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>27078</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>18:46:12</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>愛とスケベの戦士</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>イキマス</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>グレートBAMBITCHマン参上！</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>27081</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>18:54:48</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>おとは</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>用足し</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>終わったら行くねー！</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>27083</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>19:17:08</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>27085</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>19:45:48</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>これから</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>行きます！</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>27087</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>19:58:38</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>まっぴー</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>２年２ヶ月</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>ぶりに</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>27089</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>20:23:02</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>しょうた、すーさん</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>２人で</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>27091</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>21:04:23</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>よしおたん</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>絶好調</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>27093</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>21:22:52</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>なお</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>カシスソーダ</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>飲みに来ました</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>27095</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>21:59:31</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ゆずきん</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>きたぜ</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>27097</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>22:55:41</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>シュンヤ、ともや</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>若者</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2人で</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>27099</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>00:39:18</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>まーくん、りゅうくん</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>27101</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>01:21:58</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>ゆうき</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>あそびに</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>きた！</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>27103</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>02:33:35</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>K,N</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>のみに</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>27105</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>04:31:09</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>ツッコミはお任せのSHIZU / えちえち裏垢女子のモカチ</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの週末営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>本日8月22日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+ツッコミはお任せのSHIZU
+えちえち裏垢女子のモカチ
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>img20260822043109.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6840,7 +7285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I249"/>
+  <dimension ref="A1:I267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17554,6 +17999,780 @@
       <c r="I249" t="inlineStr">
         <is>
           <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>17:52:44</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>27077</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>てつじ</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>1</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>てつじ</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>縄持って</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>行きます</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>18:46:12</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>27078</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>愛とスケベの戦士</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>2</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>愛とスケベの戦士</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>イキマス</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>グレートBAMBITCHマン参上！</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>18:54:48</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>27081</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>おとは</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>3</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>おとは</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>用足し</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>終わったら行くねー！</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>19:17:08</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>27083</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>7</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>19:45:48</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>27085</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>3</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>これから</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>行きます！</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>19:58:38</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>27087</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>まっぴー</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>1</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>まっぴー</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>２年２ヶ月</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>ぶりに</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>20:23:02</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>27089</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>しょうた</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>1</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>しょうた、すーさん</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>２人で</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>20:23:02</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>27089</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>すーさん</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>2</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>しょうた、すーさん</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>２人で</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>21:04:23</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>27091</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>よしおたん</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>2</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>よしおたん</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>絶好調</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>21:22:52</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>27093</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>なお</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
+        <v>4</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>なお</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>カシスソーダ</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>飲みに来ました</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>21:59:31</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>27095</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>ゆずきん</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>2</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>ゆずきん</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>きたぜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>22:55:41</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>27097</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>シュンヤ</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>1</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>シュンヤ、ともや</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>若者</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>2人で</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>22:55:41</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>27097</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>ともや</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>1</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>シュンヤ、ともや</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>若者</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>2人で</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>00:39:18</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>27099</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>まーくん</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>2</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>まーくん、りゅうくん</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>00:39:18</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>27099</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>りゅうくん</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>1</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>まーくん、りゅうくん</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>01:21:58</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>27101</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>ゆうき</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>3</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>ゆうき</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>あそびに</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>きた！</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>02:33:35</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>27103</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>2</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>K,N</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>のみに</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>02:33:35</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>27103</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>3</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>K,N</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>のみに</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>きました！</t>
         </is>
       </c>
     </row>
@@ -17568,7 +18787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D187"/>
+  <dimension ref="A1:D193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17596,7 +18815,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ゆずき</t>
+          <t>ひがん</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -17604,32 +18823,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ひがん</t>
+          <t>ゆずき</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -17656,7 +18875,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -17664,7 +18883,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -17676,7 +18895,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -17684,27 +18903,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>zin</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -17716,7 +18935,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>たいせい</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -17724,19 +18943,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>zin</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -17744,19 +18963,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -17764,7 +18983,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -17776,7 +18995,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>みなっち</t>
+          <t>たいせい</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -17796,11 +19015,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -17809,74 +19028,74 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>みなっち</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>彩</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -17884,19 +19103,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -17904,19 +19123,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -17924,19 +19143,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -17944,19 +19163,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>しーたん</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -17964,19 +19183,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -17984,7 +19203,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -17996,7 +19215,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>たかやまん</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -18004,19 +19223,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>たつや</t>
+          <t>しーたん</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -18024,19 +19243,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>でで</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -18044,19 +19263,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -18069,14 +19288,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>たかやまん</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -18084,7 +19303,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -18096,7 +19315,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>たつや</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -18104,19 +19323,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>でで</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -18124,7 +19343,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -18136,7 +19355,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -18149,14 +19368,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -18164,19 +19383,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -18184,19 +19403,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>よっち</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -18204,19 +19423,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -18224,19 +19443,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -18249,14 +19468,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>れいら</t>
+          <t>ゆずきん</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -18264,19 +19483,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>よしおたん</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -18284,7 +19503,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -18296,7 +19515,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -18304,19 +19523,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>タツヤ</t>
+          <t>よっち</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -18324,19 +19543,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>マッスル</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -18344,19 +19563,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>マロ</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -18364,19 +19583,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>れいら</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -18384,7 +19603,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -18396,71 +19615,71 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>コテッチャン</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>タツヤ</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>マッスル</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -18469,54 +19688,54 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>マロ</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>愛とスケベの戦士</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -18524,19 +19743,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -18544,19 +19763,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -18564,19 +19783,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TKC</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -18584,19 +19803,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -18616,7 +19835,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -18624,19 +19843,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -18644,19 +19863,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>nuri</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -18664,19 +19883,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>TKC</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -18684,19 +19903,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>★Zakk★</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -18704,19 +19923,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -18736,7 +19955,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -18756,7 +19975,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>nuri</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -18764,19 +19983,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>うらら</t>
+          <t>−</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -18784,19 +20003,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>★Zakk★</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -18804,19 +20023,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>おじきち</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -18836,7 +20055,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -18856,7 +20075,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -18864,19 +20083,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>かける</t>
+          <t>うらら</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -18884,19 +20103,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -18904,19 +20123,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>おじきち</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -18924,19 +20143,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>おちんぽベルセルク</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -18944,19 +20163,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -18964,19 +20183,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>かける</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -18984,19 +20203,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -19016,7 +20235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>けん</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -19024,19 +20243,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -19044,19 +20263,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>こてっちゃん</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -19076,7 +20295,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -19084,19 +20303,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -19104,19 +20323,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>けん</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -19124,19 +20343,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -19144,19 +20363,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>しゅん</t>
+          <t>こてっちゃん</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -19164,19 +20383,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>しん</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -19196,7 +20415,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>すず</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -19204,19 +20423,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>さくら</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -19224,19 +20443,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -19244,19 +20463,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>しゅん</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -19264,19 +20483,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>しょうた</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -19284,19 +20503,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>しん</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -19304,19 +20523,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>すず</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -19324,19 +20543,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -19356,7 +20575,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>だいご</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -19364,19 +20583,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -19384,19 +20603,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -19404,19 +20623,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -19424,19 +20643,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ちっち</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -19444,19 +20663,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ちゃそたけ</t>
+          <t>だいご</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -19464,19 +20683,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -19484,19 +20703,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -19516,7 +20735,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -19536,7 +20755,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>ちっち</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -19544,19 +20763,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>ちゃそたけ</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -19564,19 +20783,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -19584,19 +20803,19 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -19604,19 +20823,19 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>てつじ</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -19624,19 +20843,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>なまがき</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -19644,19 +20863,19 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>にこちん</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -19664,19 +20883,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>にょ</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -19684,19 +20903,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -19704,19 +20923,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -19736,7 +20955,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>はなまる</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -19744,19 +20963,19 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ひがんたん</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -19764,19 +20983,19 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>なまがき</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -19784,19 +21003,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>にこちん</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -19804,19 +21023,19 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>にょ</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -19824,19 +21043,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -19844,19 +21063,19 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -19864,19 +21083,19 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ぽちゃりす組</t>
+          <t>はなまる</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -19884,19 +21103,19 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>まいなす</t>
+          <t>ひがんたん</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -19904,19 +21123,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -19924,19 +21143,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -19944,19 +21163,19 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>まっする</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -19964,19 +21183,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -19984,19 +21203,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -20004,19 +21223,19 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>ぽちゃりす組</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -20024,19 +21243,19 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>みかん</t>
+          <t>まいなす</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -20044,19 +21263,19 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まいまいん</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -20064,19 +21283,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -20084,19 +21303,19 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>みなつちん</t>
+          <t>まっする</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -20104,19 +21323,19 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>みるこ</t>
+          <t>まっぴー</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -20124,19 +21343,19 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -20156,7 +21375,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -20176,7 +21395,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>もかちんぽぽ</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -20184,19 +21403,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -20204,19 +21423,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>やえ</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -20224,19 +21443,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -20244,19 +21463,19 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ゆうくん</t>
+          <t>みるこ</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -20264,19 +21483,19 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -20284,19 +21503,19 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -20304,19 +21523,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ゆうや</t>
+          <t>もかちんぽぽ</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -20336,7 +21555,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -20344,19 +21563,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>やえ</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -20364,19 +21583,19 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ゆずきん</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -20396,7 +21615,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>ゆうくん</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -20404,19 +21623,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -20424,19 +21643,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -20444,19 +21663,19 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>よしお</t>
+          <t>ゆうや</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -20464,19 +21683,19 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>よしおたん</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -20484,19 +21703,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -20504,19 +21723,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -20524,19 +21743,19 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -20556,7 +21775,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -20564,19 +21783,19 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>よしお</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -20584,19 +21803,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -20604,19 +21823,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -20624,19 +21843,19 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -20644,19 +21863,19 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -20664,19 +21883,19 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>るい</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -20684,19 +21903,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -20704,19 +21923,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ろくじ</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -20724,19 +21943,19 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -20744,19 +21963,19 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -20764,19 +21983,19 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -20784,19 +22003,19 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>カー</t>
+          <t>るい</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -20804,19 +22023,19 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -20824,19 +22043,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>キムとどえむちゃん</t>
+          <t>ろくじ</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -20844,19 +22063,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -20864,19 +22083,19 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>キムと新しい奴隷ちゃん</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -20884,19 +22103,19 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -20904,19 +22123,19 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>カー</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -20924,19 +22143,19 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -20944,19 +22163,19 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>キムとどえむちゃん</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -20964,19 +22183,19 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -20984,19 +22203,19 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -21004,19 +22223,19 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -21024,19 +22243,19 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -21044,19 +22263,19 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -21064,19 +22283,19 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>マイナス</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -21084,19 +22303,19 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -21104,19 +22323,19 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ダイチ</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -21124,19 +22343,19 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>マナティ</t>
+          <t>テクノとポチ</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -21156,7 +22375,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>ナカヤマヤ</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -21164,19 +22383,19 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ユッキー</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -21184,19 +22403,19 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ロタポジ</t>
+          <t>ボンタ</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -21204,19 +22423,19 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>マイナス</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -21224,19 +22443,19 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>マサ</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -21244,19 +22463,19 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>愛とスケベの戦士</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -21264,19 +22483,19 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>マナティ</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -21284,30 +22503,150 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>ユッキー</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>1</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>ロタポジ</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>1</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>1</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>女子三人衆</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>1</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>絶</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>1</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
           <t>赤ちゃん</t>
         </is>
       </c>
-      <c r="B187" t="n">
-        <v>1</v>
-      </c>
-      <c r="C187" t="inlineStr">
+      <c r="B193" t="n">
+        <v>1</v>
+      </c>
+      <c r="C193" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="D193" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -21403,10 +22742,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -21416,10 +22755,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -21473,10 +22812,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -21486,10 +22825,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -21499,10 +22838,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -21694,10 +23033,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -21707,10 +23046,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -21720,10 +23059,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C21" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
@@ -21733,10 +23072,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -21746,10 +23085,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C23" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -21759,10 +23098,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
@@ -21821,13 +23160,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="C2" t="n">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="D2" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -21841,7 +23180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21864,12 +23203,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>たかやまん</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -21879,16 +23218,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>たかやまん</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -21899,7 +23238,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -21909,7 +23248,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -21924,12 +23263,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -22374,12 +23713,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>しょうた</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -22389,12 +23728,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -22404,12 +23743,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -22419,12 +23758,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -22434,12 +23773,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -22454,7 +23793,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -22464,12 +23803,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -22479,12 +23818,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -22494,12 +23833,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -22509,12 +23848,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -22524,12 +23863,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -22539,12 +23878,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -22554,12 +23893,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -22569,12 +23908,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ゆずき</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -22584,12 +23923,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -22604,7 +23943,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>ゆずき</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -22614,12 +23953,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -22629,12 +23968,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -22649,7 +23988,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -22659,12 +23998,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -22674,12 +24013,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>絶</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -22689,12 +24028,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -22704,12 +24043,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -22719,12 +24058,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -22734,12 +24073,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -22749,12 +24088,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -22764,12 +24103,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -22779,12 +24118,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -22794,12 +24133,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -22809,12 +24148,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -22824,12 +24163,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -22839,12 +24178,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -22854,12 +24193,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -22869,12 +24208,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -22884,15 +24223,60 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>アキ</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>コオリ</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>カズ</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ダイゴ</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>タカス</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>マサ</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>テクノ</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>ミコト</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="C73" t="n">
         <v>1</v>
       </c>
     </row>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H218"/>
+  <dimension ref="A1:H242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6792,7 +6792,6 @@
           <t>てつじ</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
           <t>縄持って</t>
@@ -6803,7 +6802,6 @@
           <t>行きます</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -6824,7 +6822,6 @@
           <t>愛とスケベの戦士</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
           <t>イキマス</t>
@@ -6835,7 +6832,6 @@
           <t>グレートBAMBITCHマン参上！</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -6856,7 +6852,6 @@
           <t>おとは</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
           <t>用足し</t>
@@ -6867,7 +6862,6 @@
           <t>終わったら行くねー！</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -6888,7 +6882,6 @@
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
           <t>今</t>
@@ -6899,7 +6892,6 @@
           <t>きたよー</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -6920,7 +6912,6 @@
           <t>彩</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
           <t>これから</t>
@@ -6931,7 +6922,6 @@
           <t>行きます！</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -6952,7 +6942,6 @@
           <t>まっぴー</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
           <t>２年２ヶ月</t>
@@ -6963,7 +6952,6 @@
           <t>ぶりに</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -6984,7 +6972,6 @@
           <t>しょうた、すーさん</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
           <t>２人で</t>
@@ -6995,7 +6982,6 @@
           <t>初めて</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -7016,7 +7002,6 @@
           <t>よしおたん</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
           <t>今日も</t>
@@ -7027,7 +7012,6 @@
           <t>絶好調</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -7048,7 +7032,6 @@
           <t>なお</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
           <t>カシスソーダ</t>
@@ -7059,7 +7042,6 @@
           <t>飲みに来ました</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -7080,7 +7062,6 @@
           <t>ゆずきん</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
           <t>今</t>
@@ -7091,7 +7072,6 @@
           <t>きたぜ</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -7112,7 +7092,6 @@
           <t>シュンヤ、ともや</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
           <t>若者</t>
@@ -7123,7 +7102,6 @@
           <t>2人で</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -7144,7 +7122,6 @@
           <t>まーくん、りゅうくん</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -7155,7 +7132,6 @@
           <t>きました♪</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -7176,7 +7152,6 @@
           <t>ゆうき</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
           <t>あそびに</t>
@@ -7187,7 +7162,6 @@
           <t>きた！</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -7208,7 +7182,6 @@
           <t>K,N</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
           <t>のみに</t>
@@ -7219,7 +7192,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -7274,6 +7246,794 @@
         </is>
       </c>
     </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>27108</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>18:56:18</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>たいせい</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>オープンから</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>いきまーす！</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>27109</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>19:06:04</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>とっしー</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>いちばんのり</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>きた</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>27110</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>19:09:44</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>さとるん、おとは</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>きた</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>27111</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>19:10:40</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>たかやま、ふくてゃ</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>きちゃ</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>27116</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>19:59:22</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>こうた、まゆ</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>27118</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>20:13:23</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>はち</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>27120</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>20:21:23</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>きちゃ</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>27122</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>20:46:21</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>おにゃん、ひがん</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>きた！！！！！！！！</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>27124</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>20:49:51</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>すー、ましゅ</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>きた</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>27125</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>20:50:06</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>まいなちゅ</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>きたよ</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>27128</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>21:12:26</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>きむむ</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>きたきむ</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>27130</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>21:26:33</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>海砂利水魚</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>こんばんわ</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>ぺろーん</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>27132</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>21:32:20</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>なな</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>ひさしぶり</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>27134</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>21:46:25</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>たけし</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>27136</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>21:50:58</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>カミさん、いっちゃん</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>きた</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>27138</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>22:24:37</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>アナルプリンス</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>こんばんわ</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>27141</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>22:45:21</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>よしやん、かな</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>27143</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>22:54:08</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>おでで</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>きちゃちゃ</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>27145</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>23:41:49</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>さと</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>きたよ♪</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>27147</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>00:27:48</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>まーさん</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>きたよ</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>27149</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>01:14:01</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>かな(絶ちゃん)/おっつん</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>いまから</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>いきまーす！</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>27151</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>01:19:45</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>ゆう</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>27153</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>02:15:27</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>はな</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>あそびに</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>27155</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>04:09:37</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>天然の100人ネキ　ねむ</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの日曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>本日8月23日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+天然の100人ネキ　ねむ
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>img20260823040937.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7285,7 +8045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I267"/>
+  <dimension ref="A1:I297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18771,6 +19531,1296 @@
         </is>
       </c>
       <c r="I267" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>18:56:18</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>27108</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>たいせい</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>4</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>たいせい</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>オープンから</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>いきまーす！</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>19:06:04</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>27109</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>とっしー</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>1</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>とっしー</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>いちばんのり</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>きた</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>19:09:44</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>27110</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>さとるん</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>1</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>さとるん、おとは</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>きた</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>19:09:44</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>27110</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>おとは</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>4</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>さとるん、おとは</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>きた</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>19:10:40</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>27111</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>たかやま</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>3</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>たかやま、ふくてゃ</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>きちゃ</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>19:10:40</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>27111</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>ふくてゃ</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>4</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>たかやま、ふくてゃ</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>きちゃ</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>19:59:22</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>27116</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>こうた</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>1</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>こうた、まゆ</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>19:59:22</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>27116</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>まゆ</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>1</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>こうた、まゆ</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>20:13:23</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>27118</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>はち</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>1</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>はち</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>20:21:23</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>27120</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>8</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>きちゃ</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>20:46:21</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>27122</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>おにゃん</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
+        <v>1</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>おにゃん、ひがん</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>きた！！！！！！！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>20:46:21</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>27122</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>8</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>おにゃん、ひがん</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>きた！！！！！！！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>20:49:51</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>27124</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>すー</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>2</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>すー、ましゅ</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>きた</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>20:49:51</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>27124</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>5</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>すー、ましゅ</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>きた</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>20:50:06</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>27125</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>まいなちゅ</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>3</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>まいなちゅ</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>きたよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>21:12:26</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>27128</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>きむむ</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>1</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>きむむ</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>きたきむ</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>21:26:33</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>27130</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>海砂利水魚</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>1</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>海砂利水魚</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>こんばんわ</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>ぺろーん</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>21:32:20</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>27132</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>なな</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>1</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>なな</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>ひさしぶり</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>21:46:25</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>27134</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>たけし</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>1</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>たけし</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>21:50:58</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>27136</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>カミさん</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>1</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>カミさん、いっちゃん</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>きた</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>21:50:58</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>27136</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>いっちゃん</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>2</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>カミさん、いっちゃん</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>きた</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>22:24:37</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>27138</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>アナルプリンス</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>1</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>アナルプリンス</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>こんばんわ</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>22:45:21</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>27141</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>よしやん</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>2</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>よしやん、かな</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>22:45:21</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>27141</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>かな</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>2</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>よしやん、かな</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>22:54:08</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>27143</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>おでで</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>1</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>おでで</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>きちゃちゃ</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>23:41:49</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>27145</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>さと</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>1</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>さと</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>きたよ♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>00:27:48</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>27147</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>まーさん</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>1</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>まーさん</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>きたよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>01:14:01</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>27149</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>かな(絶ちゃん)/おっつん</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>かな(絶ちゃん)/おっつん</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>いまから</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>いきまーす！</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>01:19:45</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>27151</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>ゆう</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>2</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>ゆう</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>02:15:27</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>27153</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>はな</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>1</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>はな</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>あそびに</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
         <is>
           <t>きました！</t>
         </is>
@@ -18787,7 +20837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18819,7 +20869,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18828,7 +20878,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -18839,7 +20889,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -18848,7 +20898,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -18875,27 +20925,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -18903,19 +20953,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>たいせい</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -18923,23 +20973,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -18948,54 +20998,54 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>zin</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>たいせい</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -19003,19 +21053,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>zin</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -19023,19 +21073,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>みなっち</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -19043,19 +21093,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -19063,7 +21113,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19075,7 +21125,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>みなっち</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -19083,59 +21133,59 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>彩</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -19143,19 +21193,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -19163,19 +21213,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -19183,19 +21233,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -19203,7 +21253,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -19215,7 +21265,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -19228,14 +21278,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>しーたん</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -19243,19 +21293,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -19263,19 +21313,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -19283,19 +21333,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>たかやまん</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -19303,19 +21353,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>たつや</t>
+          <t>しーたん</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -19323,19 +21373,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>でで</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -19343,19 +21393,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -19363,19 +21413,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>たかやまん</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -19383,7 +21433,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -19395,7 +21445,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>たつや</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -19403,19 +21453,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>でで</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -19423,7 +21473,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -19435,7 +21485,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -19443,19 +21493,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -19463,19 +21513,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ゆずきん</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -19483,19 +21533,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>よしおたん</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -19503,19 +21553,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -19523,19 +21573,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>よっち</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -19543,19 +21593,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>ゆずきん</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -19563,19 +21613,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>よしおたん</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -19583,19 +21633,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>れいら</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -19603,19 +21653,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -19623,19 +21673,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>よっち</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -19643,19 +21693,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>タツヤ</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -19663,19 +21713,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>マッスル</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -19683,19 +21733,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>マロ</t>
+          <t>れいら</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -19703,7 +21753,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -19715,7 +21765,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>愛とスケベの戦士</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -19723,7 +21773,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -19735,107 +21785,107 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>コテッチャン</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>タツヤ</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>マッスル</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>マロ</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>愛とスケベの戦士</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -19843,19 +21893,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -19863,19 +21913,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -19883,19 +21933,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TKC</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -19903,19 +21953,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -19935,7 +21985,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -19943,19 +21993,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -19963,19 +22013,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>nuri</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -19983,19 +22033,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>TKC</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -20003,19 +22053,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>★Zakk★</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -20023,19 +22073,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -20055,7 +22105,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -20075,7 +22125,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>nuri</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -20083,19 +22133,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>うらら</t>
+          <t>−</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -20103,19 +22153,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>★Zakk★</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -20123,19 +22173,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>おじきち</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -20155,7 +22205,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -20175,7 +22225,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>うらら</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -20183,19 +22233,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>かける</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -20203,19 +22253,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>おじきち</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -20223,19 +22273,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>おちんぽベルセルク</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -20243,19 +22293,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>おでで</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -20263,19 +22313,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>おにゃん</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -20283,19 +22333,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -20303,19 +22353,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>かける</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -20323,19 +22373,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>けん</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -20355,7 +22405,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -20363,19 +22413,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>こてっちゃん</t>
+          <t>かな(絶ちゃん)/おっつん</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -20383,19 +22433,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>きむむ</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -20403,19 +22453,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -20423,19 +22473,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -20443,19 +22493,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -20463,19 +22513,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>しゅん</t>
+          <t>けん</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -20483,19 +22533,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>しょうた</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -20503,19 +22553,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>しん</t>
+          <t>こうた</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -20523,19 +22573,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>すず</t>
+          <t>こてっちゃん</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -20543,19 +22593,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -20563,19 +22613,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -20583,19 +22633,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>さくら</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -20603,19 +22653,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>さと</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -20623,19 +22673,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>さとるん</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -20643,19 +22693,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -20663,19 +22713,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>だいご</t>
+          <t>しゅん</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -20683,19 +22733,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>しょうた</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -20703,19 +22753,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>しん</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -20723,19 +22773,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>すず</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -20743,19 +22793,19 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ちっち</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -20763,19 +22813,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ちゃそたけ</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -20783,19 +22833,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -20803,19 +22853,19 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -20823,19 +22873,19 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>てつじ</t>
+          <t>たけし</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -20843,19 +22893,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -20863,19 +22913,19 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>だいご</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -20883,19 +22933,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -20903,19 +22953,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ともや</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -20923,19 +22973,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -20943,19 +22993,19 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>ちっち</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -20963,19 +23013,19 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ちゃそたけ</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -20983,19 +23033,19 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>なまがき</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -21003,19 +23053,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>にこちん</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -21023,19 +23073,19 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>にょ</t>
+          <t>てつじ</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -21043,19 +23093,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -21075,7 +23125,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -21083,19 +23133,19 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>はなまる</t>
+          <t>とっしー</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -21103,19 +23153,19 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ひがんたん</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -21123,19 +23173,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -21143,19 +23193,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -21175,7 +23225,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -21183,19 +23233,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -21203,19 +23253,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>なな</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -21223,19 +23273,19 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ぽちゃりす組</t>
+          <t>なまがき</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -21243,19 +23293,19 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>まいなす</t>
+          <t>にこちん</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -21275,7 +23325,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>にょ</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -21283,19 +23333,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -21303,19 +23353,19 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>まっする</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -21323,19 +23373,19 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>まっぴー</t>
+          <t>はち</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -21343,19 +23393,19 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>はな</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -21363,19 +23413,19 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>はなまる</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -21383,19 +23433,19 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>みかん</t>
+          <t>ひがんたん</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -21403,19 +23453,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -21423,19 +23473,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -21443,19 +23493,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>みなつちん</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -21463,19 +23513,19 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>みるこ</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -21483,19 +23533,19 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -21503,19 +23553,19 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>ぽちゃりす組</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -21523,19 +23573,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>もかちんぽぽ</t>
+          <t>まいなす</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -21543,19 +23593,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>まいまいん</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -21563,19 +23613,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>やえ</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -21583,19 +23633,19 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>まっする</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -21603,19 +23653,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ゆうくん</t>
+          <t>まっぴー</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -21623,19 +23673,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>まゆ</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -21643,19 +23693,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -21663,19 +23713,19 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ゆうや</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -21683,19 +23733,19 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>まーさん</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -21703,19 +23753,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -21723,19 +23773,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -21743,19 +23793,19 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -21763,19 +23813,19 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -21783,19 +23833,19 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>よしお</t>
+          <t>みるこ</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -21803,19 +23853,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -21823,19 +23873,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -21843,19 +23893,19 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>もかちんぽぽ</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -21863,19 +23913,19 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -21883,19 +23933,19 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>やえ</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -21903,19 +23953,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>ゆうくん</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -21923,19 +23973,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -21943,19 +23993,19 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -21963,19 +24013,19 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>ゆうや</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -21983,19 +24033,19 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -22003,19 +24053,19 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>るい</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -22035,7 +24085,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -22043,19 +24093,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ろくじ</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -22063,19 +24113,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -22083,19 +24133,19 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>よしお</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -22103,19 +24153,19 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -22135,7 +24185,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>カー</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -22143,19 +24193,19 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -22163,19 +24213,19 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>キムとどえむちゃん</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -22183,19 +24233,19 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -22203,19 +24253,19 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>キムと新しい奴隷ちゃん</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -22223,19 +24273,19 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -22243,19 +24293,19 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -22263,19 +24313,19 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -22283,19 +24333,19 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>るい</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -22303,19 +24353,19 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -22323,19 +24373,19 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>ろくじ</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -22343,19 +24393,19 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -22363,19 +24413,19 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>アナルプリンス</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -22383,19 +24433,19 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -22403,19 +24453,19 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>カミさん</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -22423,19 +24473,19 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>マイナス</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -22443,19 +24493,19 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>カー</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -22463,19 +24513,19 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -22483,19 +24533,19 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>マナティ</t>
+          <t>キムとどえむちゃん</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -22503,19 +24553,19 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -22523,19 +24573,19 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ユッキー</t>
+          <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -22543,19 +24593,19 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ロタポジ</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -22563,19 +24613,19 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -22583,19 +24633,19 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -22603,19 +24653,19 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -22623,30 +24673,370 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
+          <t>ダイゴ</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>1</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ダイチ</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>1</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>テクノとポチ</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>1</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ナカヤマヤ</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>1</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>フジ</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>1</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>ボンタ</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>マイナス</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>1</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>マサ</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>マッチョ</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>1</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>マナティ</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>1</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>ユッキー</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>1</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>ロタポジ</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>1</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>1</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>女子三人衆</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>1</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>海砂利水魚</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>1</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>絶</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
           <t>赤ちゃん</t>
         </is>
       </c>
-      <c r="B193" t="n">
-        <v>1</v>
-      </c>
-      <c r="C193" t="inlineStr">
+      <c r="B210" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -22755,10 +25145,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -22768,10 +25158,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -22812,10 +25202,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -22825,10 +25215,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -22838,10 +25228,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -23046,10 +25436,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -23059,10 +25449,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C21" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22">
@@ -23072,10 +25462,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C22" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -23085,10 +25475,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C23" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
@@ -23098,10 +25488,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C24" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
@@ -23111,10 +25501,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -23160,13 +25550,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="C2" t="n">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="D2" t="n">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -23180,7 +25570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23218,12 +25608,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>たかやまん</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -23233,16 +25623,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>たかやまん</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -23253,7 +25643,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -23263,7 +25653,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -23278,12 +25668,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -23293,12 +25683,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>−</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -23308,12 +25698,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>彩</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -23328,7 +25718,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -23338,12 +25728,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -23353,12 +25743,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>zin</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -23368,12 +25758,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>zin</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -23383,12 +25773,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -23403,7 +25793,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -23413,12 +25803,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -23428,12 +25818,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -23443,12 +25833,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>カミさん</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -23463,7 +25853,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -23478,7 +25868,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -23493,7 +25883,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -23503,12 +25893,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -23518,12 +25908,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -23533,12 +25923,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -23548,12 +25938,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>さとるん</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -23563,12 +25953,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -23578,12 +25968,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>おにゃん</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>ひがん</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -23593,12 +25983,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -23608,12 +25998,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -23623,12 +26013,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -23638,12 +26028,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -23653,12 +26043,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -23668,12 +26058,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -23683,12 +26073,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -23698,12 +26088,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -23713,12 +26103,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>しょうた</t>
+          <t>こうた</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>まゆ</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -23728,12 +26118,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -23743,12 +26133,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -23758,12 +26148,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -23773,12 +26163,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>しょうた</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -23788,12 +26178,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -23803,12 +26193,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -23818,12 +26208,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -23833,12 +26223,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ともや</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -23848,12 +26238,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -23863,12 +26253,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -23878,12 +26268,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -23893,12 +26283,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -23908,12 +26298,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -23923,12 +26313,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -23938,12 +26328,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ゆずき</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -23953,12 +26343,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -23968,12 +26358,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -23983,12 +26373,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -23998,12 +26388,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -24013,12 +26403,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -24028,12 +26418,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>ゆずき</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -24043,12 +26433,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -24058,12 +26448,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -24073,12 +26463,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -24088,12 +26478,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -24103,12 +26493,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>絶</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -24118,12 +26508,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -24133,12 +26523,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -24148,12 +26538,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -24163,12 +26553,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -24178,12 +26568,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -24193,12 +26583,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -24208,12 +26598,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -24223,12 +26613,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -24238,12 +26628,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -24253,12 +26643,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -24268,15 +26658,105 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>ゆり</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>りえ</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>よっしー</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ザッキー</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>りく</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>アキ</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>コオリ</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>カズ</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ダイゴ</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>タカス</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>マサ</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>テクノ</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>ミコト</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C79" t="n">
         <v>1</v>
       </c>
     </row>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H242"/>
+  <dimension ref="A1:H254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7265,7 +7265,6 @@
           <t>たいせい</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
           <t>オープンから</t>
@@ -7276,7 +7275,6 @@
           <t>いきまーす！</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -7297,7 +7295,6 @@
           <t>とっしー</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
           <t>いちばんのり</t>
@@ -7308,7 +7305,6 @@
           <t>きた</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -7329,7 +7325,6 @@
           <t>さとるん、おとは</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
           <t>さっき</t>
@@ -7340,7 +7335,6 @@
           <t>きた</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -7361,7 +7355,6 @@
           <t>たかやま、ふくてゃ</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
           <t>今</t>
@@ -7372,7 +7365,6 @@
           <t>きちゃ</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -7393,7 +7385,6 @@
           <t>こうた、まゆ</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
           <t>初めて</t>
@@ -7404,7 +7395,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -7425,7 +7415,6 @@
           <t>はち</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
           <t>今</t>
@@ -7436,7 +7425,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -7457,7 +7445,6 @@
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
           <t>今</t>
@@ -7468,7 +7455,6 @@
           <t>きちゃ</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -7489,7 +7475,6 @@
           <t>おにゃん、ひがん</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
           <t>今</t>
@@ -7500,7 +7485,6 @@
           <t>きた！！！！！！！！</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -7521,7 +7505,6 @@
           <t>すー、ましゅ</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
           <t>いま</t>
@@ -7532,7 +7515,6 @@
           <t>きた</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -7553,7 +7535,6 @@
           <t>まいなちゅ</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
           <t>いま</t>
@@ -7564,7 +7545,6 @@
           <t>きたよ</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -7585,7 +7565,6 @@
           <t>きむむ</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
           <t>いま</t>
@@ -7596,7 +7575,6 @@
           <t>きたきむ</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -7617,7 +7595,6 @@
           <t>海砂利水魚</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
           <t>こんばんわ</t>
@@ -7628,7 +7605,6 @@
           <t>ぺろーん</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -7649,7 +7625,6 @@
           <t>なな</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
           <t>ひさしぶり</t>
@@ -7660,7 +7635,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -7681,7 +7655,6 @@
           <t>たけし</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
           <t>初めて</t>
@@ -7692,7 +7665,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -7713,7 +7685,6 @@
           <t>カミさん、いっちゃん</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
           <t>今</t>
@@ -7724,7 +7695,6 @@
           <t>きた</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -7745,7 +7715,6 @@
           <t>アナルプリンス</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
           <t>こんばんわ</t>
@@ -7756,7 +7725,6 @@
           <t>きました♪</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -7777,7 +7745,6 @@
           <t>よしやん、かな</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
           <t>今</t>
@@ -7788,7 +7755,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -7809,7 +7775,6 @@
           <t>おでで</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
           <t>今</t>
@@ -7820,7 +7785,6 @@
           <t>きちゃちゃ</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -7841,7 +7805,6 @@
           <t>さと</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
           <t>今</t>
@@ -7852,7 +7815,6 @@
           <t>きたよ♪</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -7873,7 +7835,6 @@
           <t>まーさん</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
           <t>今</t>
@@ -7884,7 +7845,6 @@
           <t>きたよ</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -7905,7 +7865,6 @@
           <t>かな(絶ちゃん)/おっつん</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
           <t>いまから</t>
@@ -7916,7 +7875,6 @@
           <t>いきまーす！</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -7937,7 +7895,6 @@
           <t>ゆう</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>すこし</t>
@@ -7948,7 +7905,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -7969,7 +7925,6 @@
           <t>はな</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
           <t>あそびに</t>
@@ -7980,7 +7935,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -8034,6 +7988,410 @@
         </is>
       </c>
     </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>27157</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>16:37:45</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>キムとドMまゆ</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>遅い時間に</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>来店します</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>27159</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>18:52:21</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>トニー・トニー・チョッパー</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>これから</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>いきます</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>27161</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>20:06:59</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>僕と私</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>密かな</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>イベント楽しみに＾＾</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>27163</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>21:14:34</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>M、T、A、R</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>きたよーん</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>27165</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>21:48:36</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>名無し</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>アナル野菜</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>見に来ました</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>27166</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>21:50:58</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>よしおたん</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>きたよーん</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>27169</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>22:50:55</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>しょうた</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>呼ばれて</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>27171</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>23:45:06</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>あんこ</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>ひさしぶりに</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>27173</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>00:32:46</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>みなっち</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>このあと</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>縛りに行くよん</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>27175</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>01:23:50</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>コテッチャン</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>きたんご</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>27177</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>02:46:41</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>ひがんちゃん</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>そういや</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>少し前にきた</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>27179</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>05:13:16</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>新妻マゾヒストのミコト</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの月曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>本日8月24日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+新妻マゾヒストのミコト
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>img20260824051316.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8045,7 +8403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I297"/>
+  <dimension ref="A1:I311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20823,6 +21181,608 @@
       <c r="I297" t="inlineStr">
         <is>
           <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>16:37:45</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>27157</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>キムとドMまゆ</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>1</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>キムとドMまゆ</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>遅い時間に</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>来店します</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>18:52:21</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>27159</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>トニー・トニー・チョッパー</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>1</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>トニー・トニー・チョッパー</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>これから</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>いきます</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>20:06:59</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>27161</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>僕と私</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>1</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>僕と私</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>密かな</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>イベント楽しみに＾＾</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>21:14:34</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>27163</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>2</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>M、T、A、R</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>きたよーん</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>21:14:34</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>27163</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>1</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>M、T、A、R</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>きたよーん</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>21:14:34</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>27163</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F303" t="n">
+        <v>2</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>M、T、A、R</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>きたよーん</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>21:14:34</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>27163</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F304" t="n">
+        <v>1</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>M、T、A、R</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>きたよーん</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>21:48:36</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>27165</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>名無し</t>
+        </is>
+      </c>
+      <c r="F305" t="n">
+        <v>1</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>名無し</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>アナル野菜</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>見に来ました</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>21:50:58</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>27166</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>よしおたん</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>3</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>よしおたん</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>きたよーん</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>22:50:55</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>27169</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>しょうた</t>
+        </is>
+      </c>
+      <c r="F307" t="n">
+        <v>2</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>しょうた</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>呼ばれて</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>23:45:06</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>27171</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>あんこ</t>
+        </is>
+      </c>
+      <c r="F308" t="n">
+        <v>1</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>あんこ</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>ひさしぶりに</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>00:32:46</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>27173</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>みなっち</t>
+        </is>
+      </c>
+      <c r="F309" t="n">
+        <v>4</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>みなっち</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>このあと</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>縛りに行くよん</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>01:23:50</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>27175</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>コテッチャン</t>
+        </is>
+      </c>
+      <c r="F310" t="n">
+        <v>3</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>コテッチャン</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>きたんご</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>02:46:41</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>27177</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>ひがんちゃん</t>
+        </is>
+      </c>
+      <c r="F311" t="n">
+        <v>1</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>ひがんちゃん</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>そういや</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>少し前にきた</t>
         </is>
       </c>
     </row>
@@ -20837,7 +21797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D210"/>
+  <dimension ref="A1:D218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21025,7 +21985,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>みなっち</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -21033,39 +21993,39 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>zin</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -21073,19 +22033,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>zin</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -21093,19 +22053,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -21113,7 +22073,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -21125,7 +22085,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>みなっち</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -21133,12 +22093,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -21165,7 +22125,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>よしおたん</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -21173,23 +22133,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>コテッチャン</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -21198,34 +22158,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>彩</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -21233,19 +22193,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -21253,19 +22213,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -21273,19 +22233,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -21293,19 +22253,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -21313,19 +22273,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -21333,19 +22293,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -21358,14 +22318,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>しーたん</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -21373,19 +22333,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -21393,19 +22353,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -21413,19 +22373,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>たかやまん</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -21433,19 +22393,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>たつや</t>
+          <t>しょうた</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -21453,19 +22413,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>でで</t>
+          <t>しーたん</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -21473,7 +22433,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -21485,7 +22445,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -21498,14 +22458,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -21513,7 +22473,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -21525,7 +22485,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>たかやまん</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -21533,19 +22493,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>たつや</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -21553,19 +22513,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>でで</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -21573,19 +22533,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -21593,19 +22553,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ゆずきん</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -21613,7 +22573,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -21625,7 +22585,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>よしおたん</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -21633,19 +22593,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -21653,7 +22613,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -21665,7 +22625,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -21673,19 +22633,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>よっち</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -21693,19 +22653,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>ゆずきん</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -21713,19 +22673,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -21733,19 +22693,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>れいら</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -21753,7 +22713,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -21765,7 +22725,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>よっち</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -21778,14 +22738,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -21793,19 +22753,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>タツヤ</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -21813,19 +22773,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>マッスル</t>
+          <t>れいら</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -21833,19 +22793,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>マロ</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -21853,19 +22813,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>愛とスケベの戦士</t>
+          <t>タツヤ</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -21873,23 +22833,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>マッスル</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -21898,18 +22858,18 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>マロ</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -21918,34 +22878,34 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>愛とスケベの戦士</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -21953,19 +22913,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -21973,19 +22933,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -21993,19 +22953,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -22013,19 +22973,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -22045,7 +23005,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TKC</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -22053,19 +23013,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -22073,19 +23033,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -22093,19 +23053,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>TKC</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -22125,7 +23085,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>nuri</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -22133,19 +23093,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -22153,19 +23113,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>★Zakk★</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -22173,19 +23133,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>nuri</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -22193,19 +23153,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>−</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -22213,19 +23173,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>うらら</t>
+          <t>★Zakk★</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -22245,7 +23205,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -22265,7 +23225,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>おじきち</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -22273,19 +23233,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
+          <t>あんこ</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -22293,19 +23253,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>おでで</t>
+          <t>うらら</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -22313,19 +23273,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>おにゃん</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -22333,19 +23293,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>おじきち</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -22353,19 +23313,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>かける</t>
+          <t>おちんぽベルセルク</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -22373,19 +23333,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>おでで</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -22393,19 +23353,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>おにゃん</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -22413,19 +23373,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>かな(絶ちゃん)/おっつん</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -22433,19 +23393,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>きむむ</t>
+          <t>かける</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -22453,19 +23413,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -22473,19 +23433,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -22493,19 +23453,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>かな(絶ちゃん)/おっつん</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -22513,19 +23473,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>けん</t>
+          <t>きむむ</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -22533,19 +23493,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -22553,19 +23513,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>こうた</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -22573,19 +23533,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>こてっちゃん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -22593,19 +23553,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>けん</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -22625,7 +23585,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -22633,19 +23593,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>こうた</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -22653,19 +23613,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>さと</t>
+          <t>こてっちゃん</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -22673,19 +23633,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>さとるん</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -22693,19 +23653,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -22713,19 +23673,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>しゅん</t>
+          <t>さくら</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -22733,19 +23693,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>しょうた</t>
+          <t>さと</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -22753,19 +23713,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>しん</t>
+          <t>さとるん</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -22773,19 +23733,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>すず</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -22793,19 +23753,19 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>しゅん</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -22813,19 +23773,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>しん</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -22833,19 +23793,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>すず</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -22853,19 +23813,19 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -22873,19 +23833,19 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>たけし</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -22893,19 +23853,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -22913,19 +23873,19 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>だいご</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -22945,7 +23905,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>たけし</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -22953,19 +23913,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -22973,19 +23933,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>だいご</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -22993,19 +23953,19 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ちっち</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -23013,19 +23973,19 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ちゃそたけ</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -23033,19 +23993,19 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -23053,19 +24013,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>ちっち</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -23073,19 +24033,19 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>てつじ</t>
+          <t>ちゃそたけ</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -23093,19 +24053,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -23113,19 +24073,19 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -23133,19 +24093,19 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>とっしー</t>
+          <t>てつじ</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -23153,19 +24113,19 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -23173,19 +24133,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ともや</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -23193,19 +24153,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>とっしー</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -23213,19 +24173,19 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -23233,19 +24193,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -23253,19 +24213,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>なな</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -23273,19 +24233,19 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>なまがき</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -23293,19 +24253,19 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>にこちん</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -23325,7 +24285,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>にょ</t>
+          <t>なな</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -23333,19 +24293,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>なまがき</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -23353,19 +24313,19 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>にこちん</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -23373,19 +24333,19 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>はち</t>
+          <t>にょ</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -23393,19 +24353,19 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>はな</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -23413,19 +24373,19 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>はなまる</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -23433,19 +24393,19 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ひがんたん</t>
+          <t>はち</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -23453,19 +24413,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>はな</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -23473,19 +24433,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>はなまる</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -23493,19 +24453,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>ひがんたん</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -23513,19 +24473,19 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ひがんちゃん</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -23533,19 +24493,19 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -23553,19 +24513,19 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ぽちゃりす組</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -23573,19 +24533,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>まいなす</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -23593,19 +24553,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -23613,19 +24573,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -23633,19 +24593,19 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>まっする</t>
+          <t>ぽちゃりす組</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -23653,19 +24613,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>まっぴー</t>
+          <t>まいなす</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -23673,19 +24633,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>まゆ</t>
+          <t>まいまいん</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -23693,19 +24653,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -23713,19 +24673,19 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>まっする</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -23745,7 +24705,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>まーさん</t>
+          <t>まっぴー</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -23753,19 +24713,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>みかん</t>
+          <t>まゆ</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -23773,19 +24733,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -23793,19 +24753,19 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -23813,19 +24773,19 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>みなつちん</t>
+          <t>まーさん</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -23833,19 +24793,19 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>みるこ</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -23853,19 +24813,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -23873,19 +24833,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -23893,19 +24853,19 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>もかちんぽぽ</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -23913,19 +24873,19 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みるこ</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -23933,19 +24893,19 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>やえ</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -23953,19 +24913,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ゆうくん</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -23973,19 +24933,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>もかちんぽぽ</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -23993,19 +24953,19 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -24013,19 +24973,19 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ゆうや</t>
+          <t>やえ</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -24033,19 +24993,19 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ゆうくん</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -24065,7 +25025,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -24073,19 +25033,19 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -24093,19 +25053,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ゆうや</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -24113,19 +25073,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -24133,19 +25093,19 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>よしお</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -24153,19 +25113,19 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -24173,19 +25133,19 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -24205,7 +25165,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -24213,19 +25173,19 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>よしお</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -24233,19 +25193,19 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -24253,19 +25213,19 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -24273,19 +25233,19 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -24293,19 +25253,19 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -24313,19 +25273,19 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -24345,7 +25305,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>るい</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -24353,19 +25313,19 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -24373,19 +25333,19 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ろくじ</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -24393,19 +25353,19 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -24413,19 +25373,19 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>アナルプリンス</t>
+          <t>るい</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -24433,19 +25393,19 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -24453,19 +25413,19 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>カミさん</t>
+          <t>ろくじ</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -24473,19 +25433,19 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -24493,19 +25453,19 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>カー</t>
+          <t>アナルプリンス</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -24513,19 +25473,19 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -24545,7 +25505,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>キムとどえむちゃん</t>
+          <t>カミさん</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -24553,19 +25513,19 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -24573,19 +25533,19 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>キムと新しい奴隷ちゃん</t>
+          <t>カー</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -24593,19 +25553,19 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -24613,19 +25573,19 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>キムとどえむちゃん</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -24633,19 +25593,19 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>キムとドMまゆ</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -24653,19 +25613,19 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -24673,19 +25633,19 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -24693,19 +25653,19 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -24725,7 +25685,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -24733,19 +25693,19 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -24753,19 +25713,19 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -24773,19 +25733,19 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -24793,19 +25753,19 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>マイナス</t>
+          <t>ダイチ</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -24813,19 +25773,19 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>テクノとポチ</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -24833,19 +25793,19 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>トニー・トニー・チョッパー</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -24853,19 +25813,19 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>マナティ</t>
+          <t>ナカヤマヤ</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -24873,19 +25833,19 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -24893,19 +25853,19 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ユッキー</t>
+          <t>ボンタ</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -24913,19 +25873,19 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ロタポジ</t>
+          <t>マイナス</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -24933,19 +25893,19 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>マサ</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -24953,19 +25913,19 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -24973,19 +25933,19 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>海砂利水魚</t>
+          <t>マナティ</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -24993,19 +25953,19 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -25013,30 +25973,190 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
+          <t>ユッキー</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>ロタポジ</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>1</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>僕と私</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>名無し</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>1</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>女子三人衆</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>1</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>海砂利水魚</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>1</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>絶</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>1</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
           <t>赤ちゃん</t>
         </is>
       </c>
-      <c r="B210" t="n">
-        <v>1</v>
-      </c>
-      <c r="C210" t="inlineStr">
+      <c r="B218" t="n">
+        <v>1</v>
+      </c>
+      <c r="C218" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D218" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -25080,10 +26200,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -25158,10 +26278,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C8" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -25202,10 +26322,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -25215,10 +26335,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -25228,10 +26348,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -25410,10 +26530,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -25436,10 +26556,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -25462,10 +26582,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -25475,10 +26595,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C23" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24">
@@ -25488,10 +26608,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25">
@@ -25501,10 +26621,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -25550,13 +26670,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="C2" t="n">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D2" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -25570,7 +26690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25638,12 +26758,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -25653,12 +26773,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -25668,12 +26788,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -25683,12 +26803,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -25698,12 +26818,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -25713,12 +26833,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -25728,12 +26848,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -25743,12 +26863,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -25758,12 +26878,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>zin</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>−</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -25773,12 +26893,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>彩</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -25788,12 +26908,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -25803,12 +26923,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -25818,12 +26938,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -25833,12 +26953,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>カミさん</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -25848,12 +26968,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>zin</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -25863,12 +26983,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -25878,12 +26998,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -25893,12 +27013,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -25908,12 +27028,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -25923,12 +27043,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>カミさん</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -25938,12 +27058,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>さとるん</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -25953,12 +27073,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -25968,12 +27088,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>おにゃん</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ひがん</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -25983,12 +27103,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -25998,12 +27118,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -26013,12 +27133,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -26028,12 +27148,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>さとるん</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -26043,12 +27163,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -26058,12 +27178,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>おにゃん</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>ひがん</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -26073,12 +27193,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -26088,12 +27208,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -26103,12 +27223,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>こうた</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>まゆ</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -26118,12 +27238,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -26133,12 +27253,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -26148,12 +27268,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -26163,12 +27283,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>しょうた</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -26178,12 +27298,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -26193,12 +27313,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>こうた</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>まゆ</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -26208,12 +27328,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -26223,12 +27343,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -26238,12 +27358,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -26253,12 +27373,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>しょうた</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -26268,12 +27388,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -26283,12 +27403,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -26298,12 +27418,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -26313,12 +27433,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ともや</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -26328,12 +27448,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -26343,12 +27463,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -26358,12 +27478,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -26373,12 +27493,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -26388,12 +27508,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -26403,12 +27523,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -26418,12 +27538,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ゆずき</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -26433,12 +27553,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -26448,12 +27568,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -26463,12 +27583,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -26478,12 +27598,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -26493,12 +27613,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -26508,12 +27628,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>ゆずき</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -26523,12 +27643,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -26538,12 +27658,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -26553,12 +27673,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -26568,12 +27688,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -26583,12 +27703,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>絶</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -26598,12 +27718,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -26613,12 +27733,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -26628,12 +27748,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -26643,12 +27763,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -26658,12 +27778,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -26673,12 +27793,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -26688,12 +27808,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -26703,12 +27823,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -26718,12 +27838,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -26733,12 +27853,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -26748,15 +27868,105 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>ゆり</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>りえ</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>よっしー</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ザッキー</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>りく</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>アキ</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>コオリ</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>カズ</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ダイゴ</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>タカス</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>マサ</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>テクノ</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>ミコト</t>
         </is>
       </c>
-      <c r="C79" t="n">
+      <c r="C85" t="n">
         <v>1</v>
       </c>
     </row>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H254"/>
+  <dimension ref="A1:H263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8007,7 +8007,6 @@
           <t>キムとドMまゆ</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
           <t>遅い時間に</t>
@@ -8018,7 +8017,6 @@
           <t>来店します</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -8039,7 +8037,6 @@
           <t>トニー・トニー・チョッパー</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
           <t>これから</t>
@@ -8050,7 +8047,6 @@
           <t>いきます</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -8071,7 +8067,6 @@
           <t>僕と私</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
           <t>密かな</t>
@@ -8082,7 +8077,6 @@
           <t>イベント楽しみに＾＾</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -8103,7 +8097,6 @@
           <t>M、T、A、R</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
           <t>みんなで</t>
@@ -8114,7 +8107,6 @@
           <t>きたよーん</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -8135,7 +8127,6 @@
           <t>名無し</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>アナル野菜</t>
@@ -8146,7 +8137,6 @@
           <t>見に来ました</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -8167,7 +8157,6 @@
           <t>よしおたん</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>今</t>
@@ -8178,7 +8167,6 @@
           <t>きたよーん</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -8199,7 +8187,6 @@
           <t>しょうた</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>呼ばれて</t>
@@ -8210,7 +8197,6 @@
           <t>きたよー</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -8231,7 +8217,6 @@
           <t>あんこ</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>ひさしぶりに</t>
@@ -8242,7 +8227,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -8263,7 +8247,6 @@
           <t>みなっち</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>このあと</t>
@@ -8274,7 +8257,6 @@
           <t>縛りに行くよん</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -8295,7 +8277,6 @@
           <t>コテッチャン</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
           <t>今</t>
@@ -8306,7 +8287,6 @@
           <t>きたんご</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -8327,7 +8307,6 @@
           <t>ひがんちゃん</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>そういや</t>
@@ -8338,7 +8317,6 @@
           <t>少し前にきた</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -8392,6 +8370,314 @@
         </is>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>27181</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>19:14:54</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>bee</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>ドカ食い気絶部が</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>きましたよ</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>27183</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>19:43:20</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>もっぷ</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>お休みだから</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>きたよーん♪</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>27185</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>20:26:31</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>ますみ、ジョーカー</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>二回目</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>ふたりで来ました！</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>27187</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>21:02:43</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>S,R</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>飲みに</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>来ましたー！！</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>27188</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>21:37:48</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>今日は早めに</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>きたお</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>27191</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>23:06:37</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>あさみ</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>ご飯食べに</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>きたよー♪</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>27192</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>23:07:01</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>カズ、TKC</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>27195</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>00:07:43</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>べー</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>アナリスト</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>27197</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>03:50:48</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>欲求不満のポコチンハンター　える</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの火曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>本日8月25日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+欲求不満のポコチンハンター　える
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>img20260825035048.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8403,7 +8689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I311"/>
+  <dimension ref="A1:I322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21783,6 +22069,479 @@
       <c r="I311" t="inlineStr">
         <is>
           <t>少し前にきた</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>19:14:54</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>27181</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>bee</t>
+        </is>
+      </c>
+      <c r="F312" t="n">
+        <v>2</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>bee</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>ドカ食い気絶部が</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>きましたよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>19:43:20</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>27183</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>もっぷ</t>
+        </is>
+      </c>
+      <c r="F313" t="n">
+        <v>1</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>もっぷ</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>お休みだから</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>きたよーん♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>20:26:31</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>27185</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>ますみ</t>
+        </is>
+      </c>
+      <c r="F314" t="n">
+        <v>1</v>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>ますみ、ジョーカー</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>二回目</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>ふたりで来ました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>20:26:31</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>27185</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>ジョーカー</t>
+        </is>
+      </c>
+      <c r="F315" t="n">
+        <v>1</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>ますみ、ジョーカー</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>二回目</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>ふたりで来ました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>21:02:43</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>27187</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F316" t="n">
+        <v>3</v>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>S,R</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>飲みに</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>来ましたー！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>21:02:43</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>27187</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F317" t="n">
+        <v>2</v>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>S,R</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>飲みに</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>来ましたー！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>21:37:48</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>27188</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="F318" t="n">
+        <v>5</v>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>今日は早めに</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>きたお</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>23:06:37</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>27191</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>あさみ</t>
+        </is>
+      </c>
+      <c r="F319" t="n">
+        <v>1</v>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>あさみ</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>ご飯食べに</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>きたよー♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>23:07:01</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>27192</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>カズ</t>
+        </is>
+      </c>
+      <c r="F320" t="n">
+        <v>3</v>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>カズ、TKC</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>23:07:01</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>27192</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>TKC</t>
+        </is>
+      </c>
+      <c r="F321" t="n">
+        <v>2</v>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>カズ、TKC</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>00:07:43</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>27195</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>べー</t>
+        </is>
+      </c>
+      <c r="F322" t="n">
+        <v>1</v>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>べー</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>アナリスト</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>来ました！</t>
         </is>
       </c>
     </row>
@@ -21797,7 +22556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D218"/>
+  <dimension ref="A1:D223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21905,27 +22664,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>たいせい</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -21945,7 +22704,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>たいせい</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -21953,19 +22712,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -21978,14 +22737,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>みなっち</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -21993,19 +22752,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>みなっち</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -22013,12 +22772,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -22045,7 +22804,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>zin</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -22053,19 +22812,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>zin</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -22073,19 +22832,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -22093,7 +22852,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -22105,7 +22864,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -22113,7 +22872,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -22125,7 +22884,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>よしおたん</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -22133,19 +22892,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>よしおたん</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -22153,19 +22912,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -22173,59 +22932,59 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>コテッチャン</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>彩</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -22233,19 +22992,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -22253,19 +23012,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -22273,19 +23032,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -22298,14 +23057,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -22313,19 +23072,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>TKC</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -22333,19 +23092,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -22353,19 +23112,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -22373,19 +23132,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -22398,14 +23157,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>しょうた</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -22413,19 +23172,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>しーたん</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -22433,19 +23192,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -22453,7 +23212,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -22465,7 +23224,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -22473,19 +23232,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>たかやまん</t>
+          <t>しょうた</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -22493,19 +23252,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>たつや</t>
+          <t>しーたん</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -22513,19 +23272,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>でで</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -22533,19 +23292,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -22553,19 +23312,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>たかやまん</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -22573,7 +23332,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -22585,7 +23344,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>たつや</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -22593,19 +23352,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>でで</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -22613,19 +23372,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -22638,14 +23397,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -22653,19 +23412,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ゆずきん</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -22673,19 +23432,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -22693,7 +23452,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -22705,7 +23464,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -22713,19 +23472,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>よっち</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -22733,19 +23492,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>ゆずきん</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -22753,19 +23512,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -22773,19 +23532,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>れいら</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -22793,7 +23552,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -22805,7 +23564,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>よっち</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -22818,14 +23577,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>タツヤ</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -22833,19 +23592,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>マッスル</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -22853,19 +23612,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>マロ</t>
+          <t>れいら</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -22873,7 +23632,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -22885,7 +23644,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>愛とスケベの戦士</t>
+          <t>タツヤ</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -22893,43 +23652,43 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>マッスル</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>マロ</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -22938,34 +23697,34 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>愛とスケベの戦士</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -22973,19 +23732,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -22993,19 +23752,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -23013,19 +23772,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -23033,19 +23792,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -23053,19 +23812,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TKC</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -23073,19 +23832,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -23093,19 +23852,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -23113,19 +23872,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -23133,12 +23892,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -23205,7 +23964,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>あさみ</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -23213,19 +23972,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -23233,19 +23992,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>あんこ</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -23253,19 +24012,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>うらら</t>
+          <t>あんこ</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -23273,19 +24032,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>うらら</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -23293,19 +24052,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>おじきち</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -23325,7 +24084,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
+          <t>おじきち</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -23333,19 +24092,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>おでで</t>
+          <t>おちんぽベルセルク</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -23353,19 +24112,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>おにゃん</t>
+          <t>おでで</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -23385,7 +24144,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>おにゃん</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -23393,19 +24152,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>かける</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -23413,19 +24172,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>かける</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -23433,19 +24192,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -23453,19 +24212,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>かな(絶ちゃん)/おっつん</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -23473,19 +24232,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>きむむ</t>
+          <t>かな(絶ちゃん)/おっつん</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -23493,19 +24252,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>きむむ</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -23513,19 +24272,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -23533,19 +24292,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -23553,19 +24312,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>けん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -23585,7 +24344,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>けん</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -23593,19 +24352,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>こうた</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -23613,19 +24372,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>こてっちゃん</t>
+          <t>こうた</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -23633,19 +24392,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>こてっちゃん</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -23653,19 +24412,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -23673,19 +24432,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -23693,19 +24452,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>さと</t>
+          <t>さくら</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -23713,19 +24472,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>さとるん</t>
+          <t>さと</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -23745,7 +24504,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>さとるん</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -23753,19 +24512,19 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>しゅん</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -23773,19 +24532,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>しん</t>
+          <t>しゅん</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -23793,19 +24552,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>すず</t>
+          <t>しん</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -23825,7 +24584,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>すず</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -23845,7 +24604,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -23853,19 +24612,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -23873,19 +24632,19 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -23893,19 +24652,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>たけし</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -23913,19 +24672,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>たけし</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -23933,19 +24692,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>だいご</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -23953,19 +24712,19 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>だいご</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -23985,7 +24744,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -23993,19 +24752,19 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -24013,19 +24772,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ちっち</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -24033,19 +24792,19 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ちゃそたけ</t>
+          <t>ちっち</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -24053,19 +24812,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>ちゃそたけ</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -24073,19 +24832,19 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -24093,19 +24852,19 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>てつじ</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -24113,19 +24872,19 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>てつじ</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -24133,19 +24892,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -24153,19 +24912,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>とっしー</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -24173,19 +24932,19 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>とっしー</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -24193,19 +24952,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ともや</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -24213,19 +24972,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -24233,19 +24992,19 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -24253,19 +25012,19 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -24273,19 +25032,19 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>なな</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -24293,19 +25052,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>なまがき</t>
+          <t>なな</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -24313,19 +25072,19 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>にこちん</t>
+          <t>なまがき</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -24333,19 +25092,19 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>にょ</t>
+          <t>にこちん</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -24353,19 +25112,19 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>にょ</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -24373,19 +25132,19 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -24393,19 +25152,19 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>はち</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -24413,19 +25172,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>はな</t>
+          <t>はち</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -24433,19 +25192,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>はなまる</t>
+          <t>はな</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -24453,19 +25212,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ひがんたん</t>
+          <t>はなまる</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -24473,19 +25232,19 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ひがんちゃん</t>
+          <t>ひがんたん</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -24493,19 +25252,19 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>ひがんちゃん</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -24513,19 +25272,19 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -24533,19 +25292,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -24553,19 +25312,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -24573,19 +25332,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -24605,7 +25364,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ぽちゃりす組</t>
+          <t>べー</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -24613,19 +25372,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>まいなす</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -24633,19 +25392,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>ぽちゃりす組</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -24665,7 +25424,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>まいなす</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -24673,19 +25432,19 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>まっする</t>
+          <t>まいまいん</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -24693,19 +25452,19 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>まっぴー</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -24713,19 +25472,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>まゆ</t>
+          <t>ますみ</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -24733,19 +25492,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>まっする</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -24765,7 +25524,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>まっぴー</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -24773,19 +25532,19 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>まーさん</t>
+          <t>まゆ</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -24793,19 +25552,19 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>みかん</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -24813,19 +25572,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -24833,19 +25592,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>まーさん</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -24853,19 +25612,19 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>みなつちん</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -24885,7 +25644,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>みるこ</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -24893,19 +25652,19 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -24913,19 +25672,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -24933,19 +25692,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>もかちんぽぽ</t>
+          <t>みるこ</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -24953,19 +25712,19 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -24973,19 +25732,19 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>やえ</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -24993,19 +25752,19 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ゆうくん</t>
+          <t>もかちんぽぽ</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -25013,19 +25772,19 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>もっぷ</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -25033,19 +25792,19 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -25053,19 +25812,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ゆうや</t>
+          <t>やえ</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -25073,19 +25832,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ゆうくん</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -25105,7 +25864,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -25113,19 +25872,19 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -25133,19 +25892,19 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ゆうや</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -25153,19 +25912,19 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -25173,19 +25932,19 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>よしお</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -25193,19 +25952,19 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -25213,19 +25972,19 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -25245,7 +26004,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -25253,19 +26012,19 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>よしお</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -25273,19 +26032,19 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -25293,19 +26052,19 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -25313,19 +26072,19 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -25333,19 +26092,19 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -25353,19 +26112,19 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -25385,7 +26144,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>るい</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -25393,19 +26152,19 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -25413,19 +26172,19 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ろくじ</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -25433,19 +26192,19 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -25453,19 +26212,19 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>アナルプリンス</t>
+          <t>るい</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -25473,19 +26232,19 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -25493,19 +26252,19 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>カミさん</t>
+          <t>ろくじ</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -25513,19 +26272,19 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -25533,19 +26292,19 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>カー</t>
+          <t>アナルプリンス</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -25553,19 +26312,19 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -25585,7 +26344,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>キムとどえむちゃん</t>
+          <t>カミさん</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -25593,19 +26352,19 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>キムとドMまゆ</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -25613,19 +26372,19 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>カー</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -25633,19 +26392,19 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>キムと新しい奴隷ちゃん</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -25653,19 +26412,19 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>キムとどえむちゃん</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -25673,19 +26432,19 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>キムとドMまゆ</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -25693,19 +26452,19 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -25713,19 +26472,19 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -25745,7 +26504,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -25753,19 +26512,19 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -25773,19 +26532,19 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -25793,19 +26552,19 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>トニー・トニー・チョッパー</t>
+          <t>ジョーカー</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -25813,19 +26572,19 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -25833,19 +26592,19 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -25853,19 +26612,19 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>ダイチ</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -25873,19 +26632,19 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>マイナス</t>
+          <t>テクノとポチ</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -25893,19 +26652,19 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>トニー・トニー・チョッパー</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -25913,19 +26672,19 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ナカヤマヤ</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -25933,19 +26692,19 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>マナティ</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -25965,7 +26724,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>ボンタ</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -25973,19 +26732,19 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ユッキー</t>
+          <t>マイナス</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -25993,19 +26752,19 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ロタポジ</t>
+          <t>マサ</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -26013,19 +26772,19 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>僕と私</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -26033,19 +26792,19 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>名無し</t>
+          <t>マナティ</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -26053,19 +26812,19 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -26085,7 +26844,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>ユッキー</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -26093,19 +26852,19 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>海砂利水魚</t>
+          <t>ロタポジ</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -26113,19 +26872,19 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>僕と私</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -26133,30 +26892,130 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
+          <t>名無し</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>1</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>女子三人衆</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>海砂利水魚</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>1</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>絶</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
           <t>赤ちゃん</t>
         </is>
       </c>
-      <c r="B218" t="n">
-        <v>1</v>
-      </c>
-      <c r="C218" t="inlineStr">
+      <c r="B223" t="n">
+        <v>1</v>
+      </c>
+      <c r="C223" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -26200,10 +27059,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -26213,10 +27072,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -26322,10 +27181,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -26569,10 +27428,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
@@ -26582,10 +27441,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C22" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
@@ -26595,10 +27454,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C23" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24">
@@ -26621,10 +27480,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C25" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -26670,13 +27529,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C2" t="n">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="D2" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -26690,7 +27549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26913,7 +27772,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -26923,12 +27782,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -26943,7 +27802,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -26953,12 +27812,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -26968,12 +27827,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>zin</t>
+          <t>TKC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -26983,12 +27842,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -26998,12 +27857,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>zin</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -27013,12 +27872,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -27028,12 +27887,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -27043,12 +27902,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>カミさん</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -27058,12 +27917,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -27073,12 +27932,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>カミさん</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -27093,7 +27952,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -27108,7 +27967,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -27123,7 +27982,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -27133,12 +27992,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -27148,12 +28007,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>さとるん</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -27163,12 +28022,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -27178,12 +28037,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>おにゃん</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ひがん</t>
+          <t>さとるん</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -27193,12 +28052,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -27208,12 +28067,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>おにゃん</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>ひがん</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -27223,12 +28082,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -27238,12 +28097,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -27258,7 +28117,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -27268,12 +28127,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -27283,12 +28142,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -27298,12 +28157,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -27313,12 +28172,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>こうた</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>まゆ</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -27328,12 +28187,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -27343,12 +28202,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>こうた</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>まゆ</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -27358,12 +28217,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -27373,12 +28232,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>しょうた</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -27388,12 +28247,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -27403,12 +28262,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>しょうた</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -27418,12 +28277,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -27433,12 +28292,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -27448,12 +28307,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -27463,12 +28322,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -27478,12 +28337,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -27493,12 +28352,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -27508,12 +28367,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -27523,12 +28382,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ともや</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -27538,12 +28397,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -27553,12 +28412,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -27568,12 +28427,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -27583,12 +28442,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -27598,12 +28457,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -27613,12 +28472,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -27628,12 +28487,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ゆずき</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -27643,12 +28502,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -27663,7 +28522,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>ゆずき</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -27673,12 +28532,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -27688,12 +28547,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -27708,7 +28567,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -27718,12 +28577,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -27733,12 +28592,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>絶</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -27748,12 +28607,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>ますみ</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>ジョーカー</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -27763,12 +28622,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -27778,12 +28637,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -27793,12 +28652,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -27808,12 +28667,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -27823,12 +28682,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -27838,12 +28697,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -27853,12 +28712,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -27868,12 +28727,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -27883,12 +28742,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -27898,12 +28757,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -27913,12 +28772,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -27928,12 +28787,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -27943,12 +28802,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -27958,15 +28817,60 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>アキ</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>コオリ</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>カズ</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ダイゴ</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>タカス</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>マサ</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>テクノ</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>ミコト</t>
         </is>
       </c>
-      <c r="C85" t="n">
+      <c r="C88" t="n">
         <v>1</v>
       </c>
     </row>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H263"/>
+  <dimension ref="A1:H290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8389,7 +8389,6 @@
           <t>bee</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
           <t>ドカ食い気絶部が</t>
@@ -8400,7 +8399,6 @@
           <t>きましたよ</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -8421,7 +8419,6 @@
           <t>もっぷ</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
           <t>お休みだから</t>
@@ -8432,7 +8429,6 @@
           <t>きたよーん♪</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -8453,7 +8449,6 @@
           <t>ますみ、ジョーカー</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
           <t>二回目</t>
@@ -8464,7 +8459,6 @@
           <t>ふたりで来ました！</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -8485,7 +8479,6 @@
           <t>S,R</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
           <t>飲みに</t>
@@ -8496,7 +8489,6 @@
           <t>来ましたー！！</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -8517,7 +8509,6 @@
           <t>テクノ</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
           <t>今日は早めに</t>
@@ -8528,7 +8519,6 @@
           <t>きたお</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -8549,7 +8539,6 @@
           <t>あさみ</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
           <t>ご飯食べに</t>
@@ -8560,7 +8549,6 @@
           <t>きたよー♪</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -8581,7 +8569,6 @@
           <t>カズ、TKC</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
           <t>遊びに</t>
@@ -8592,7 +8579,6 @@
           <t>来ました！</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -8613,7 +8599,6 @@
           <t>べー</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
           <t>アナリスト</t>
@@ -8624,7 +8609,6 @@
           <t>来ました！</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -8678,6 +8662,912 @@
         </is>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>27199</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>19:11:23</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>オカニー</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>今から3人で行きたいです。</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>本日3人で行きたいです。
+よろしくお願いいたします。</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>27200</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>19:33:51</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>マロ</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>今日はラストまで</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>いまーす！</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>27201</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>19:45:17</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>彩、なまがき</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>きたよー！</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>27205</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>19:47:46</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>オカニー、ミッシ、ダイキ</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>楽しみます！！</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>27206</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>20:13:26</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>ヨシヤ</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>初めてです！</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>きてみました！</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>27207</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>20:13:45</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>よしお</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>すこしだお</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>27211</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>22:07:30</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>けい、さや</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>お初カップルです！</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>はじめてきました！</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>27212</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>22:08:36</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>リョウ、タク</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>27213</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>22:10:32</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>TARU</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>出張帰りに</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>きたよ！</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>27217</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>22:43:12</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>飲むぞーーー！！</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>27219</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>01:25:08</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>がん</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>27220</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>01:51:24</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>モジャ、さない</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>きましたー！！</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>27223</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>02:13:45</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>かず</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>きたぜ</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>27225</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>04:25:41</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>ツッコミはお任せのShizu / えちえち裏垢女子のモカチ</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの水曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>本日8月25日の営業時間は♪
+オープン14:00！ラスト5:00なのよ☆
+担当は
+ツッコミはお任せのShizu
+えちえち裏垢女子のモカチ
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>img20260826042541.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>27227</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>14:10:41</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>zin</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>オープン凸</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>すこしだけ</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>27229</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>16:16:42</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>みみ</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>いきます</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>27230</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>16:24:28</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>ひるばんび</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>27231</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>16:24:50</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>のんのん</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>わたしも</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>ひるばんび！</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>27235</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>17:26:25</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>T山</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>しごまえ</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>きたわよ</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>27237</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>17:38:46</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>きた！</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>27239</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>18:16:18</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>らお</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>はやめに</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>27241</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>18:51:33</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>ゆずきん</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>連チャン</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>きた！</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>27243</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>20:13:04</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>あそびに</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>27245</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>22:14:27</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>とし</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>きたよん</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>27247</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>23:48:09</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>てくのっち</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>きまんこ</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>27248</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>23:49:19</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>ふくてゃ</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>きちゃ</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>27251</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>03:01:40</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>ツッコミはお任せのShizu</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの木曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>本日8月26日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+ツッコミはお任せのShizu
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>img20260827030140.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8689,7 +9579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I322"/>
+  <dimension ref="A1:I353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22542,6 +23432,1340 @@
       <c r="I322" t="inlineStr">
         <is>
           <t>来ました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>19:11:23</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>27199</v>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>オカニー</t>
+        </is>
+      </c>
+      <c r="F323" t="n">
+        <v>1</v>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>オカニー</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>今から3人で行きたいです。</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>本日3人で行きたいです。
+よろしくお願いいたします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>19:33:51</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>27200</v>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>マロ</t>
+        </is>
+      </c>
+      <c r="F324" t="n">
+        <v>3</v>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>マロ</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>今日はラストまで</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>いまーす！</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>19:45:17</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>27201</v>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="F325" t="n">
+        <v>4</v>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>彩、なまがき</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>きたよー！</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>19:45:17</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>27201</v>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>なまがき</t>
+        </is>
+      </c>
+      <c r="F326" t="n">
+        <v>2</v>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>彩、なまがき</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>きたよー！</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>19:47:46</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>27205</v>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>オカニー</t>
+        </is>
+      </c>
+      <c r="F327" t="n">
+        <v>2</v>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>オカニー、ミッシ、ダイキ</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>楽しみます！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>19:47:46</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>27205</v>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>ミッシ</t>
+        </is>
+      </c>
+      <c r="F328" t="n">
+        <v>1</v>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>オカニー、ミッシ、ダイキ</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>楽しみます！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>19:47:46</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>27205</v>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>ダイキ</t>
+        </is>
+      </c>
+      <c r="F329" t="n">
+        <v>1</v>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>オカニー、ミッシ、ダイキ</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>楽しみます！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>20:13:26</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>27206</v>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>ヨシヤ</t>
+        </is>
+      </c>
+      <c r="F330" t="n">
+        <v>1</v>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>ヨシヤ</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>初めてです！</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>きてみました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>20:13:45</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>27207</v>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>よしお</t>
+        </is>
+      </c>
+      <c r="F331" t="n">
+        <v>2</v>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>よしお</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>すこしだお</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>22:07:30</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>27211</v>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>けい</t>
+        </is>
+      </c>
+      <c r="F332" t="n">
+        <v>1</v>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>けい、さや</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>お初カップルです！</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>はじめてきました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>22:07:30</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>27211</v>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>さや</t>
+        </is>
+      </c>
+      <c r="F333" t="n">
+        <v>1</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>けい、さや</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>お初カップルです！</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>はじめてきました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>22:08:36</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>27212</v>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>リョウ</t>
+        </is>
+      </c>
+      <c r="F334" t="n">
+        <v>1</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>リョウ、タク</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>22:08:36</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>27212</v>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>タク</t>
+        </is>
+      </c>
+      <c r="F335" t="n">
+        <v>1</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>リョウ、タク</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>22:10:32</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>27213</v>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>TARU</t>
+        </is>
+      </c>
+      <c r="F336" t="n">
+        <v>1</v>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>TARU</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>出張帰りに</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>きたよ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>22:43:12</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>27217</v>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="F337" t="n">
+        <v>6</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>飲むぞーーー！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>01:25:08</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>27219</v>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>がん</t>
+        </is>
+      </c>
+      <c r="F338" t="n">
+        <v>1</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>がん</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>01:51:24</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>27220</v>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>モジャ</t>
+        </is>
+      </c>
+      <c r="F339" t="n">
+        <v>1</v>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>モジャ、さない</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>きましたー！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>01:51:24</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>27220</v>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>さない</t>
+        </is>
+      </c>
+      <c r="F340" t="n">
+        <v>1</v>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>モジャ、さない</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>きましたー！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>02:13:45</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>27223</v>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>かず</t>
+        </is>
+      </c>
+      <c r="F341" t="n">
+        <v>2</v>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>かず</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>きたぜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>14:10:41</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>27227</v>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>zin</t>
+        </is>
+      </c>
+      <c r="F342" t="n">
+        <v>4</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>zin</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>オープン凸</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>すこしだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>16:16:42</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>27229</v>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>みみ</t>
+        </is>
+      </c>
+      <c r="F343" t="n">
+        <v>1</v>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>みみ</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>いきます</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>16:24:28</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>27230</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="F344" t="n">
+        <v>5</v>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>ひるばんび</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>16:24:50</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>27231</v>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>のんのん</t>
+        </is>
+      </c>
+      <c r="F345" t="n">
+        <v>3</v>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>のんのん</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>わたしも</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>ひるばんび！</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>17:26:25</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>27235</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>T山</t>
+        </is>
+      </c>
+      <c r="F346" t="n">
+        <v>2</v>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>T山</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>しごまえ</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>きたわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>17:38:46</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>27237</v>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F347" t="n">
+        <v>3</v>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>きた！</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>18:16:18</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>27239</v>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>らお</t>
+        </is>
+      </c>
+      <c r="F348" t="n">
+        <v>1</v>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>らお</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>はやめに</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>18:51:33</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>27241</v>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>ゆずきん</t>
+        </is>
+      </c>
+      <c r="F349" t="n">
+        <v>3</v>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>ゆずきん</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>連チャン</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>きた！</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>20:13:04</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>27243</v>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="F350" t="n">
+        <v>9</v>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>あそびに</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>22:14:27</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>27245</v>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>とし</t>
+        </is>
+      </c>
+      <c r="F351" t="n">
+        <v>1</v>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>とし</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>きたよん</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>23:48:09</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>27247</v>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>てくのっち</t>
+        </is>
+      </c>
+      <c r="F352" t="n">
+        <v>1</v>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>てくのっち</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>きまんこ</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>23:49:19</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>27248</v>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>ふくてゃ</t>
+        </is>
+      </c>
+      <c r="F353" t="n">
+        <v>5</v>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>ふくてゃ</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>きちゃ</t>
         </is>
       </c>
     </row>
@@ -22556,7 +24780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22588,7 +24812,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -22597,7 +24821,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -22644,27 +24868,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -22672,27 +24896,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -22704,27 +24928,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>たいせい</t>
+          <t>彩</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>zin</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -22732,19 +24956,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -22752,7 +24976,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -22764,7 +24988,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>みなっち</t>
+          <t>たいせい</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -22777,18 +25001,18 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -22797,22 +25021,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>みなっち</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -22824,7 +25048,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>zin</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -22832,19 +25056,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -22852,7 +25076,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -22864,7 +25088,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -22877,14 +25101,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -22892,7 +25116,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -22904,7 +25128,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>よしおたん</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -22912,19 +25136,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -22932,19 +25156,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -22952,19 +25176,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>ゆずきん</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -22972,23 +25196,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>よしおたん</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -23004,51 +25228,51 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>コテッチャン</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>マロ</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -23057,14 +25281,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -23072,19 +25296,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TKC</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -23092,19 +25316,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -23112,19 +25336,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -23132,19 +25356,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>TKC</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -23152,19 +25376,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -23177,14 +25401,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -23192,19 +25416,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -23212,19 +25436,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -23237,14 +25461,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>しょうた</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -23252,19 +25476,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>しーたん</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -23272,19 +25496,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -23292,19 +25516,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -23312,19 +25536,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>たかやまん</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -23332,19 +25556,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>たつや</t>
+          <t>しょうた</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -23352,19 +25576,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>でで</t>
+          <t>しーたん</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -23372,7 +25596,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -23384,7 +25608,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -23397,14 +25621,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -23412,7 +25636,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -23424,7 +25648,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>たかやまん</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -23432,19 +25656,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>たつや</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -23452,19 +25676,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>でで</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -23472,19 +25696,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>なまがき</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -23497,14 +25721,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ゆずきん</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -23512,7 +25736,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -23524,7 +25748,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -23532,19 +25756,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -23552,19 +25776,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>よっち</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -23572,19 +25796,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -23592,19 +25816,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>よしお</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -23612,19 +25836,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>れいら</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -23632,19 +25856,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>タツヤ</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -23652,19 +25876,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>マッスル</t>
+          <t>よっち</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -23672,19 +25896,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>マロ</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -23692,7 +25916,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -23704,7 +25928,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>愛とスケベの戦士</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -23712,119 +25936,119 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>れいら</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>オカニー</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>タツヤ</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>マッスル</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>愛とスケベの戦士</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -23832,19 +26056,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -23852,19 +26076,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -23872,19 +26096,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -23892,19 +26116,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>nuri</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -23912,19 +26136,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -23932,19 +26156,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>★Zakk★</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -23952,19 +26176,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>あさみ</t>
+          <t>TARU</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -23972,19 +26196,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -24004,7 +26228,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>nuri</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -24012,19 +26236,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>あんこ</t>
+          <t>−</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -24032,19 +26256,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>うらら</t>
+          <t>★Zakk★</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -24064,7 +26288,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>あさみ</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -24072,19 +26296,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>おじきち</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -24104,7 +26328,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -24124,7 +26348,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>おでで</t>
+          <t>あんこ</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -24132,19 +26356,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>おにゃん</t>
+          <t>うらら</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -24152,19 +26376,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -24172,19 +26396,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>かける</t>
+          <t>おじきち</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -24192,19 +26416,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>おちんぽベルセルク</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -24212,19 +26436,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>おでで</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -24232,19 +26456,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>かな(絶ちゃん)/おっつん</t>
+          <t>おにゃん</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -24252,19 +26476,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>きむむ</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -24272,19 +26496,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>かける</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -24292,19 +26516,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -24312,19 +26536,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>かな(絶ちゃん)/おっつん</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -24332,19 +26556,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>けん</t>
+          <t>がん</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -24352,19 +26576,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>きむむ</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -24372,19 +26596,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>こうた</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -24392,19 +26616,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>こてっちゃん</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -24412,19 +26636,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -24444,7 +26668,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>けい</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -24452,19 +26676,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>けん</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -24472,19 +26696,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>さと</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -24492,19 +26716,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>さとるん</t>
+          <t>こうた</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -24524,7 +26748,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>こてっちゃん</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -24532,19 +26756,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>しゅん</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -24552,19 +26776,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>しん</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -24572,19 +26796,19 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>すず</t>
+          <t>さくら</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -24592,19 +26816,19 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>さと</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -24612,19 +26836,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>さとるん</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -24632,19 +26856,19 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>さない</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -24652,19 +26876,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>さや</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -24672,19 +26896,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>たけし</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -24692,19 +26916,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>しゅん</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -24712,19 +26936,19 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>だいご</t>
+          <t>しん</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -24732,19 +26956,19 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>すず</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -24752,19 +26976,19 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -24772,19 +26996,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -24804,7 +27028,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ちっち</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -24812,19 +27036,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ちゃそたけ</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -24832,19 +27056,19 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>たけし</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -24852,19 +27076,19 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -24872,19 +27096,19 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>てつじ</t>
+          <t>だいご</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -24892,19 +27116,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -24912,19 +27136,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -24932,19 +27156,19 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>とっしー</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -24952,19 +27176,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>ちっち</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -24972,19 +27196,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ともや</t>
+          <t>ちゃそたけ</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -24992,19 +27216,19 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>てくのっち</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -25012,19 +27236,19 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -25032,19 +27256,19 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -25052,19 +27276,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>なな</t>
+          <t>てつじ</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -25072,19 +27296,19 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>なまがき</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -25092,19 +27316,19 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>にこちん</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -25112,19 +27336,19 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>にょ</t>
+          <t>とし</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -25132,19 +27356,19 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>とっしー</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -25152,19 +27376,19 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -25172,19 +27396,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>はち</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -25192,19 +27416,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>はな</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -25212,19 +27436,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>はなまる</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -25232,19 +27456,19 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ひがんたん</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -25252,19 +27476,19 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ひがんちゃん</t>
+          <t>なな</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -25272,19 +27496,19 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>にこちん</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -25292,19 +27516,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>にょ</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -25312,19 +27536,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -25332,19 +27556,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -25352,19 +27576,19 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>べー</t>
+          <t>はち</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -25372,19 +27596,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>はな</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -25392,19 +27616,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ぽちゃりす組</t>
+          <t>はなまる</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -25412,19 +27636,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>まいなす</t>
+          <t>ひがんたん</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -25432,19 +27656,19 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>ひがんちゃん</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -25452,19 +27676,19 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -25472,19 +27696,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ますみ</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -25492,19 +27716,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>まっする</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -25512,19 +27736,19 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>まっぴー</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -25532,19 +27756,19 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>まゆ</t>
+          <t>べー</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -25552,19 +27776,19 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -25572,19 +27796,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>ぽちゃりす組</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -25592,19 +27816,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>まーさん</t>
+          <t>まいなす</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -25612,19 +27836,19 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>みかん</t>
+          <t>まいまいん</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -25632,19 +27856,19 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -25652,19 +27876,19 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>ますみ</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -25672,19 +27896,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>みなつちん</t>
+          <t>まっする</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -25692,19 +27916,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>みるこ</t>
+          <t>まっぴー</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -25712,19 +27936,19 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>まゆ</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -25732,19 +27956,19 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -25764,7 +27988,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>もかちんぽぽ</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -25772,19 +27996,19 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>もっぷ</t>
+          <t>まーさん</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -25792,19 +28016,19 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -25812,19 +28036,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>やえ</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -25832,19 +28056,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ゆうくん</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -25852,19 +28076,19 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -25872,19 +28096,19 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>みみ</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -25892,19 +28116,19 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ゆうや</t>
+          <t>みるこ</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -25912,19 +28136,19 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -25932,19 +28156,19 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -25952,19 +28176,19 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>もかちんぽぽ</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -25972,19 +28196,19 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>もっぷ</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -25992,19 +28216,19 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -26024,7 +28248,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>よしお</t>
+          <t>やえ</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -26032,19 +28256,19 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>ゆうくん</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -26052,19 +28276,19 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -26072,19 +28296,19 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -26092,19 +28316,19 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>ゆうや</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -26112,19 +28336,19 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -26132,19 +28356,19 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -26152,19 +28376,19 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -26172,19 +28396,19 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -26192,19 +28416,19 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -26212,19 +28436,19 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>るい</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -26232,19 +28456,19 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>らお</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -26252,19 +28476,19 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ろくじ</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -26272,19 +28496,19 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -26292,19 +28516,19 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>アナルプリンス</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -26312,19 +28536,19 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -26344,7 +28568,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>カミさん</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -26352,19 +28576,19 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -26372,19 +28596,19 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>カー</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -26392,19 +28616,19 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -26424,7 +28648,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>キムとどえむちゃん</t>
+          <t>るい</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -26432,19 +28656,19 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>キムとドMまゆ</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -26452,19 +28676,19 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>ろくじ</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -26472,19 +28696,19 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>キムと新しい奴隷ちゃん</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -26492,19 +28716,19 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>アナルプリンス</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -26512,19 +28736,19 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -26532,19 +28756,19 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>カミさん</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -26552,19 +28776,19 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ジョーカー</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -26572,19 +28796,19 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>カー</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -26592,19 +28816,19 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -26612,19 +28836,19 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>キムとどえむちゃん</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -26632,19 +28856,19 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>キムとドMまゆ</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -26652,19 +28876,19 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>トニー・トニー・チョッパー</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -26672,19 +28896,19 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -26692,19 +28916,19 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -26712,19 +28936,19 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -26732,19 +28956,19 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>マイナス</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -26752,19 +28976,19 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>ジョーカー</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -26772,19 +28996,19 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -26792,19 +29016,19 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>マナティ</t>
+          <t>タク</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -26812,19 +29036,19 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>ダイキ</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -26832,19 +29056,19 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ユッキー</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -26852,19 +29076,19 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ロタポジ</t>
+          <t>ダイチ</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -26872,19 +29096,19 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>僕と私</t>
+          <t>テクノとポチ</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -26892,19 +29116,19 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>名無し</t>
+          <t>トニー・トニー・チョッパー</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -26924,7 +29148,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>ナカヤマヤ</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -26932,19 +29156,19 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -26952,19 +29176,19 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>海砂利水魚</t>
+          <t>ボンタ</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -26972,19 +29196,19 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>マイナス</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -26992,30 +29216,350 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
+          <t>マサ</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>1</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>マッチョ</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>1</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>マナティ</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>1</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>1</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>ミッシ</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>1</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>モジャ</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>1</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>ユッキー</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>1</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>ヨシヤ</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>1</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>リョウ</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>1</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>ロタポジ</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>1</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>僕と私</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>1</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>名無し</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>1</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>1</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>女子三人衆</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>1</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>海砂利水魚</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>1</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>絶</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>1</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
           <t>赤ちゃん</t>
         </is>
       </c>
-      <c r="B223" t="n">
-        <v>1</v>
-      </c>
-      <c r="C223" t="inlineStr">
+      <c r="B239" t="n">
+        <v>1</v>
+      </c>
+      <c r="C239" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D239" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -27072,10 +29616,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -27085,10 +29629,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -27194,10 +29738,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
@@ -27207,10 +29751,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -27363,10 +29907,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -27389,10 +29933,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -27402,10 +29946,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -27415,10 +29959,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -27428,10 +29972,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C21" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22">
@@ -27441,10 +29985,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -27467,10 +30011,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C24" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25">
@@ -27480,10 +30024,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C25" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -27529,13 +30073,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="C2" t="n">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="D2" t="n">
-        <v>222</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -27549,7 +30093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28187,12 +30731,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>けい</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>さや</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -28202,12 +30746,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>こうた</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>まゆ</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -28217,12 +30761,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>こうた</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>まゆ</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -28232,12 +30776,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -28247,12 +30791,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -28262,12 +30806,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>しょうた</t>
+          <t>さない</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>モジャ</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -28277,12 +30821,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -28292,12 +30836,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>しょうた</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -28307,12 +30851,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -28322,12 +30866,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -28337,12 +30881,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -28352,12 +30896,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -28367,12 +30911,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -28382,12 +30926,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -28397,12 +30941,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -28412,12 +30956,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ともや</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -28427,12 +30971,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -28442,12 +30986,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -28457,12 +31001,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -28472,12 +31016,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -28487,12 +31031,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>なまがき</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>彩</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -28502,12 +31046,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -28517,12 +31061,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ゆずき</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -28532,12 +31076,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -28547,12 +31091,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -28562,12 +31106,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>ゆずき</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -28577,12 +31121,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -28592,12 +31136,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -28607,12 +31151,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ますみ</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ジョーカー</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -28622,12 +31166,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -28637,12 +31181,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>絶</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -28652,12 +31196,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>ますみ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>ジョーカー</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -28667,12 +31211,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -28682,12 +31226,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -28697,12 +31241,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -28712,12 +31256,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -28727,12 +31271,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -28742,12 +31286,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -28757,12 +31301,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -28772,12 +31316,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -28787,12 +31331,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -28802,12 +31346,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -28817,12 +31361,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -28832,12 +31376,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -28847,12 +31391,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -28862,15 +31406,120 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>アキ</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>コオリ</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>オカニー</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ダイキ</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>オカニー</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ミッシ</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>カズ</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ダイゴ</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>タカス</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>マサ</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>タク</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>リョウ</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ダイキ</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ミッシ</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>テクノ</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>ミコト</t>
         </is>
       </c>
-      <c r="C88" t="n">
+      <c r="C95" t="n">
         <v>1</v>
       </c>
     </row>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H290"/>
+  <dimension ref="A1:H304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8681,7 +8681,6 @@
           <t>オカニー</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>今から3人で行きたいです。</t>
@@ -8693,7 +8692,6 @@
 よろしくお願いいたします。</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -8714,7 +8712,6 @@
           <t>マロ</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
           <t>今日はラストまで</t>
@@ -8725,7 +8722,6 @@
           <t>いまーす！</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -8746,7 +8742,6 @@
           <t>彩、なまがき</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
           <t>いま</t>
@@ -8757,7 +8752,6 @@
           <t>きたよー！</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -8778,7 +8772,6 @@
           <t>オカニー、ミッシ、ダイキ</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -8789,7 +8782,6 @@
           <t>楽しみます！！</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -8810,7 +8802,6 @@
           <t>ヨシヤ</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
           <t>初めてです！</t>
@@ -8821,7 +8812,6 @@
           <t>きてみました！</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -8842,7 +8832,6 @@
           <t>よしお</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
           <t>今日は</t>
@@ -8853,7 +8842,6 @@
           <t>すこしだお</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -8874,7 +8862,6 @@
           <t>けい、さや</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
           <t>お初カップルです！</t>
@@ -8885,7 +8872,6 @@
           <t>はじめてきました！</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -8906,7 +8892,6 @@
           <t>リョウ、タク</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -8917,7 +8902,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -8938,7 +8922,6 @@
           <t>TARU</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
           <t>出張帰りに</t>
@@ -8949,7 +8932,6 @@
           <t>きたよ！</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -8970,7 +8952,6 @@
           <t>テクノ</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
         <is>
           <t>今日は</t>
@@ -8981,7 +8962,6 @@
           <t>飲むぞーーー！！</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -9002,7 +8982,6 @@
           <t>がん</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
           <t>すこし</t>
@@ -9013,7 +8992,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -9034,7 +9012,6 @@
           <t>モジャ、さない</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -9045,7 +9022,6 @@
           <t>きましたー！！</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -9066,7 +9042,6 @@
           <t>かず</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
           <t>すこし</t>
@@ -9077,7 +9052,6 @@
           <t>きたぜ</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -9151,7 +9125,6 @@
           <t>zin</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
           <t>オープン凸</t>
@@ -9162,7 +9135,6 @@
           <t>すこしだけ</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -9183,7 +9155,6 @@
           <t>みみ</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
           <t>今日も</t>
@@ -9194,7 +9165,6 @@
           <t>いきます</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -9215,7 +9185,6 @@
           <t>彩</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
         <is>
           <t>ひるばんび</t>
@@ -9226,7 +9195,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -9247,7 +9215,6 @@
           <t>のんのん</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
           <t>わたしも</t>
@@ -9258,7 +9225,6 @@
           <t>ひるばんび！</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -9279,7 +9245,6 @@
           <t>T山</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
         <is>
           <t>しごまえ</t>
@@ -9290,7 +9255,6 @@
           <t>きたわよ</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -9311,7 +9275,6 @@
           <t>M</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
           <t>いま</t>
@@ -9322,7 +9285,6 @@
           <t>きた！</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -9343,7 +9305,6 @@
           <t>らお</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
           <t>今日は</t>
@@ -9354,7 +9315,6 @@
           <t>はやめに</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -9375,7 +9335,6 @@
           <t>ゆずきん</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
           <t>連チャン</t>
@@ -9386,7 +9345,6 @@
           <t>きた！</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -9407,7 +9365,6 @@
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
           <t>あそびに</t>
@@ -9418,7 +9375,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -9439,7 +9395,6 @@
           <t>とし</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
           <t>今</t>
@@ -9450,7 +9405,6 @@
           <t>きたよん</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -9471,7 +9425,6 @@
           <t>てくのっち</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
           <t>さっき</t>
@@ -9482,7 +9435,6 @@
           <t>きまんこ</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -9503,7 +9455,6 @@
           <t>ふくてゃ</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
           <t>いま</t>
@@ -9514,7 +9465,6 @@
           <t>きちゃ</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -9568,6 +9518,475 @@
         </is>
       </c>
     </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>27253</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>19:28:59</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>今夜</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>おじゃまします</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>27255</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>20:05:54</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>あそびにきました！</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>27257</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>21:03:14</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>たかち</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr"/>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>27259</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>21:29:38</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>YZK</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>おばん</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>27261</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>21:31:18</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr"/>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>のみに</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>27263</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>21:48:40</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>高田</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>おぼえてる？</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>ひさしぶりです</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>27265</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>22:12:21</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>これから</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>行きます</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>27267</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>23:01:21</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>HGN</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>しごおわ</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>27269</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>23:06:35</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>これから</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>行きます</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>27271</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>23:27:43</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>てくのちゃん</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>のみがえり</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>27272</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>23:38:27</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>ニト</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>27275</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>00:42:39</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>タカ、なな、タク</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>一年ぶり</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>27277</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>02:29:54</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>27279</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>03:57:39</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>ツッコミはお任せのShizu / 新妻マゾヒストのミコト</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの週末営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>本日8月27日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+ツッコミはお任せのShizu
+新妻マゾヒストのミコト
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>img20260828035739.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9579,7 +9998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I353"/>
+  <dimension ref="A1:I368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24766,6 +25185,651 @@
       <c r="I353" t="inlineStr">
         <is>
           <t>きちゃ</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>19:28:59</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>27253</v>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F354" t="n">
+        <v>4</v>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>今夜</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>おじゃまします</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>20:05:54</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>27255</v>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="F355" t="n">
+        <v>3</v>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>あそびにきました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>21:03:14</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>27257</v>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>たかち</t>
+        </is>
+      </c>
+      <c r="F356" t="n">
+        <v>1</v>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>たかち</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>21:29:38</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>27259</v>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>YZK</t>
+        </is>
+      </c>
+      <c r="F357" t="n">
+        <v>1</v>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>YZK</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>おばん</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>21:31:18</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>27261</v>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="F358" t="n">
+        <v>1</v>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>のみに</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>21:48:40</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>27263</v>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>高田</t>
+        </is>
+      </c>
+      <c r="F359" t="n">
+        <v>1</v>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>高田</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>おぼえてる？</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>ひさしぶりです</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>22:12:21</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>27265</v>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="F360" t="n">
+        <v>6</v>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>これから</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>行きます</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>23:01:21</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>27267</v>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>HGN</t>
+        </is>
+      </c>
+      <c r="F361" t="n">
+        <v>1</v>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>HGN</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>しごおわ</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>23:06:35</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
+        <v>27269</v>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="F362" t="n">
+        <v>2</v>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>これから</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>行きます</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>23:27:43</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>27271</v>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>てくのちゃん</t>
+        </is>
+      </c>
+      <c r="F363" t="n">
+        <v>1</v>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>てくのちゃん</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>のみがえり</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>23:38:27</t>
+        </is>
+      </c>
+      <c r="D364" t="n">
+        <v>27272</v>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>ニト</t>
+        </is>
+      </c>
+      <c r="F364" t="n">
+        <v>1</v>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>ニト</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>00:42:39</t>
+        </is>
+      </c>
+      <c r="D365" t="n">
+        <v>27275</v>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>タカ</t>
+        </is>
+      </c>
+      <c r="F365" t="n">
+        <v>1</v>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>タカ、なな、タク</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>一年ぶり</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>00:42:39</t>
+        </is>
+      </c>
+      <c r="D366" t="n">
+        <v>27275</v>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>なな</t>
+        </is>
+      </c>
+      <c r="F366" t="n">
+        <v>2</v>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>タカ、なな、タク</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>一年ぶり</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>00:42:39</t>
+        </is>
+      </c>
+      <c r="D367" t="n">
+        <v>27275</v>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>タク</t>
+        </is>
+      </c>
+      <c r="F367" t="n">
+        <v>2</v>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>タカ、なな、タク</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>一年ぶり</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>02:29:54</t>
+        </is>
+      </c>
+      <c r="D368" t="n">
+        <v>27277</v>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="F368" t="n">
+        <v>6</v>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>すこし</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>きました</t>
         </is>
       </c>
     </row>
@@ -24780,7 +25844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D239"/>
+  <dimension ref="A1:D247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24868,7 +25932,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -24876,43 +25940,43 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>彩</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -24921,14 +25985,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -24936,7 +26000,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -24948,7 +26012,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>zin</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -24956,19 +26020,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>zin</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -24981,14 +26045,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>たいせい</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -25008,7 +26072,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>たいせい</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -25016,19 +26080,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>みなっち</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -25036,32 +26100,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>みなっち</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -25228,7 +26292,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -25236,19 +26300,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -25256,7 +26320,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -25268,7 +26332,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>マロ</t>
+          <t>コテッチャン</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -25276,39 +26340,39 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>マロ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -25316,19 +26380,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -25336,19 +26400,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -25356,19 +26420,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TKC</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -25376,7 +26440,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -25388,7 +26452,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>TKC</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -25396,19 +26460,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -25416,19 +26480,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -25436,19 +26500,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -25456,19 +26520,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -25476,19 +26540,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -25501,14 +26565,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -25516,19 +26580,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -25536,19 +26600,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -25556,19 +26620,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>しょうた</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -25576,19 +26640,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>しーたん</t>
+          <t>しょうた</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -25596,19 +26660,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>しーたん</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -25616,19 +26680,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -25636,19 +26700,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>たかやまん</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -25656,7 +26720,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -25668,7 +26732,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>たつや</t>
+          <t>たかやまん</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -25676,19 +26740,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>でで</t>
+          <t>たつや</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -25696,19 +26760,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>なまがき</t>
+          <t>でで</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -25716,19 +26780,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>なな</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -25736,19 +26800,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>なまがき</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -25756,19 +26820,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -25776,19 +26840,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -25796,19 +26860,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -25816,19 +26880,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>よしお</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -25836,19 +26900,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -25856,19 +26920,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>よしお</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -25876,19 +26940,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>よっち</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -25896,19 +26960,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -25916,7 +26980,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -25928,7 +26992,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>よっち</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -25936,19 +27000,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>れいら</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -25956,7 +27020,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -25968,7 +27032,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>オカニー</t>
+          <t>れいら</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -25976,19 +27040,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>タツヤ</t>
+          <t>オカニー</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -25996,19 +27060,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>マッスル</t>
+          <t>タク</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -26016,19 +27080,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>愛とスケベの戦士</t>
+          <t>タツヤ</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -26036,79 +27100,79 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>マッスル</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>愛とスケベの戦士</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -26116,19 +27180,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -26136,19 +27200,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>HGN</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -26156,19 +27220,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -26176,19 +27240,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TARU</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -26196,19 +27260,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -26216,19 +27280,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>nuri</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -26236,19 +27300,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -26256,19 +27320,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>★Zakk★</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -26276,19 +27340,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>あさみ</t>
+          <t>TARU</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -26296,19 +27360,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -26328,7 +27392,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>YZK</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -26336,19 +27400,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>あんこ</t>
+          <t>nuri</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -26356,19 +27420,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>うらら</t>
+          <t>−</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -26376,19